--- a/data/撲克資料.xlsx
+++ b/data/撲克資料.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my program\NLP\NLP_Poker_Chinese\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B7CFDB-0C3C-44AB-A9A1-D42CFAC7F399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13151A66-F4C8-4DAC-AD23-26C1FBF5D022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1788,64 +1788,6 @@
   </si>
   <si>
     <r>
-      <t>Edge</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（優勢）：「擁有優勢」意味著比其他玩家更具優勢。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>例如，好的手牌比弱的手牌有優勢。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>技術水準高或桌上位置好的玩家也有優勢。</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>Flop</t>
     </r>
     <r>
@@ -8557,6 +8499,42 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Edge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>（優勢）：「擁有優勢」意味著比其他玩家更具優勢。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>技術水準高或桌上位置好的玩家也有優勢。</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -9041,13 +9019,13 @@
     </row>
     <row r="2" spans="1:3" ht="27">
       <c r="A2" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="12.75">
@@ -9107,7 +9085,7 @@
     </row>
     <row r="8" spans="1:3" ht="27">
       <c r="A8" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>13</v>
@@ -9118,7 +9096,7 @@
     </row>
     <row r="9" spans="1:3" ht="13.5">
       <c r="A9" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>13</v>
@@ -9129,7 +9107,7 @@
     </row>
     <row r="10" spans="1:3" ht="13.5">
       <c r="A10" s="16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>13</v>
@@ -9140,7 +9118,7 @@
     </row>
     <row r="11" spans="1:3" ht="38.25">
       <c r="A11" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>13</v>
@@ -9162,18 +9140,18 @@
     </row>
     <row r="13" spans="1:3" ht="27">
       <c r="A13" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="12.75">
       <c r="A14" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>13</v>
@@ -9184,13 +9162,13 @@
     </row>
     <row r="15" spans="1:3" ht="54">
       <c r="A15" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="38.25">
@@ -9217,29 +9195,29 @@
     </row>
     <row r="18" spans="1:3" ht="38.25">
       <c r="A18" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="38.25">
       <c r="A19" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="54">
       <c r="A20" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>13</v>
@@ -9250,18 +9228,18 @@
     </row>
     <row r="21" spans="1:3" ht="13.5">
       <c r="A21" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="40.5">
       <c r="A22" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>13</v>
@@ -9272,7 +9250,7 @@
     </row>
     <row r="23" spans="1:3" ht="38.25">
       <c r="A23" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>13</v>
@@ -9283,24 +9261,24 @@
     </row>
     <row r="24" spans="1:3" ht="27">
       <c r="A24" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="40.5">
       <c r="A25" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="25.5">
@@ -9327,7 +9305,7 @@
     </row>
     <row r="28" spans="1:3" ht="40.5">
       <c r="A28" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>33</v>
@@ -9338,7 +9316,7 @@
     </row>
     <row r="29" spans="1:3" ht="40.5">
       <c r="A29" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>33</v>
@@ -9349,7 +9327,7 @@
     </row>
     <row r="30" spans="1:3" ht="25.5">
       <c r="A30" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>33</v>
@@ -9360,7 +9338,7 @@
     </row>
     <row r="31" spans="1:3" ht="25.5">
       <c r="A31" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>33</v>
@@ -9382,7 +9360,7 @@
     </row>
     <row r="33" spans="1:3" ht="13.5">
       <c r="A33" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>33</v>
@@ -9393,7 +9371,7 @@
     </row>
     <row r="34" spans="1:3" ht="27">
       <c r="A34" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>33</v>
@@ -9404,7 +9382,7 @@
     </row>
     <row r="35" spans="1:3" ht="40.5">
       <c r="A35" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>33</v>
@@ -9415,7 +9393,7 @@
     </row>
     <row r="36" spans="1:3" ht="40.5">
       <c r="A36" s="16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>43</v>
@@ -9426,29 +9404,29 @@
     </row>
     <row r="37" spans="1:3" ht="40.5">
       <c r="A37" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="54">
       <c r="A38" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="40.5">
       <c r="A39" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>45</v>
@@ -9459,7 +9437,7 @@
     </row>
     <row r="40" spans="1:3" ht="27">
       <c r="A40" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>45</v>
@@ -9470,10 +9448,10 @@
     </row>
     <row r="41" spans="1:3" ht="12.75">
       <c r="A41" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>184</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>185</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>87</v>
@@ -9481,40 +9459,40 @@
     </row>
     <row r="42" spans="1:3" ht="13.5">
       <c r="A42" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="27">
       <c r="A43" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="13.5">
       <c r="A44" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="40.5">
       <c r="A45" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>45</v>
@@ -9525,7 +9503,7 @@
     </row>
     <row r="46" spans="1:3" ht="54">
       <c r="A46" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>49</v>
@@ -9536,7 +9514,7 @@
     </row>
     <row r="47" spans="1:3" ht="78" customHeight="1">
       <c r="A47" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>49</v>
@@ -9547,7 +9525,7 @@
     </row>
     <row r="48" spans="1:3" ht="40.5">
       <c r="A48" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>49</v>
@@ -9558,7 +9536,7 @@
     </row>
     <row r="49" spans="1:3" ht="38.25">
       <c r="A49" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>49</v>
@@ -9569,7 +9547,7 @@
     </row>
     <row r="50" spans="1:3" ht="27">
       <c r="A50" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>49</v>
@@ -9580,13 +9558,13 @@
     </row>
     <row r="51" spans="1:3" ht="40.5">
       <c r="A51" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>49</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="38.25">
@@ -9624,7 +9602,7 @@
     </row>
     <row r="55" spans="1:3" ht="38.25">
       <c r="A55" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>60</v>
@@ -9635,7 +9613,7 @@
     </row>
     <row r="56" spans="1:3" ht="27">
       <c r="A56" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B56" t="s">
         <v>63</v>
@@ -9646,7 +9624,7 @@
     </row>
     <row r="57" spans="1:3" ht="27">
       <c r="A57" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B57" t="s">
         <v>63</v>
@@ -9657,7 +9635,7 @@
     </row>
     <row r="58" spans="1:3" ht="27">
       <c r="A58" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B58" t="s">
         <v>63</v>
@@ -9668,18 +9646,18 @@
     </row>
     <row r="59" spans="1:3" ht="40.5">
       <c r="A59" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B59" t="s">
         <v>63</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="27">
       <c r="A60" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B60" t="s">
         <v>63</v>
@@ -9690,7 +9668,7 @@
     </row>
     <row r="61" spans="1:3" ht="40.5">
       <c r="A61" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B61" t="s">
         <v>63</v>
@@ -9701,7 +9679,7 @@
     </row>
     <row r="62" spans="1:3" ht="40.5">
       <c r="A62" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B62" t="s">
         <v>63</v>
@@ -9723,128 +9701,128 @@
     </row>
     <row r="64" spans="1:3" ht="13.5">
       <c r="A64" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B64" t="s">
         <v>69</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="13.5">
       <c r="A65" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B65" t="s">
         <v>69</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="13.5">
       <c r="A66" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B66" t="s">
         <v>69</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="13.5">
       <c r="A67" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B67" t="s">
         <v>69</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="13.5">
       <c r="A68" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B68" t="s">
         <v>69</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="13.5">
       <c r="A69" s="14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
         <v>69</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="13.5">
       <c r="A70" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B70" t="s">
         <v>69</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="13.5">
       <c r="A71" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B71" t="s">
         <v>69</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="13.5">
       <c r="A72" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B72" t="s">
         <v>69</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="13.5">
       <c r="A73" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B73" t="s">
         <v>69</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="14.25">
       <c r="A74" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B74" t="s">
         <v>69</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="30.75">
       <c r="A75" s="17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B75" t="s">
         <v>69</v>
@@ -9877,7 +9855,7 @@
     </row>
     <row r="78" spans="1:3" ht="40.5">
       <c r="A78" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B78" t="s">
         <v>75</v>
@@ -9910,7 +9888,7 @@
     </row>
     <row r="81" spans="1:3" ht="27">
       <c r="A81" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B81" t="s">
         <v>75</v>
@@ -9921,7 +9899,7 @@
     </row>
     <row r="82" spans="1:3" ht="27">
       <c r="A82" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B82" t="s">
         <v>75</v>
@@ -9932,7 +9910,7 @@
     </row>
     <row r="83" spans="1:3" ht="13.5">
       <c r="A83" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B83" t="s">
         <v>75</v>
@@ -9943,7 +9921,7 @@
     </row>
     <row r="84" spans="1:3" ht="27">
       <c r="A84" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B84" t="s">
         <v>75</v>
@@ -9954,7 +9932,7 @@
     </row>
     <row r="85" spans="1:3" ht="25.5">
       <c r="A85" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B85" t="s">
         <v>86</v>
@@ -9976,7 +9954,7 @@
     </row>
     <row r="87" spans="1:3" ht="25.5">
       <c r="A87" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B87" t="s">
         <v>86</v>
@@ -9987,7 +9965,7 @@
     </row>
     <row r="88" spans="1:3" ht="27">
       <c r="A88" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B88" t="s">
         <v>86</v>
@@ -10009,7 +9987,7 @@
     </row>
     <row r="90" spans="1:3" ht="27">
       <c r="A90" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B90" t="s">
         <v>86</v>
@@ -10031,7 +10009,7 @@
     </row>
     <row r="92" spans="1:3" ht="27">
       <c r="A92" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B92" t="s">
         <v>86</v>
@@ -10053,7 +10031,7 @@
     </row>
     <row r="94" spans="1:3" ht="25.5">
       <c r="A94" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B94" t="s">
         <v>86</v>
@@ -10086,7 +10064,7 @@
     </row>
     <row r="97" spans="1:3" ht="13.5">
       <c r="A97" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B97" t="s">
         <v>86</v>
@@ -10108,7 +10086,7 @@
     </row>
     <row r="99" spans="1:3" ht="13.5">
       <c r="A99" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B99" t="s">
         <v>86</v>
@@ -10119,7 +10097,7 @@
     </row>
     <row r="100" spans="1:3" ht="13.5">
       <c r="A100" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B100" t="s">
         <v>86</v>
@@ -10152,7 +10130,7 @@
     </row>
     <row r="103" spans="1:3" ht="13.5">
       <c r="A103" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B103" t="s">
         <v>86</v>
@@ -10161,9 +10139,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="25.5">
+    <row r="104" spans="1:3" ht="13.5">
       <c r="A104" s="5" t="s">
-        <v>97</v>
+        <v>248</v>
       </c>
       <c r="B104" t="s">
         <v>86</v>
@@ -10174,7 +10152,7 @@
     </row>
     <row r="105" spans="1:3" ht="27">
       <c r="A105" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B105" t="s">
         <v>86</v>
@@ -10185,7 +10163,7 @@
     </row>
     <row r="106" spans="1:3" ht="12.75">
       <c r="A106" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B106" t="s">
         <v>86</v>
@@ -10196,7 +10174,7 @@
     </row>
     <row r="107" spans="1:3" ht="25.5">
       <c r="A107" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B107" t="s">
         <v>86</v>
@@ -10207,7 +10185,7 @@
     </row>
     <row r="108" spans="1:3" ht="27">
       <c r="A108" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B108" t="s">
         <v>86</v>
@@ -10218,7 +10196,7 @@
     </row>
     <row r="109" spans="1:3" ht="38.25">
       <c r="A109" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B109" t="s">
         <v>86</v>
@@ -10229,7 +10207,7 @@
     </row>
     <row r="110" spans="1:3" ht="38.25">
       <c r="A110" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B110" t="s">
         <v>86</v>
@@ -10240,7 +10218,7 @@
     </row>
     <row r="111" spans="1:3" ht="27">
       <c r="A111" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B111" t="s">
         <v>86</v>
@@ -10251,7 +10229,7 @@
     </row>
     <row r="112" spans="1:3" ht="13.5">
       <c r="A112" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B112" t="s">
         <v>86</v>
@@ -10262,7 +10240,7 @@
     </row>
     <row r="113" spans="1:3" ht="63.75">
       <c r="A113" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B113" t="s">
         <v>86</v>
@@ -10273,7 +10251,7 @@
     </row>
     <row r="114" spans="1:3" ht="13.5">
       <c r="A114" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B114" t="s">
         <v>86</v>
@@ -10284,7 +10262,7 @@
     </row>
     <row r="115" spans="1:3" ht="40.5">
       <c r="A115" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B115" t="s">
         <v>86</v>
@@ -10295,7 +10273,7 @@
     </row>
     <row r="116" spans="1:3" ht="25.5">
       <c r="A116" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B116" t="s">
         <v>86</v>
@@ -10306,7 +10284,7 @@
     </row>
     <row r="117" spans="1:3" ht="27">
       <c r="A117" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B117" t="s">
         <v>86</v>
@@ -10317,7 +10295,7 @@
     </row>
     <row r="118" spans="1:3" ht="25.5">
       <c r="A118" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B118" t="s">
         <v>86</v>
@@ -10328,7 +10306,7 @@
     </row>
     <row r="119" spans="1:3" ht="27">
       <c r="A119" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B119" t="s">
         <v>86</v>
@@ -10339,7 +10317,7 @@
     </row>
     <row r="120" spans="1:3" ht="27.75">
       <c r="A120" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B120" t="s">
         <v>86</v>
@@ -10350,7 +10328,7 @@
     </row>
     <row r="121" spans="1:3" ht="13.5">
       <c r="A121" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B121" t="s">
         <v>86</v>
@@ -10361,7 +10339,7 @@
     </row>
     <row r="122" spans="1:3" ht="13.5">
       <c r="A122" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B122" t="s">
         <v>86</v>
@@ -10372,7 +10350,7 @@
     </row>
     <row r="123" spans="1:3" ht="13.5">
       <c r="A123" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B123" t="s">
         <v>86</v>
@@ -10383,7 +10361,7 @@
     </row>
     <row r="124" spans="1:3" ht="27">
       <c r="A124" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B124" t="s">
         <v>86</v>
@@ -10394,7 +10372,7 @@
     </row>
     <row r="125" spans="1:3" ht="27">
       <c r="A125" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B125" t="s">
         <v>86</v>
@@ -10405,7 +10383,7 @@
     </row>
     <row r="126" spans="1:3" ht="39.6" customHeight="1">
       <c r="A126" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B126" t="s">
         <v>86</v>
@@ -10416,7 +10394,7 @@
     </row>
     <row r="127" spans="1:3" ht="38.25">
       <c r="A127" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B127" t="s">
         <v>86</v>
@@ -10427,7 +10405,7 @@
     </row>
     <row r="128" spans="1:3" ht="27">
       <c r="A128" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B128" t="s">
         <v>86</v>
@@ -10438,7 +10416,7 @@
     </row>
     <row r="129" spans="1:3" ht="12.75">
       <c r="A129" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B129" t="s">
         <v>86</v>
@@ -10449,7 +10427,7 @@
     </row>
     <row r="130" spans="1:3" ht="13.5">
       <c r="A130" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B130" t="s">
         <v>86</v>
@@ -10460,7 +10438,7 @@
     </row>
     <row r="131" spans="1:3" ht="27">
       <c r="A131" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B131" t="s">
         <v>86</v>
@@ -10471,7 +10449,7 @@
     </row>
     <row r="132" spans="1:3" ht="25.5">
       <c r="A132" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B132" t="s">
         <v>86</v>
@@ -10482,7 +10460,7 @@
     </row>
     <row r="133" spans="1:3" ht="27">
       <c r="A133" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B133" t="s">
         <v>86</v>
@@ -10493,7 +10471,7 @@
     </row>
     <row r="134" spans="1:3" ht="12.75">
       <c r="A134" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B134" t="s">
         <v>86</v>
@@ -10504,7 +10482,7 @@
     </row>
     <row r="135" spans="1:3" ht="25.5">
       <c r="A135" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B135" t="s">
         <v>86</v>
@@ -10515,7 +10493,7 @@
     </row>
     <row r="136" spans="1:3" ht="25.5">
       <c r="A136" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B136" t="s">
         <v>86</v>
@@ -10526,7 +10504,7 @@
     </row>
     <row r="137" spans="1:3" ht="40.5">
       <c r="A137" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B137" t="s">
         <v>86</v>
@@ -10537,7 +10515,7 @@
     </row>
     <row r="138" spans="1:3" ht="67.5">
       <c r="A138" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B138" t="s">
         <v>86</v>
@@ -10548,7 +10526,7 @@
     </row>
     <row r="139" spans="1:3" ht="27">
       <c r="A139" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B139" t="s">
         <v>86</v>
@@ -10559,7 +10537,7 @@
     </row>
     <row r="140" spans="1:3" ht="12.75">
       <c r="A140" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B140" t="s">
         <v>86</v>
@@ -10570,7 +10548,7 @@
     </row>
     <row r="141" spans="1:3" ht="12.75">
       <c r="A141" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B141" t="s">
         <v>86</v>
@@ -10581,7 +10559,7 @@
     </row>
     <row r="142" spans="1:3" ht="25.5">
       <c r="A142" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B142" t="s">
         <v>86</v>
@@ -10592,7 +10570,7 @@
     </row>
     <row r="143" spans="1:3" ht="13.5">
       <c r="A143" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B143" t="s">
         <v>86</v>
@@ -10603,7 +10581,7 @@
     </row>
     <row r="144" spans="1:3" ht="54">
       <c r="A144" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B144" t="s">
         <v>86</v>
@@ -10614,7 +10592,7 @@
     </row>
     <row r="145" spans="1:3" ht="27">
       <c r="A145" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B145" t="s">
         <v>86</v>
@@ -10625,112 +10603,112 @@
     </row>
     <row r="146" spans="1:3" ht="25.5">
       <c r="A146" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B146" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B146" s="6" t="s">
+      <c r="C146" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="C146" s="7" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="41.25">
       <c r="A147" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="27">
       <c r="A148" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="40.5">
       <c r="A149" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="41.45" customHeight="1">
       <c r="A150" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="38.25">
       <c r="A151" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B151" t="s">
         <v>49</v>
       </c>
       <c r="C151" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="38.25">
       <c r="A152" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B152" t="s">
         <v>49</v>
       </c>
       <c r="C152" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="27">
       <c r="A153" s="19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B153" t="s">
         <v>49</v>
       </c>
       <c r="C153" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="38.25">
       <c r="A154" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B154" t="s">
         <v>49</v>
       </c>
       <c r="C154" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="38.25">
       <c r="A155" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B155" t="s">
         <v>49</v>
       </c>
       <c r="C155" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="12.75">

--- a/data/撲克資料.xlsx
+++ b/data/撲克資料.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pytest\NLP\final\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my program\NLP\NLP_Poker_Chinese\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3EA2FE-8C19-4007-9F1D-8479E008188F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0A0D53-E1C9-4E17-89B2-8949B86F0D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2610" yWindow="2610" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="撲克流程資料分段建議" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="331">
   <si>
     <t>欄位 A (text)</t>
   </si>
@@ -8385,13 +8385,531 @@
   </si>
   <si>
     <t>彩池無法均分時的小額籌碼分配：當彩池由兩個以上玩家平分時，若有無法平分之小額籌碼（零頭），將由順時針方向算過去，最靠近發牌者(Dealer)的贏家取得。</t>
+  </si>
+  <si>
+    <t>新手補充(AI生成)</t>
+  </si>
+  <si>
+    <t>下注尺寸：開局加注</t>
+  </si>
+  <si>
+    <t>下注尺寸：持續下注</t>
+  </si>
+  <si>
+    <t>下注尺寸：以底池為基準</t>
+  </si>
+  <si>
+    <t>翻牌前再加注(3bet)該下多少？面對對手的開局加注，新手可以簡化成原加注額的 3 到 4 倍。位置好可下小一點，位置差(在對手前面行動)就下大一點來保護。</t>
+  </si>
+  <si>
+    <t>下注尺寸：3bet</t>
+  </si>
+  <si>
+    <t>新手常見的下注尺寸錯誤：價值大牌時下很大、詐唬時下很小，這會讓觀察力好的對手一眼看穿你的牌力。應該讓相同情境下的下注大小盡量一致。</t>
+  </si>
+  <si>
+    <t>下注尺寸：避免洩漏牌力</t>
+  </si>
+  <si>
+    <t>下注尺寸：避免下太小</t>
+  </si>
+  <si>
+    <t>輪到你才行動。在還沒輪到你的時候就先表態、先亮牌或先把牌丟出去，會洩漏資訊、影響其他玩家的決定，是牌桌上的大忌。</t>
+  </si>
+  <si>
+    <t>牌桌禮儀：依序行動</t>
+  </si>
+  <si>
+    <t>牌桌禮儀：避免分次下注</t>
+  </si>
+  <si>
+    <t>還沒攤牌前，不要評論正在進行的這手牌，也不要把你已蓋掉的牌內容說出來。討論進行中的牌局會影響仍在牌局裡的玩家，屬於違規行為。</t>
+  </si>
+  <si>
+    <t>牌桌禮儀：牌局進行中保持安靜</t>
+  </si>
+  <si>
+    <t>保護好你的底牌：用一個籌碼或專用牌蓋壓在牌上，避免荷官誤收或和別人的棄牌混在一起。一旦底牌碰到棄牌堆，這手牌通常就作廢了。</t>
+  </si>
+  <si>
+    <t>牌桌禮儀：保護底牌</t>
+  </si>
+  <si>
+    <t>不要對其他玩家的打法指指點點或當場教學，也不要催促別人快點行動。給每位玩家合理的思考時間，是基本的尊重。</t>
+  </si>
+  <si>
+    <t>牌桌禮儀：尊重其他玩家</t>
+  </si>
+  <si>
+    <t>該帶多少錢上桌？現金桌只帶你「願意輸掉」的金額，絕對不要帶上全部身家或生活費。把撲克的資金和日常生活開銷完全分開。</t>
+  </si>
+  <si>
+    <t>資金管理：上桌金額</t>
+  </si>
+  <si>
+    <t>資金管理：buy-in原則</t>
+  </si>
+  <si>
+    <t>選擇適合自己資金的盲注級別，不要越級挑戰高盲注的桌。級別越高、對手越強、波動越大，新手應該從小級別開始累積經驗與資金。</t>
+  </si>
+  <si>
+    <t>資金管理：選擇桌位</t>
+  </si>
+  <si>
+    <t>設定停損點：給自己定一個「今天輸到多少就離桌」的金額。輸牌後容易情緒化追損(上頭)，事先設好停損能保護你的資金與心態。</t>
+  </si>
+  <si>
+    <t>資金管理：停損</t>
+  </si>
+  <si>
+    <t>錦標賽的資金需求比現金桌更高。因為錦標賽名次波動(方差)很大，常常要打很多場才會中獎，建議單場買入只占總資金更小的比例。</t>
+  </si>
+  <si>
+    <t>資金管理：錦標賽方差</t>
+  </si>
+  <si>
+    <t>哪些起手牌一定能玩？大對子 AA、KK、QQ、JJ，以及 AK、AQ 這類強牌，在任何位置幾乎都可以加注進場，是新手最安全的選擇。</t>
+  </si>
+  <si>
+    <t>起手牌：必玩強牌</t>
+  </si>
+  <si>
+    <t>新手可以玩的中等起手牌：中小對子(例如 99、88、77)、同花的 A(如 A5s)、以及同花連張(如 JTs、98s)。這些牌有成順子或同花的潛力。</t>
+  </si>
+  <si>
+    <t>起手牌：可玩的潛力牌</t>
+  </si>
+  <si>
+    <t>起手牌：該丟的牌</t>
+  </si>
+  <si>
+    <t>位置會大幅影響起手牌選擇：在前面位置(如槍口位 UTG)後面還有很多人沒行動，只玩很強的牌；在後面位置(如按鈕位 BTN)可以玩寬一點。口訣是「位置越好，能玩的牌越多」。</t>
+  </si>
+  <si>
+    <t>起手牌：位置與範圍</t>
+  </si>
+  <si>
+    <t>同花不代表什麼牌都能玩。雖然同花的兩張牌比不同花稍強一點點，但像 92 同花這種差距太大的牌還是該丟，別被「同花」兩個字騙了。</t>
+  </si>
+  <si>
+    <t>起手牌：同花迷思</t>
+  </si>
+  <si>
+    <t>該不該 limp(只跟大盲、不加注就進場)？新手通常不建議 limp，因為放棄了主動權、也容易讓很多人一起看翻牌。要玩這手牌就用加注進場，不想玩就棄牌。</t>
+  </si>
+  <si>
+    <t>起手牌：避免limp</t>
+  </si>
+  <si>
+    <t>人少的牌桌(例如 6 人桌)起手牌可以比 9 人滿桌玩得更寬，因為位置輪轉快、盲注壓力大；滿桌則要打得更緊一些。</t>
+  </si>
+  <si>
+    <t>起手牌：依人數調整</t>
+  </si>
+  <si>
+    <t>最常見的新手錯誤是「玩太多手牌」。覺得每手都想參與，結果常拿著弱牌進場、翻牌後陷入兩難。正確做法是打緊一點，多數爛牌直接棄掉。</t>
+  </si>
+  <si>
+    <t>常見錯誤：玩太多手</t>
+  </si>
+  <si>
+    <t>新手很愛 limp(只跟不加注)進場。這會放棄主動權、把底池搞得很多人一起玩。建議：值得玩的牌就用加注進場，不值得就棄牌，少用 limp。</t>
+  </si>
+  <si>
+    <t>常見錯誤：愛limp</t>
+  </si>
+  <si>
+    <t>常見錯誤：無腦跟注</t>
+  </si>
+  <si>
+    <t>常見錯誤：盲目追聽牌</t>
+  </si>
+  <si>
+    <t>上頭(tilt)：輸了一手大牌之後情緒失控、開始亂打想討回來，結果輸更多。最好的處理方式是先離桌休息、冷靜下來，再決定要不要繼續。</t>
+  </si>
+  <si>
+    <t>常見錯誤：上頭(tilt)</t>
+  </si>
+  <si>
+    <t>太黏成手牌：拿到一對 A 就死不放手，明明牌面出現同花或順子的危險、對手又重注，還是硬跟到底。學會在情況不對時放掉好牌，是進步的關鍵。</t>
+  </si>
+  <si>
+    <t>常見錯誤：太黏成手牌</t>
+  </si>
+  <si>
+    <t>不看位置就行動：忽略自己在這手牌是先行動還是後行動。位置差時要更謹慎，位置好(較晚行動)才有資訊優勢可以玩寬一點。</t>
+  </si>
+  <si>
+    <t>常見錯誤：忽略位置</t>
+  </si>
+  <si>
+    <t>下注大小要用「底池的幾分之幾」來想，而不是固定幾個籌碼。用相對底池的概念，才能在不同底池大小下都做出合理的下注。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>下注太小的問題：在大底池只下一點點，等於送給對手很好的賠率去追聽牌。想要保護成手牌或施壓，就要下到足夠的大小。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>開局加注該下多少？常見的標準開局加注是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>個大盲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(BB)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。線上多用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2~2.5 BB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，實體現場多用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 3 BB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。若前面已有人只跟大盲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(limp)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>進場，通常每多一個</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> limper </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>就多加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 1 BB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>持續下注</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(c_bet)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>要下多大？翻牌後第一槍通常下底池的三分之一到三分之二。對手不容易聽牌可以下小，約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 1/3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>底池；很多同花、順子聽牌就下大一點，約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2/3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 3/4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>底池施壓。</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>下注時請一次把籌碼放到下注線前，不要分好幾次把籌碼一點一點推出去，分次推注通常不被允許，只會算第一次的金額。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>資金管理的常見原則：玩現金桌時，準備約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 20 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>個買入的總資金，這樣即使連續輸幾局，也不會一次就破產出局。</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>該直接丟掉的起手牌：不成對、又不同花、數字又差很多的雜牌，新手直接棄牌就好，不要因為想玩而勉強進場。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>無腦跟注是燒錢的壞習慣：沒有明確理由就一直跟注到底。每次跟注前先問自己「我跟的理由是什麼」，要嘛有勝算或好賠率，要嘛就棄牌。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>追聽牌不算賠率：為了湊同花或順子一路跟注，卻沒算底池賠率划不划算。聽牌要看「補牌張數」和「底池給的賠率」是否值得追。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://monsterstack.com.tw/</t>
+  </si>
+  <si>
+    <t>價值下注解釋</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>什麼是價值下注？價值下注是指你覺得自己的手牌是領先的，因此下注是為了從對手那裡「榨取更多籌碼」，下注金額不能太大，否則會嚇跑對手</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>下注是你在遊戲中唯一能主動發聲的方式，所以才會有這麼多種下注策略。每一種下注金額、時機、方式，其實都是在告訴對手一個訊息，也是在試圖引導他們做出你希望的反應。不同情況，需要不同目的的下注，增加不可預測性，讓對手無法掌握你的節奏</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>下處策略意義</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="30">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -8567,6 +9085,42 @@
       <family val="3"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -8585,10 +9139,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -8653,9 +9208,22 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="一般 2" xfId="1" xr:uid="{ECA66C50-1599-46DB-8458-54BE81690104}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -8875,15 +9443,15 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C996"/>
-  <sheetFormatPr defaultColWidth="12.7265625" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:C995"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="127.1796875" style="9" customWidth="1"/>
-    <col min="2" max="3" width="33.26953125" customWidth="1"/>
-    <col min="5" max="5" width="12.7265625" customWidth="1"/>
+    <col min="1" max="1" width="127.140625" style="9" customWidth="1"/>
+    <col min="2" max="3" width="33.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12.5">
+    <row r="1" spans="1:3" ht="12.75">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -8894,7 +9462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="13">
+    <row r="2" spans="1:3" ht="13.5">
       <c r="A2" s="12" t="s">
         <v>234</v>
       </c>
@@ -8905,7 +9473,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="12.5">
+    <row r="3" spans="1:3" ht="12.75">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -8916,7 +9484,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="12.5">
+    <row r="4" spans="1:3" ht="12.75">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
@@ -8927,7 +9495,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="12.5">
+    <row r="5" spans="1:3" ht="12.75">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -8938,7 +9506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="12.5">
+    <row r="6" spans="1:3" ht="12.75">
       <c r="A6" s="5" t="s">
         <v>262</v>
       </c>
@@ -8949,7 +9517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="25">
+    <row r="7" spans="1:3" ht="25.5">
       <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
@@ -8960,7 +9528,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="26">
+    <row r="8" spans="1:3" ht="25.5">
       <c r="A8" s="10" t="s">
         <v>263</v>
       </c>
@@ -8971,7 +9539,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="13">
+    <row r="9" spans="1:3" ht="13.5">
       <c r="A9" s="10" t="s">
         <v>233</v>
       </c>
@@ -8982,7 +9550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13">
+    <row r="10" spans="1:3" ht="13.5">
       <c r="A10" s="16" t="s">
         <v>175</v>
       </c>
@@ -8993,7 +9561,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="37.5">
+    <row r="11" spans="1:3" ht="38.25">
       <c r="A11" s="3" t="s">
         <v>181</v>
       </c>
@@ -9004,7 +9572,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="12.5">
+    <row r="12" spans="1:3" ht="12.75">
       <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
@@ -9015,7 +9583,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="26">
+    <row r="13" spans="1:3" ht="27">
       <c r="A13" s="10" t="s">
         <v>232</v>
       </c>
@@ -9026,7 +9594,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="12.5">
+    <row r="14" spans="1:3" ht="12.75">
       <c r="A14" s="3" t="s">
         <v>156</v>
       </c>
@@ -9037,7 +9605,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="39">
+    <row r="15" spans="1:3" ht="40.5">
       <c r="A15" s="10" t="s">
         <v>231</v>
       </c>
@@ -9048,7 +9616,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="25">
+    <row r="16" spans="1:3" ht="25.5">
       <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
@@ -9059,7 +9627,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="25">
+    <row r="17" spans="1:3" ht="25.5">
       <c r="A17" s="3" t="s">
         <v>23</v>
       </c>
@@ -9070,7 +9638,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="25">
+    <row r="18" spans="1:3" ht="25.5">
       <c r="A18" s="3" t="s">
         <v>158</v>
       </c>
@@ -9081,7 +9649,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="25">
+    <row r="19" spans="1:3" ht="25.5">
       <c r="A19" s="3" t="s">
         <v>160</v>
       </c>
@@ -9092,7 +9660,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="39">
+    <row r="20" spans="1:3" ht="40.5">
       <c r="A20" s="10" t="s">
         <v>229</v>
       </c>
@@ -9103,7 +9671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="13">
+    <row r="21" spans="1:3" ht="13.5">
       <c r="A21" s="10" t="s">
         <v>228</v>
       </c>
@@ -9114,7 +9682,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="26">
+    <row r="22" spans="1:3" ht="40.5">
       <c r="A22" s="10" t="s">
         <v>125</v>
       </c>
@@ -9125,7 +9693,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="25">
+    <row r="23" spans="1:3" ht="25.5">
       <c r="A23" s="3" t="s">
         <v>162</v>
       </c>
@@ -9136,7 +9704,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="13">
+    <row r="24" spans="1:3" ht="13.5">
       <c r="A24" s="10" t="s">
         <v>227</v>
       </c>
@@ -9147,7 +9715,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="26">
+    <row r="25" spans="1:3" ht="27">
       <c r="A25" s="10" t="s">
         <v>226</v>
       </c>
@@ -9158,7 +9726,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="12.5">
+    <row r="26" spans="1:3" ht="12.75">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -9169,7 +9737,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="26">
+    <row r="27" spans="1:3" ht="25.5">
       <c r="A27" s="10" t="s">
         <v>264</v>
       </c>
@@ -9180,7 +9748,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="26">
+    <row r="28" spans="1:3" ht="27">
       <c r="A28" s="10" t="s">
         <v>176</v>
       </c>
@@ -9191,7 +9759,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="26">
+    <row r="29" spans="1:3" ht="27">
       <c r="A29" s="10" t="s">
         <v>199</v>
       </c>
@@ -9202,7 +9770,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="25">
+    <row r="30" spans="1:3" ht="25.5">
       <c r="A30" s="3" t="s">
         <v>167</v>
       </c>
@@ -9213,7 +9781,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="25">
+    <row r="31" spans="1:3" ht="25.5">
       <c r="A31" s="3" t="s">
         <v>168</v>
       </c>
@@ -9224,7 +9792,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="25">
+    <row r="32" spans="1:3" ht="25.5">
       <c r="A32" s="3" t="s">
         <v>36</v>
       </c>
@@ -9235,7 +9803,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="13">
+    <row r="33" spans="1:3" ht="13.5">
       <c r="A33" s="10" t="s">
         <v>177</v>
       </c>
@@ -9246,7 +9814,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="26">
+    <row r="34" spans="1:3" ht="27">
       <c r="A34" s="10" t="s">
         <v>225</v>
       </c>
@@ -9257,7 +9825,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="26">
+    <row r="35" spans="1:3" ht="27">
       <c r="A35" s="10" t="s">
         <v>224</v>
       </c>
@@ -9268,7 +9836,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="39">
+    <row r="36" spans="1:3" ht="40.5">
       <c r="A36" s="16" t="s">
         <v>169</v>
       </c>
@@ -9279,7 +9847,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="26">
+    <row r="37" spans="1:3" ht="27">
       <c r="A37" s="10" t="s">
         <v>170</v>
       </c>
@@ -9290,7 +9858,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="39">
+    <row r="38" spans="1:3" ht="40.5">
       <c r="A38" s="10" t="s">
         <v>171</v>
       </c>
@@ -9301,7 +9869,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="26">
+    <row r="39" spans="1:3" ht="27">
       <c r="A39" s="10" t="s">
         <v>126</v>
       </c>
@@ -9312,7 +9880,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="26">
+    <row r="40" spans="1:3" ht="27">
       <c r="A40" s="10" t="s">
         <v>172</v>
       </c>
@@ -9323,7 +9891,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="13">
+    <row r="41" spans="1:3" ht="13.5">
       <c r="A41" s="10" t="s">
         <v>257</v>
       </c>
@@ -9334,7 +9902,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="32.5" customHeight="1">
+    <row r="42" spans="1:3" ht="32.450000000000003" customHeight="1">
       <c r="A42" s="26" t="s">
         <v>222</v>
       </c>
@@ -9345,14 +9913,14 @@
         <v>221</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="13.5">
+    <row r="43" spans="1:3" ht="14.25">
       <c r="A43" s="25" t="s">
         <v>256</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="21"/>
     </row>
-    <row r="44" spans="1:3" ht="26">
+    <row r="44" spans="1:3" ht="27">
       <c r="A44" s="10" t="s">
         <v>255</v>
       </c>
@@ -9363,7 +9931,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="13">
+    <row r="45" spans="1:3" ht="13.5">
       <c r="A45" s="15" t="s">
         <v>223</v>
       </c>
@@ -9374,7 +9942,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="26">
+    <row r="46" spans="1:3" ht="27">
       <c r="A46" s="10" t="s">
         <v>179</v>
       </c>
@@ -9385,7 +9953,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="39">
+    <row r="47" spans="1:3" ht="40.5">
       <c r="A47" s="10" t="s">
         <v>220</v>
       </c>
@@ -9407,7 +9975,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="26">
+    <row r="49" spans="1:3" ht="27">
       <c r="A49" s="10" t="s">
         <v>219</v>
       </c>
@@ -9418,7 +9986,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="37.5">
+    <row r="50" spans="1:3" ht="38.25">
       <c r="A50" s="10" t="s">
         <v>184</v>
       </c>
@@ -9429,7 +9997,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="26">
+    <row r="51" spans="1:3" ht="27">
       <c r="A51" s="10" t="s">
         <v>218</v>
       </c>
@@ -9440,7 +10008,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="26">
+    <row r="52" spans="1:3" ht="27">
       <c r="A52" s="10" t="s">
         <v>217</v>
       </c>
@@ -9451,7 +10019,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="25">
+    <row r="53" spans="1:3" ht="25.5">
       <c r="A53" s="3" t="s">
         <v>53</v>
       </c>
@@ -9462,7 +10030,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="25">
+    <row r="54" spans="1:3" ht="25.5">
       <c r="A54" s="3" t="s">
         <v>55</v>
       </c>
@@ -9473,7 +10041,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="25">
+    <row r="55" spans="1:3" ht="25.5">
       <c r="A55" s="3" t="s">
         <v>57</v>
       </c>
@@ -9484,7 +10052,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="25">
+    <row r="56" spans="1:3" ht="25.5">
       <c r="A56" s="3" t="s">
         <v>183</v>
       </c>
@@ -9495,7 +10063,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="26">
+    <row r="57" spans="1:3" ht="27">
       <c r="A57" s="13" t="s">
         <v>147</v>
       </c>
@@ -9506,7 +10074,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="26">
+    <row r="58" spans="1:3" ht="27">
       <c r="A58" s="12" t="s">
         <v>148</v>
       </c>
@@ -9517,7 +10085,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="26">
+    <row r="59" spans="1:3" ht="27">
       <c r="A59" s="12" t="s">
         <v>149</v>
       </c>
@@ -9528,7 +10096,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="26">
+    <row r="60" spans="1:3" ht="27">
       <c r="A60" s="12" t="s">
         <v>150</v>
       </c>
@@ -9539,7 +10107,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="26">
+    <row r="61" spans="1:3" ht="27">
       <c r="A61" s="5" t="s">
         <v>151</v>
       </c>
@@ -9550,7 +10118,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="26">
+    <row r="62" spans="1:3" ht="27">
       <c r="A62" s="5" t="s">
         <v>186</v>
       </c>
@@ -9561,7 +10129,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="26">
+    <row r="63" spans="1:3" ht="27">
       <c r="A63" s="12" t="s">
         <v>152</v>
       </c>
@@ -9572,7 +10140,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="25">
+    <row r="64" spans="1:3" ht="25.5">
       <c r="A64" s="7" t="s">
         <v>66</v>
       </c>
@@ -9583,7 +10151,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="13">
+    <row r="65" spans="1:3" ht="13.5">
       <c r="A65" s="14" t="s">
         <v>146</v>
       </c>
@@ -9594,7 +10162,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="13">
+    <row r="66" spans="1:3" ht="13.5">
       <c r="A66" s="14" t="s">
         <v>145</v>
       </c>
@@ -9605,7 +10173,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="13">
+    <row r="67" spans="1:3" ht="13.5">
       <c r="A67" s="15" t="s">
         <v>144</v>
       </c>
@@ -9616,7 +10184,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="13">
+    <row r="68" spans="1:3" ht="13.5">
       <c r="A68" s="14" t="s">
         <v>143</v>
       </c>
@@ -9627,7 +10195,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="13">
+    <row r="69" spans="1:3" ht="13.5">
       <c r="A69" s="15" t="s">
         <v>142</v>
       </c>
@@ -9638,7 +10206,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="13">
+    <row r="70" spans="1:3" ht="13.5">
       <c r="A70" s="14" t="s">
         <v>141</v>
       </c>
@@ -9649,7 +10217,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="13">
+    <row r="71" spans="1:3" ht="13.5">
       <c r="A71" s="15" t="s">
         <v>140</v>
       </c>
@@ -9660,7 +10228,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="13">
+    <row r="72" spans="1:3" ht="13.5">
       <c r="A72" s="14" t="s">
         <v>139</v>
       </c>
@@ -9671,7 +10239,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="13">
+    <row r="73" spans="1:3" ht="13.5">
       <c r="A73" s="14" t="s">
         <v>138</v>
       </c>
@@ -9682,7 +10250,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="13">
+    <row r="74" spans="1:3" ht="13.5">
       <c r="A74" s="20" t="s">
         <v>198</v>
       </c>
@@ -9693,7 +10261,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="13.5">
+    <row r="75" spans="1:3" ht="14.25">
       <c r="A75" s="18" t="s">
         <v>188</v>
       </c>
@@ -9715,7 +10283,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="25">
+    <row r="77" spans="1:3" ht="25.5">
       <c r="A77" s="7" t="s">
         <v>70</v>
       </c>
@@ -9726,7 +10294,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="25">
+    <row r="78" spans="1:3" ht="25.5">
       <c r="A78" s="7" t="s">
         <v>72</v>
       </c>
@@ -9737,7 +10305,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="26">
+    <row r="79" spans="1:3" ht="27">
       <c r="A79" s="11" t="s">
         <v>127</v>
       </c>
@@ -9748,7 +10316,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="37.5">
+    <row r="80" spans="1:3" ht="38.25">
       <c r="A80" s="5" t="s">
         <v>76</v>
       </c>
@@ -9759,7 +10327,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="37.5">
+    <row r="81" spans="1:3" ht="38.25">
       <c r="A81" s="5" t="s">
         <v>78</v>
       </c>
@@ -9770,7 +10338,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="26">
+    <row r="82" spans="1:3" ht="27">
       <c r="A82" s="11" t="s">
         <v>128</v>
       </c>
@@ -9781,7 +10349,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="26">
+    <row r="83" spans="1:3" ht="27">
       <c r="A83" s="11" t="s">
         <v>129</v>
       </c>
@@ -9792,7 +10360,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="13">
+    <row r="84" spans="1:3" ht="13.5">
       <c r="A84" s="11" t="s">
         <v>130</v>
       </c>
@@ -9803,7 +10371,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="26">
+    <row r="85" spans="1:3" ht="27">
       <c r="A85" s="11" t="s">
         <v>131</v>
       </c>
@@ -9814,7 +10382,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="25">
+    <row r="86" spans="1:3" ht="25.5">
       <c r="A86" s="5" t="s">
         <v>165</v>
       </c>
@@ -9825,7 +10393,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="25">
+    <row r="87" spans="1:3" ht="25.5">
       <c r="A87" s="5" t="s">
         <v>86</v>
       </c>
@@ -9836,7 +10404,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="12.5">
+    <row r="88" spans="1:3" ht="12.75">
       <c r="A88" s="5" t="s">
         <v>189</v>
       </c>
@@ -9847,7 +10415,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="13">
+    <row r="89" spans="1:3" ht="13.5">
       <c r="A89" s="5" t="s">
         <v>216</v>
       </c>
@@ -9858,7 +10426,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="25">
+    <row r="90" spans="1:3" ht="25.5">
       <c r="A90" s="5" t="s">
         <v>87</v>
       </c>
@@ -9869,7 +10437,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="13">
+    <row r="91" spans="1:3" ht="13.5">
       <c r="A91" s="11" t="s">
         <v>132</v>
       </c>
@@ -9880,7 +10448,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="12.5">
+    <row r="92" spans="1:3" ht="12.75">
       <c r="A92" s="5" t="s">
         <v>88</v>
       </c>
@@ -9891,7 +10459,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="12.5">
+    <row r="93" spans="1:3" ht="12.75">
       <c r="A93" s="5" t="s">
         <v>246</v>
       </c>
@@ -9902,7 +10470,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="25">
+    <row r="94" spans="1:3" ht="25.5">
       <c r="A94" s="5" t="s">
         <v>89</v>
       </c>
@@ -9913,7 +10481,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="12.5">
+    <row r="95" spans="1:3" ht="12.75">
       <c r="A95" s="5" t="s">
         <v>190</v>
       </c>
@@ -9924,7 +10492,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="12.5">
+    <row r="96" spans="1:3" ht="12.75">
       <c r="A96" s="5" t="s">
         <v>90</v>
       </c>
@@ -9935,7 +10503,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="12.5">
+    <row r="97" spans="1:3" ht="25.5">
       <c r="A97" s="5" t="s">
         <v>91</v>
       </c>
@@ -9946,7 +10514,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="13">
+    <row r="98" spans="1:3" ht="13.5">
       <c r="A98" s="5" t="s">
         <v>215</v>
       </c>
@@ -9957,7 +10525,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="25">
+    <row r="99" spans="1:3" ht="25.5">
       <c r="A99" s="5" t="s">
         <v>92</v>
       </c>
@@ -9968,7 +10536,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="13">
+    <row r="100" spans="1:3" ht="13.5">
       <c r="A100" s="5" t="s">
         <v>214</v>
       </c>
@@ -9979,7 +10547,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="13">
+    <row r="101" spans="1:3" ht="13.5">
       <c r="A101" s="5" t="s">
         <v>213</v>
       </c>
@@ -9990,7 +10558,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="12.5">
+    <row r="102" spans="1:3" ht="12.75">
       <c r="A102" s="5" t="s">
         <v>93</v>
       </c>
@@ -10001,7 +10569,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="12.5">
+    <row r="103" spans="1:3" ht="12.75">
       <c r="A103" s="5" t="s">
         <v>94</v>
       </c>
@@ -10012,7 +10580,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="13">
+    <row r="104" spans="1:3" ht="13.5">
       <c r="A104" s="5" t="s">
         <v>212</v>
       </c>
@@ -10023,7 +10591,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="13">
+    <row r="105" spans="1:3" ht="13.5">
       <c r="A105" s="5" t="s">
         <v>236</v>
       </c>
@@ -10034,7 +10602,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="13">
+    <row r="106" spans="1:3" ht="13.5">
       <c r="A106" s="5" t="s">
         <v>191</v>
       </c>
@@ -10045,7 +10613,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="12.5">
+    <row r="107" spans="1:3" ht="12.75">
       <c r="A107" s="5" t="s">
         <v>95</v>
       </c>
@@ -10056,7 +10624,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="12.5">
+    <row r="108" spans="1:3" ht="12.75">
       <c r="A108" s="5" t="s">
         <v>96</v>
       </c>
@@ -10067,7 +10635,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="13">
+    <row r="109" spans="1:3" ht="13.5">
       <c r="A109" s="5" t="s">
         <v>134</v>
       </c>
@@ -10078,7 +10646,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="25">
+    <row r="110" spans="1:3" ht="25.5">
       <c r="A110" s="5" t="s">
         <v>97</v>
       </c>
@@ -10089,7 +10657,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="25">
+    <row r="111" spans="1:3" ht="25.5">
       <c r="A111" s="5" t="s">
         <v>98</v>
       </c>
@@ -10100,7 +10668,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="26">
+    <row r="112" spans="1:3" ht="27">
       <c r="A112" s="5" t="s">
         <v>211</v>
       </c>
@@ -10111,7 +10679,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="13">
+    <row r="113" spans="1:3" ht="13.5">
       <c r="A113" s="5" t="s">
         <v>210</v>
       </c>
@@ -10122,7 +10690,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="50">
+    <row r="114" spans="1:3" ht="51">
       <c r="A114" s="5" t="s">
         <v>99</v>
       </c>
@@ -10133,7 +10701,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="13">
+    <row r="115" spans="1:3" ht="13.5">
       <c r="A115" s="5" t="s">
         <v>235</v>
       </c>
@@ -10144,7 +10712,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="26">
+    <row r="116" spans="1:3" ht="27">
       <c r="A116" s="11" t="s">
         <v>133</v>
       </c>
@@ -10155,7 +10723,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="12.5">
+    <row r="117" spans="1:3" ht="12.75">
       <c r="A117" s="5" t="s">
         <v>100</v>
       </c>
@@ -10166,7 +10734,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="26">
+    <row r="118" spans="1:3" ht="27">
       <c r="A118" s="5" t="s">
         <v>192</v>
       </c>
@@ -10177,7 +10745,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="25">
+    <row r="119" spans="1:3" ht="25.5">
       <c r="A119" s="5" t="s">
         <v>101</v>
       </c>
@@ -10188,7 +10756,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="13">
+    <row r="120" spans="1:3" ht="13.5">
       <c r="A120" s="5" t="s">
         <v>193</v>
       </c>
@@ -10199,7 +10767,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="25">
+    <row r="121" spans="1:3" ht="25.5">
       <c r="A121" s="5" t="s">
         <v>247</v>
       </c>
@@ -10210,7 +10778,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="13">
+    <row r="122" spans="1:3" ht="13.5">
       <c r="A122" s="5" t="s">
         <v>194</v>
       </c>
@@ -10221,7 +10789,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="13">
+    <row r="123" spans="1:3" ht="13.5">
       <c r="A123" s="5" t="s">
         <v>209</v>
       </c>
@@ -10232,7 +10800,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="13">
+    <row r="124" spans="1:3" ht="13.5">
       <c r="A124" s="5" t="s">
         <v>174</v>
       </c>
@@ -10243,7 +10811,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="26">
+    <row r="125" spans="1:3" ht="27">
       <c r="A125" s="5" t="s">
         <v>208</v>
       </c>
@@ -10254,7 +10822,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="13">
+    <row r="126" spans="1:3" ht="13.5">
       <c r="A126" s="5" t="s">
         <v>207</v>
       </c>
@@ -10265,7 +10833,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="39.65" customHeight="1">
+    <row r="127" spans="1:3" ht="39.6" customHeight="1">
       <c r="A127" s="5" t="s">
         <v>206</v>
       </c>
@@ -10276,7 +10844,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="25">
+    <row r="128" spans="1:3" ht="25.5">
       <c r="A128" s="5" t="s">
         <v>102</v>
       </c>
@@ -10287,7 +10855,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="26">
+    <row r="129" spans="1:3" ht="27">
       <c r="A129" s="5" t="s">
         <v>205</v>
       </c>
@@ -10298,7 +10866,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="12.5">
+    <row r="130" spans="1:3" ht="12.75">
       <c r="A130" s="5" t="s">
         <v>103</v>
       </c>
@@ -10309,7 +10877,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="13">
+    <row r="131" spans="1:3" ht="13.5">
       <c r="A131" s="5" t="s">
         <v>153</v>
       </c>
@@ -10320,7 +10888,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="13">
+    <row r="132" spans="1:3" ht="13.5">
       <c r="A132" s="5" t="s">
         <v>195</v>
       </c>
@@ -10331,7 +10899,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="25">
+    <row r="133" spans="1:3" ht="25.5">
       <c r="A133" s="5" t="s">
         <v>104</v>
       </c>
@@ -10342,7 +10910,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="26">
+    <row r="134" spans="1:3" ht="27">
       <c r="A134" s="5" t="s">
         <v>204</v>
       </c>
@@ -10353,7 +10921,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="12.5">
+    <row r="135" spans="1:3" ht="12.75">
       <c r="A135" s="5" t="s">
         <v>105</v>
       </c>
@@ -10364,7 +10932,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="25">
+    <row r="136" spans="1:3" ht="25.5">
       <c r="A136" s="5" t="s">
         <v>106</v>
       </c>
@@ -10375,7 +10943,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="25">
+    <row r="137" spans="1:3" ht="25.5">
       <c r="A137" s="5" t="s">
         <v>107</v>
       </c>
@@ -10386,7 +10954,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="26">
+    <row r="138" spans="1:3" ht="27">
       <c r="A138" s="5" t="s">
         <v>203</v>
       </c>
@@ -10397,7 +10965,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="39">
+    <row r="139" spans="1:3" ht="40.5">
       <c r="A139" s="5" t="s">
         <v>202</v>
       </c>
@@ -10408,7 +10976,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="25">
+    <row r="140" spans="1:3" ht="25.5">
       <c r="A140" s="5" t="s">
         <v>248</v>
       </c>
@@ -10419,7 +10987,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="12.5">
+    <row r="141" spans="1:3" ht="12.75">
       <c r="A141" s="5" t="s">
         <v>108</v>
       </c>
@@ -10430,7 +10998,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="12.5">
+    <row r="142" spans="1:3" ht="12.75">
       <c r="A142" s="5" t="s">
         <v>109</v>
       </c>
@@ -10441,7 +11009,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="25">
+    <row r="143" spans="1:3" ht="25.5">
       <c r="A143" s="5" t="s">
         <v>110</v>
       </c>
@@ -10452,7 +11020,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="13">
+    <row r="144" spans="1:3" ht="13.5">
       <c r="A144" s="5" t="s">
         <v>135</v>
       </c>
@@ -10463,7 +11031,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="39">
+    <row r="145" spans="1:3" ht="40.5">
       <c r="A145" s="5" t="s">
         <v>136</v>
       </c>
@@ -10474,7 +11042,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="26">
+    <row r="146" spans="1:3" ht="27">
       <c r="A146" s="5" t="s">
         <v>201</v>
       </c>
@@ -10485,7 +11053,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="13.5">
+    <row r="147" spans="1:3" ht="28.5">
       <c r="A147" s="12" t="s">
         <v>259</v>
       </c>
@@ -10496,7 +11064,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="25">
+    <row r="148" spans="1:3" ht="25.5">
       <c r="A148" s="7" t="s">
         <v>249</v>
       </c>
@@ -10507,7 +11075,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="26.5">
+    <row r="149" spans="1:3" ht="27.75">
       <c r="A149" s="5" t="s">
         <v>258</v>
       </c>
@@ -10518,7 +11086,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="26">
+    <row r="150" spans="1:3" ht="27">
       <c r="A150" s="13" t="s">
         <v>251</v>
       </c>
@@ -10529,7 +11097,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="26">
+    <row r="151" spans="1:3" ht="27">
       <c r="A151" s="12" t="s">
         <v>196</v>
       </c>
@@ -10540,7 +11108,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="41.5" customHeight="1">
+    <row r="152" spans="1:3" ht="41.45" customHeight="1">
       <c r="A152" s="12" t="s">
         <v>200</v>
       </c>
@@ -10551,7 +11119,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="25">
+    <row r="153" spans="1:3" ht="25.5">
       <c r="A153" s="8" t="s">
         <v>116</v>
       </c>
@@ -10562,7 +11130,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="25">
+    <row r="154" spans="1:3" ht="25.5">
       <c r="A154" s="8" t="s">
         <v>118</v>
       </c>
@@ -10573,7 +11141,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="26">
+    <row r="155" spans="1:3" ht="27">
       <c r="A155" s="19" t="s">
         <v>197</v>
       </c>
@@ -10584,7 +11152,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="25">
+    <row r="156" spans="1:3" ht="25.5">
       <c r="A156" s="8" t="s">
         <v>121</v>
       </c>
@@ -10595,7 +11163,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="25">
+    <row r="157" spans="1:3" ht="25.5">
       <c r="A157" s="8" t="s">
         <v>123</v>
       </c>
@@ -10617,7 +11185,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="32" customHeight="1">
+    <row r="159" spans="1:3" ht="32.1" customHeight="1">
       <c r="A159" s="18" t="s">
         <v>244</v>
       </c>
@@ -10628,7 +11196,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="13.5">
+    <row r="160" spans="1:3" ht="14.25">
       <c r="A160" s="22" t="s">
         <v>245</v>
       </c>
@@ -10639,7 +11207,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="13.5">
+    <row r="161" spans="1:3" ht="14.25">
       <c r="A161" s="22" t="s">
         <v>242</v>
       </c>
@@ -10650,7 +11218,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="27">
+    <row r="162" spans="1:3" ht="28.5">
       <c r="A162" s="23" t="s">
         <v>253</v>
       </c>
@@ -10661,3343 +11229,3561 @@
         <v>252</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="12.5">
-      <c r="A163" s="5"/>
-      <c r="B163" s="22"/>
-      <c r="C163" s="5"/>
-    </row>
-    <row r="164" spans="1:3" ht="12.5">
-      <c r="A164" s="5"/>
-      <c r="B164" s="22"/>
-      <c r="C164" s="5"/>
-    </row>
-    <row r="165" spans="1:3" ht="12.5">
-      <c r="A165" s="5"/>
-      <c r="C165" s="5"/>
-    </row>
-    <row r="166" spans="1:3" ht="12.5">
-      <c r="A166" s="5"/>
-      <c r="C166" s="5"/>
-    </row>
-    <row r="167" spans="1:3" ht="12.5">
-      <c r="A167" s="5"/>
-      <c r="C167" s="5"/>
-    </row>
-    <row r="168" spans="1:3" ht="12.5">
-      <c r="A168" s="5"/>
-      <c r="C168" s="5"/>
-    </row>
-    <row r="169" spans="1:3" ht="12.5">
-      <c r="A169" s="5"/>
-      <c r="C169" s="5"/>
-    </row>
-    <row r="170" spans="1:3" ht="12.5">
-      <c r="A170" s="5"/>
-      <c r="C170" s="5"/>
-    </row>
-    <row r="171" spans="1:3" ht="12.5">
-      <c r="A171" s="5"/>
-      <c r="C171" s="5"/>
-    </row>
-    <row r="172" spans="1:3" ht="12.5">
-      <c r="A172" s="5"/>
-      <c r="C172" s="5"/>
-    </row>
-    <row r="173" spans="1:3" ht="12.5">
-      <c r="A173" s="5"/>
-      <c r="C173" s="5"/>
-    </row>
-    <row r="174" spans="1:3" ht="12.5">
-      <c r="A174" s="5"/>
-      <c r="C174" s="5"/>
-    </row>
-    <row r="175" spans="1:3" ht="12.5">
-      <c r="A175" s="5"/>
-      <c r="C175" s="5"/>
-    </row>
-    <row r="176" spans="1:3" ht="12.5">
-      <c r="A176" s="5"/>
-      <c r="C176" s="5"/>
-    </row>
-    <row r="177" spans="1:3" ht="12.5">
-      <c r="A177" s="5"/>
-      <c r="C177" s="5"/>
-    </row>
-    <row r="178" spans="1:3" ht="12.5">
-      <c r="A178" s="5"/>
-      <c r="C178" s="5"/>
-    </row>
-    <row r="179" spans="1:3" ht="12.5">
-      <c r="A179" s="5"/>
-      <c r="C179" s="5"/>
-    </row>
-    <row r="180" spans="1:3" ht="12.5">
-      <c r="A180" s="5"/>
-      <c r="C180" s="5"/>
-    </row>
-    <row r="181" spans="1:3" ht="12.5">
-      <c r="A181" s="5"/>
-      <c r="C181" s="5"/>
-    </row>
-    <row r="182" spans="1:3" ht="12.5">
-      <c r="A182" s="5"/>
-      <c r="C182" s="5"/>
-    </row>
-    <row r="183" spans="1:3" ht="12.5">
-      <c r="A183" s="5"/>
-      <c r="C183" s="5"/>
-    </row>
-    <row r="184" spans="1:3" ht="12.5">
-      <c r="A184" s="5"/>
-      <c r="C184" s="5"/>
-    </row>
-    <row r="185" spans="1:3" ht="12.5">
-      <c r="A185" s="5"/>
-      <c r="C185" s="5"/>
-    </row>
-    <row r="186" spans="1:3" ht="12.5">
-      <c r="A186" s="5"/>
-      <c r="C186" s="5"/>
-    </row>
-    <row r="187" spans="1:3" ht="12.5">
-      <c r="A187" s="5"/>
-      <c r="C187" s="5"/>
-    </row>
-    <row r="188" spans="1:3" ht="12.5">
-      <c r="A188" s="5"/>
-      <c r="C188" s="5"/>
-    </row>
-    <row r="189" spans="1:3" ht="12.5">
-      <c r="A189" s="5"/>
-      <c r="C189" s="5"/>
-    </row>
-    <row r="190" spans="1:3" ht="12.5">
-      <c r="A190" s="5"/>
-      <c r="C190" s="5"/>
-    </row>
-    <row r="191" spans="1:3" ht="12.5">
-      <c r="A191" s="5"/>
-      <c r="C191" s="5"/>
-    </row>
-    <row r="192" spans="1:3" ht="12.5">
-      <c r="A192" s="5"/>
-      <c r="C192" s="5"/>
-    </row>
-    <row r="193" spans="1:3" ht="12.5">
-      <c r="A193" s="5"/>
-      <c r="C193" s="5"/>
-    </row>
-    <row r="194" spans="1:3" ht="12.5">
-      <c r="A194" s="5"/>
-      <c r="C194" s="5"/>
-    </row>
-    <row r="195" spans="1:3" ht="12.5">
+    <row r="163" spans="1:3" ht="30">
+      <c r="A163" s="31" t="s">
+        <v>319</v>
+      </c>
+      <c r="B163" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C163" s="28" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="30">
+      <c r="A164" s="31" t="s">
+        <v>320</v>
+      </c>
+      <c r="B164" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C164" s="28" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="15">
+      <c r="A165" s="30" t="s">
+        <v>317</v>
+      </c>
+      <c r="B165" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C165" s="28" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="28.5">
+      <c r="A166" s="29" t="s">
+        <v>269</v>
+      </c>
+      <c r="B166" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C166" s="28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="28.5">
+      <c r="A167" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="B167" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C167" s="28" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" ht="15">
+      <c r="A168" s="30" t="s">
+        <v>318</v>
+      </c>
+      <c r="B168" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C168" s="28" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="30">
+      <c r="A169" s="30" t="s">
+        <v>328</v>
+      </c>
+      <c r="B169" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="C169" s="32" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="30">
+      <c r="A170" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="B170" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="C170" s="33" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="14.25">
+      <c r="A171" s="29" t="s">
+        <v>274</v>
+      </c>
+      <c r="B171" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C171" s="28" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="15">
+      <c r="A172" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="B172" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C172" s="28" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="28.5">
+      <c r="A173" s="29" t="s">
+        <v>277</v>
+      </c>
+      <c r="B173" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C173" s="28" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="28.5">
+      <c r="A174" s="29" t="s">
+        <v>279</v>
+      </c>
+      <c r="B174" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C174" s="28" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="14.25">
+      <c r="A175" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B175" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C175" s="28" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="14.25">
+      <c r="A176" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="B176" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C176" s="28" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="15">
+      <c r="A177" s="31" t="s">
+        <v>322</v>
+      </c>
+      <c r="B177" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C177" s="28" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="14.25">
+      <c r="A178" s="29" t="s">
+        <v>286</v>
+      </c>
+      <c r="B178" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C178" s="28" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="14.25">
+      <c r="A179" s="29" t="s">
+        <v>288</v>
+      </c>
+      <c r="B179" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C179" s="28" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="14.25">
+      <c r="A180" s="29" t="s">
+        <v>290</v>
+      </c>
+      <c r="B180" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C180" s="28" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="14.25">
+      <c r="A181" s="29" t="s">
+        <v>292</v>
+      </c>
+      <c r="B181" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C181" s="28" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="28.5">
+      <c r="A182" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="B182" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C182" s="28" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" ht="15">
+      <c r="A183" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="B183" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C183" s="28" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="28.5">
+      <c r="A184" s="29" t="s">
+        <v>297</v>
+      </c>
+      <c r="B184" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C184" s="28" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="28.5">
+      <c r="A185" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="B185" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C185" s="28" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="28.5">
+      <c r="A186" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="B186" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C186" s="28" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="14.25">
+      <c r="A187" s="29" t="s">
+        <v>303</v>
+      </c>
+      <c r="B187" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C187" s="28" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="28.5">
+      <c r="A188" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="B188" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C188" s="28" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="28.5">
+      <c r="A189" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="B189" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C189" s="28" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="30">
+      <c r="A190" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="B190" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C190" s="28" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="15">
+      <c r="A191" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="B191" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C191" s="28" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" ht="28.5">
+      <c r="A192" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="B192" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C192" s="28" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="28.5">
+      <c r="A193" s="29" t="s">
+        <v>313</v>
+      </c>
+      <c r="B193" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C193" s="28" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" ht="14.25">
+      <c r="A194" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="B194" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C194" s="28" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" ht="12.75">
       <c r="A195" s="5"/>
       <c r="C195" s="5"/>
     </row>
-    <row r="196" spans="1:3" ht="12.5">
+    <row r="196" spans="1:3" ht="12.75">
       <c r="A196" s="5"/>
       <c r="C196" s="5"/>
     </row>
-    <row r="197" spans="1:3" ht="12.5">
+    <row r="197" spans="1:3" ht="12.75">
       <c r="A197" s="5"/>
       <c r="C197" s="5"/>
     </row>
-    <row r="198" spans="1:3" ht="12.5">
+    <row r="198" spans="1:3" ht="12.75">
       <c r="A198" s="5"/>
       <c r="C198" s="5"/>
     </row>
-    <row r="199" spans="1:3" ht="12.5">
+    <row r="199" spans="1:3" ht="12.75">
       <c r="A199" s="5"/>
       <c r="C199" s="5"/>
     </row>
-    <row r="200" spans="1:3" ht="12.5">
+    <row r="200" spans="1:3" ht="12.75">
       <c r="A200" s="5"/>
       <c r="C200" s="5"/>
     </row>
-    <row r="201" spans="1:3" ht="12.5">
+    <row r="201" spans="1:3" ht="12.75">
       <c r="A201" s="5"/>
       <c r="C201" s="5"/>
     </row>
-    <row r="202" spans="1:3" ht="12.5">
+    <row r="202" spans="1:3" ht="12.75">
       <c r="A202" s="5"/>
       <c r="C202" s="5"/>
     </row>
-    <row r="203" spans="1:3" ht="12.5">
+    <row r="203" spans="1:3" ht="12.75">
       <c r="A203" s="5"/>
       <c r="C203" s="5"/>
     </row>
-    <row r="204" spans="1:3" ht="12.5">
+    <row r="204" spans="1:3" ht="12.75">
       <c r="A204" s="5"/>
       <c r="C204" s="5"/>
     </row>
-    <row r="205" spans="1:3" ht="12.5">
+    <row r="205" spans="1:3" ht="12.75">
       <c r="A205" s="5"/>
       <c r="C205" s="5"/>
     </row>
-    <row r="206" spans="1:3" ht="12.5">
+    <row r="206" spans="1:3" ht="12.75">
       <c r="A206" s="5"/>
       <c r="C206" s="5"/>
     </row>
-    <row r="207" spans="1:3" ht="12.5">
+    <row r="207" spans="1:3" ht="12.75">
       <c r="A207" s="5"/>
       <c r="C207" s="5"/>
     </row>
-    <row r="208" spans="1:3" ht="12.5">
+    <row r="208" spans="1:3" ht="12.75">
       <c r="A208" s="5"/>
       <c r="C208" s="5"/>
     </row>
-    <row r="209" spans="1:3" ht="12.5">
+    <row r="209" spans="1:3" ht="12.75">
       <c r="A209" s="5"/>
       <c r="C209" s="5"/>
     </row>
-    <row r="210" spans="1:3" ht="12.5">
+    <row r="210" spans="1:3" ht="12.75">
       <c r="A210" s="5"/>
       <c r="C210" s="5"/>
     </row>
-    <row r="211" spans="1:3" ht="12.5">
+    <row r="211" spans="1:3" ht="12.75">
       <c r="A211" s="5"/>
       <c r="C211" s="5"/>
     </row>
-    <row r="212" spans="1:3" ht="12.5">
+    <row r="212" spans="1:3" ht="12.75">
       <c r="A212" s="5"/>
       <c r="C212" s="5"/>
     </row>
-    <row r="213" spans="1:3" ht="12.5">
+    <row r="213" spans="1:3" ht="12.75">
       <c r="A213" s="5"/>
       <c r="C213" s="5"/>
     </row>
-    <row r="214" spans="1:3" ht="12.5">
+    <row r="214" spans="1:3" ht="12.75">
       <c r="A214" s="5"/>
       <c r="C214" s="5"/>
     </row>
-    <row r="215" spans="1:3" ht="12.5">
+    <row r="215" spans="1:3" ht="12.75">
       <c r="A215" s="5"/>
       <c r="C215" s="5"/>
     </row>
-    <row r="216" spans="1:3" ht="12.5">
+    <row r="216" spans="1:3" ht="12.75">
       <c r="A216" s="5"/>
       <c r="C216" s="5"/>
     </row>
-    <row r="217" spans="1:3" ht="12.5">
+    <row r="217" spans="1:3" ht="12.75">
       <c r="A217" s="5"/>
       <c r="C217" s="5"/>
     </row>
-    <row r="218" spans="1:3" ht="12.5">
+    <row r="218" spans="1:3" ht="12.75">
       <c r="A218" s="5"/>
       <c r="C218" s="5"/>
     </row>
-    <row r="219" spans="1:3" ht="12.5">
+    <row r="219" spans="1:3" ht="12.75">
       <c r="A219" s="5"/>
       <c r="C219" s="5"/>
     </row>
-    <row r="220" spans="1:3" ht="12.5">
+    <row r="220" spans="1:3" ht="12.75">
       <c r="A220" s="5"/>
       <c r="C220" s="5"/>
     </row>
-    <row r="221" spans="1:3" ht="12.5">
+    <row r="221" spans="1:3" ht="12.75">
       <c r="A221" s="5"/>
       <c r="C221" s="5"/>
     </row>
-    <row r="222" spans="1:3" ht="12.5">
+    <row r="222" spans="1:3" ht="12.75">
       <c r="A222" s="5"/>
       <c r="C222" s="5"/>
     </row>
-    <row r="223" spans="1:3" ht="12.5">
+    <row r="223" spans="1:3" ht="12.75">
       <c r="A223" s="5"/>
       <c r="C223" s="5"/>
     </row>
-    <row r="224" spans="1:3" ht="12.5">
+    <row r="224" spans="1:3" ht="12.75">
       <c r="A224" s="5"/>
       <c r="C224" s="5"/>
     </row>
-    <row r="225" spans="1:3" ht="12.5">
+    <row r="225" spans="1:3" ht="12.75">
       <c r="A225" s="5"/>
       <c r="C225" s="5"/>
     </row>
-    <row r="226" spans="1:3" ht="12.5">
+    <row r="226" spans="1:3" ht="12.75">
       <c r="A226" s="5"/>
       <c r="C226" s="5"/>
     </row>
-    <row r="227" spans="1:3" ht="12.5">
+    <row r="227" spans="1:3" ht="12.75">
       <c r="A227" s="5"/>
       <c r="C227" s="5"/>
     </row>
-    <row r="228" spans="1:3" ht="12.5">
+    <row r="228" spans="1:3" ht="12.75">
       <c r="A228" s="5"/>
       <c r="C228" s="5"/>
     </row>
-    <row r="229" spans="1:3" ht="12.5">
+    <row r="229" spans="1:3" ht="12.75">
       <c r="A229" s="5"/>
       <c r="C229" s="5"/>
     </row>
-    <row r="230" spans="1:3" ht="12.5">
+    <row r="230" spans="1:3" ht="12.75">
       <c r="A230" s="5"/>
       <c r="C230" s="5"/>
     </row>
-    <row r="231" spans="1:3" ht="12.5">
+    <row r="231" spans="1:3" ht="12.75">
       <c r="A231" s="5"/>
       <c r="C231" s="5"/>
     </row>
-    <row r="232" spans="1:3" ht="12.5">
+    <row r="232" spans="1:3" ht="12.75">
       <c r="A232" s="5"/>
       <c r="C232" s="5"/>
     </row>
-    <row r="233" spans="1:3" ht="12.5">
+    <row r="233" spans="1:3" ht="12.75">
       <c r="A233" s="5"/>
       <c r="C233" s="5"/>
     </row>
-    <row r="234" spans="1:3" ht="12.5">
+    <row r="234" spans="1:3" ht="12.75">
       <c r="A234" s="5"/>
       <c r="C234" s="5"/>
     </row>
-    <row r="235" spans="1:3" ht="12.5">
+    <row r="235" spans="1:3" ht="12.75">
       <c r="A235" s="5"/>
       <c r="C235" s="5"/>
     </row>
-    <row r="236" spans="1:3" ht="12.5">
+    <row r="236" spans="1:3" ht="12.75">
       <c r="A236" s="5"/>
       <c r="C236" s="5"/>
     </row>
-    <row r="237" spans="1:3" ht="12.5">
+    <row r="237" spans="1:3" ht="12.75">
       <c r="A237" s="5"/>
       <c r="C237" s="5"/>
     </row>
-    <row r="238" spans="1:3" ht="12.5">
+    <row r="238" spans="1:3" ht="12.75">
       <c r="A238" s="5"/>
       <c r="C238" s="5"/>
     </row>
-    <row r="239" spans="1:3" ht="12.5">
+    <row r="239" spans="1:3" ht="12.75">
       <c r="A239" s="5"/>
       <c r="C239" s="5"/>
     </row>
-    <row r="240" spans="1:3" ht="12.5">
+    <row r="240" spans="1:3" ht="12.75">
       <c r="A240" s="5"/>
       <c r="C240" s="5"/>
     </row>
-    <row r="241" spans="1:3" ht="12.5">
+    <row r="241" spans="1:3" ht="12.75">
       <c r="A241" s="5"/>
       <c r="C241" s="5"/>
     </row>
-    <row r="242" spans="1:3" ht="12.5">
+    <row r="242" spans="1:3" ht="12.75">
       <c r="A242" s="5"/>
       <c r="C242" s="5"/>
     </row>
-    <row r="243" spans="1:3" ht="12.5">
+    <row r="243" spans="1:3" ht="12.75">
       <c r="A243" s="5"/>
       <c r="C243" s="5"/>
     </row>
-    <row r="244" spans="1:3" ht="12.5">
+    <row r="244" spans="1:3" ht="12.75">
       <c r="A244" s="5"/>
       <c r="C244" s="5"/>
     </row>
-    <row r="245" spans="1:3" ht="12.5">
+    <row r="245" spans="1:3" ht="12.75">
       <c r="A245" s="5"/>
       <c r="C245" s="5"/>
     </row>
-    <row r="246" spans="1:3" ht="12.5">
+    <row r="246" spans="1:3" ht="12.75">
       <c r="A246" s="5"/>
       <c r="C246" s="5"/>
     </row>
-    <row r="247" spans="1:3" ht="12.5">
+    <row r="247" spans="1:3" ht="12.75">
       <c r="A247" s="5"/>
       <c r="C247" s="5"/>
     </row>
-    <row r="248" spans="1:3" ht="12.5">
+    <row r="248" spans="1:3" ht="12.75">
       <c r="A248" s="5"/>
       <c r="C248" s="5"/>
     </row>
-    <row r="249" spans="1:3" ht="12.5">
+    <row r="249" spans="1:3" ht="12.75">
       <c r="A249" s="5"/>
       <c r="C249" s="5"/>
     </row>
-    <row r="250" spans="1:3" ht="12.5">
+    <row r="250" spans="1:3" ht="12.75">
       <c r="A250" s="5"/>
       <c r="C250" s="5"/>
     </row>
-    <row r="251" spans="1:3" ht="12.5">
+    <row r="251" spans="1:3" ht="12.75">
       <c r="A251" s="5"/>
       <c r="C251" s="5"/>
     </row>
-    <row r="252" spans="1:3" ht="12.5">
+    <row r="252" spans="1:3" ht="12.75">
       <c r="A252" s="5"/>
       <c r="C252" s="5"/>
     </row>
-    <row r="253" spans="1:3" ht="12.5">
+    <row r="253" spans="1:3" ht="12.75">
       <c r="A253" s="5"/>
       <c r="C253" s="5"/>
     </row>
-    <row r="254" spans="1:3" ht="12.5">
+    <row r="254" spans="1:3" ht="12.75">
       <c r="A254" s="5"/>
       <c r="C254" s="5"/>
     </row>
-    <row r="255" spans="1:3" ht="12.5">
+    <row r="255" spans="1:3" ht="12.75">
       <c r="A255" s="5"/>
       <c r="C255" s="5"/>
     </row>
-    <row r="256" spans="1:3" ht="12.5">
+    <row r="256" spans="1:3" ht="12.75">
       <c r="A256" s="5"/>
       <c r="C256" s="5"/>
     </row>
-    <row r="257" spans="1:3" ht="12.5">
+    <row r="257" spans="1:3" ht="12.75">
       <c r="A257" s="5"/>
       <c r="C257" s="5"/>
     </row>
-    <row r="258" spans="1:3" ht="12.5">
+    <row r="258" spans="1:3" ht="12.75">
       <c r="A258" s="5"/>
       <c r="C258" s="5"/>
     </row>
-    <row r="259" spans="1:3" ht="12.5">
+    <row r="259" spans="1:3" ht="12.75">
       <c r="A259" s="5"/>
       <c r="C259" s="5"/>
     </row>
-    <row r="260" spans="1:3" ht="12.5">
+    <row r="260" spans="1:3" ht="12.75">
       <c r="A260" s="5"/>
       <c r="C260" s="5"/>
     </row>
-    <row r="261" spans="1:3" ht="12.5">
+    <row r="261" spans="1:3" ht="12.75">
       <c r="A261" s="5"/>
       <c r="C261" s="5"/>
     </row>
-    <row r="262" spans="1:3" ht="12.5">
+    <row r="262" spans="1:3" ht="12.75">
       <c r="A262" s="5"/>
       <c r="C262" s="5"/>
     </row>
-    <row r="263" spans="1:3" ht="12.5">
+    <row r="263" spans="1:3" ht="12.75">
       <c r="A263" s="5"/>
       <c r="C263" s="5"/>
     </row>
-    <row r="264" spans="1:3" ht="12.5">
+    <row r="264" spans="1:3" ht="12.75">
       <c r="A264" s="5"/>
       <c r="C264" s="5"/>
     </row>
-    <row r="265" spans="1:3" ht="12.5">
+    <row r="265" spans="1:3" ht="12.75">
       <c r="A265" s="5"/>
       <c r="C265" s="5"/>
     </row>
-    <row r="266" spans="1:3" ht="12.5">
+    <row r="266" spans="1:3" ht="12.75">
       <c r="A266" s="5"/>
       <c r="C266" s="5"/>
     </row>
-    <row r="267" spans="1:3" ht="12.5">
+    <row r="267" spans="1:3" ht="12.75">
       <c r="A267" s="5"/>
       <c r="C267" s="5"/>
     </row>
-    <row r="268" spans="1:3" ht="12.5">
+    <row r="268" spans="1:3" ht="12.75">
       <c r="A268" s="5"/>
       <c r="C268" s="5"/>
     </row>
-    <row r="269" spans="1:3" ht="12.5">
+    <row r="269" spans="1:3" ht="12.75">
       <c r="A269" s="5"/>
       <c r="C269" s="5"/>
     </row>
-    <row r="270" spans="1:3" ht="12.5">
+    <row r="270" spans="1:3" ht="12.75">
       <c r="A270" s="5"/>
       <c r="C270" s="5"/>
     </row>
-    <row r="271" spans="1:3" ht="12.5">
+    <row r="271" spans="1:3" ht="12.75">
       <c r="A271" s="5"/>
       <c r="C271" s="5"/>
     </row>
-    <row r="272" spans="1:3" ht="12.5">
+    <row r="272" spans="1:3" ht="12.75">
       <c r="A272" s="5"/>
       <c r="C272" s="5"/>
     </row>
-    <row r="273" spans="1:3" ht="12.5">
+    <row r="273" spans="1:3" ht="12.75">
       <c r="A273" s="5"/>
       <c r="C273" s="5"/>
     </row>
-    <row r="274" spans="1:3" ht="12.5">
+    <row r="274" spans="1:3" ht="12.75">
       <c r="A274" s="5"/>
       <c r="C274" s="5"/>
     </row>
-    <row r="275" spans="1:3" ht="12.5">
+    <row r="275" spans="1:3" ht="12.75">
       <c r="A275" s="5"/>
       <c r="C275" s="5"/>
     </row>
-    <row r="276" spans="1:3" ht="12.5">
+    <row r="276" spans="1:3" ht="12.75">
       <c r="A276" s="5"/>
       <c r="C276" s="5"/>
     </row>
-    <row r="277" spans="1:3" ht="12.5">
+    <row r="277" spans="1:3" ht="12.75">
       <c r="A277" s="5"/>
       <c r="C277" s="5"/>
     </row>
-    <row r="278" spans="1:3" ht="12.5">
+    <row r="278" spans="1:3" ht="12.75">
       <c r="A278" s="5"/>
       <c r="C278" s="5"/>
     </row>
-    <row r="279" spans="1:3" ht="12.5">
+    <row r="279" spans="1:3" ht="12.75">
       <c r="A279" s="5"/>
       <c r="C279" s="5"/>
     </row>
-    <row r="280" spans="1:3" ht="12.5">
+    <row r="280" spans="1:3" ht="12.75">
       <c r="A280" s="5"/>
       <c r="C280" s="5"/>
     </row>
-    <row r="281" spans="1:3" ht="12.5">
+    <row r="281" spans="1:3" ht="12.75">
       <c r="A281" s="5"/>
       <c r="C281" s="5"/>
     </row>
-    <row r="282" spans="1:3" ht="12.5">
+    <row r="282" spans="1:3" ht="12.75">
       <c r="A282" s="5"/>
       <c r="C282" s="5"/>
     </row>
-    <row r="283" spans="1:3" ht="12.5">
+    <row r="283" spans="1:3" ht="12.75">
       <c r="A283" s="5"/>
       <c r="C283" s="5"/>
     </row>
-    <row r="284" spans="1:3" ht="12.5">
+    <row r="284" spans="1:3" ht="12.75">
       <c r="A284" s="5"/>
       <c r="C284" s="5"/>
     </row>
-    <row r="285" spans="1:3" ht="12.5">
+    <row r="285" spans="1:3" ht="12.75">
       <c r="A285" s="5"/>
       <c r="C285" s="5"/>
     </row>
-    <row r="286" spans="1:3" ht="12.5">
+    <row r="286" spans="1:3" ht="12.75">
       <c r="A286" s="5"/>
       <c r="C286" s="5"/>
     </row>
-    <row r="287" spans="1:3" ht="12.5">
+    <row r="287" spans="1:3" ht="12.75">
       <c r="A287" s="5"/>
       <c r="C287" s="5"/>
     </row>
-    <row r="288" spans="1:3" ht="12.5">
+    <row r="288" spans="1:3" ht="12.75">
       <c r="A288" s="5"/>
       <c r="C288" s="5"/>
     </row>
-    <row r="289" spans="1:3" ht="12.5">
+    <row r="289" spans="1:3" ht="12.75">
       <c r="A289" s="5"/>
       <c r="C289" s="5"/>
     </row>
-    <row r="290" spans="1:3" ht="12.5">
+    <row r="290" spans="1:3" ht="12.75">
       <c r="A290" s="5"/>
       <c r="C290" s="5"/>
     </row>
-    <row r="291" spans="1:3" ht="12.5">
+    <row r="291" spans="1:3" ht="12.75">
       <c r="A291" s="5"/>
       <c r="C291" s="5"/>
     </row>
-    <row r="292" spans="1:3" ht="12.5">
+    <row r="292" spans="1:3" ht="12.75">
       <c r="A292" s="5"/>
       <c r="C292" s="5"/>
     </row>
-    <row r="293" spans="1:3" ht="12.5">
+    <row r="293" spans="1:3" ht="12.75">
       <c r="A293" s="5"/>
       <c r="C293" s="5"/>
     </row>
-    <row r="294" spans="1:3" ht="12.5">
+    <row r="294" spans="1:3" ht="12.75">
       <c r="A294" s="5"/>
       <c r="C294" s="5"/>
     </row>
-    <row r="295" spans="1:3" ht="12.5">
+    <row r="295" spans="1:3" ht="12.75">
       <c r="A295" s="5"/>
       <c r="C295" s="5"/>
     </row>
-    <row r="296" spans="1:3" ht="12.5">
+    <row r="296" spans="1:3" ht="12.75">
       <c r="A296" s="5"/>
       <c r="C296" s="5"/>
     </row>
-    <row r="297" spans="1:3" ht="12.5">
+    <row r="297" spans="1:3" ht="12.75">
       <c r="A297" s="5"/>
       <c r="C297" s="5"/>
     </row>
-    <row r="298" spans="1:3" ht="12.5">
+    <row r="298" spans="1:3" ht="12.75">
       <c r="A298" s="5"/>
       <c r="C298" s="5"/>
     </row>
-    <row r="299" spans="1:3" ht="12.5">
+    <row r="299" spans="1:3" ht="12.75">
       <c r="A299" s="5"/>
       <c r="C299" s="5"/>
     </row>
-    <row r="300" spans="1:3" ht="12.5">
+    <row r="300" spans="1:3" ht="12.75">
       <c r="A300" s="5"/>
       <c r="C300" s="5"/>
     </row>
-    <row r="301" spans="1:3" ht="12.5">
+    <row r="301" spans="1:3" ht="12.75">
       <c r="A301" s="5"/>
       <c r="C301" s="5"/>
     </row>
-    <row r="302" spans="1:3" ht="12.5">
+    <row r="302" spans="1:3" ht="12.75">
       <c r="A302" s="5"/>
       <c r="C302" s="5"/>
     </row>
-    <row r="303" spans="1:3" ht="12.5">
+    <row r="303" spans="1:3" ht="12.75">
       <c r="A303" s="5"/>
       <c r="C303" s="5"/>
     </row>
-    <row r="304" spans="1:3" ht="12.5">
+    <row r="304" spans="1:3" ht="12.75">
       <c r="A304" s="5"/>
       <c r="C304" s="5"/>
     </row>
-    <row r="305" spans="1:3" ht="12.5">
+    <row r="305" spans="1:3" ht="12.75">
       <c r="A305" s="5"/>
       <c r="C305" s="5"/>
     </row>
-    <row r="306" spans="1:3" ht="12.5">
+    <row r="306" spans="1:3" ht="12.75">
       <c r="A306" s="5"/>
       <c r="C306" s="5"/>
     </row>
-    <row r="307" spans="1:3" ht="12.5">
+    <row r="307" spans="1:3" ht="12.75">
       <c r="A307" s="5"/>
       <c r="C307" s="5"/>
     </row>
-    <row r="308" spans="1:3" ht="12.5">
+    <row r="308" spans="1:3" ht="12.75">
       <c r="A308" s="5"/>
       <c r="C308" s="5"/>
     </row>
-    <row r="309" spans="1:3" ht="12.5">
+    <row r="309" spans="1:3" ht="12.75">
       <c r="A309" s="5"/>
       <c r="C309" s="5"/>
     </row>
-    <row r="310" spans="1:3" ht="12.5">
+    <row r="310" spans="1:3" ht="12.75">
       <c r="A310" s="5"/>
       <c r="C310" s="5"/>
     </row>
-    <row r="311" spans="1:3" ht="12.5">
+    <row r="311" spans="1:3" ht="12.75">
       <c r="A311" s="5"/>
       <c r="C311" s="5"/>
     </row>
-    <row r="312" spans="1:3" ht="12.5">
+    <row r="312" spans="1:3" ht="12.75">
       <c r="A312" s="5"/>
       <c r="C312" s="5"/>
     </row>
-    <row r="313" spans="1:3" ht="12.5">
+    <row r="313" spans="1:3" ht="12.75">
       <c r="A313" s="5"/>
       <c r="C313" s="5"/>
     </row>
-    <row r="314" spans="1:3" ht="12.5">
+    <row r="314" spans="1:3" ht="12.75">
       <c r="A314" s="5"/>
       <c r="C314" s="5"/>
     </row>
-    <row r="315" spans="1:3" ht="12.5">
+    <row r="315" spans="1:3" ht="12.75">
       <c r="A315" s="5"/>
       <c r="C315" s="5"/>
     </row>
-    <row r="316" spans="1:3" ht="12.5">
+    <row r="316" spans="1:3" ht="12.75">
       <c r="A316" s="5"/>
       <c r="C316" s="5"/>
     </row>
-    <row r="317" spans="1:3" ht="12.5">
+    <row r="317" spans="1:3" ht="12.75">
       <c r="A317" s="5"/>
       <c r="C317" s="5"/>
     </row>
-    <row r="318" spans="1:3" ht="12.5">
+    <row r="318" spans="1:3" ht="12.75">
       <c r="A318" s="5"/>
       <c r="C318" s="5"/>
     </row>
-    <row r="319" spans="1:3" ht="12.5">
+    <row r="319" spans="1:3" ht="12.75">
       <c r="A319" s="5"/>
       <c r="C319" s="5"/>
     </row>
-    <row r="320" spans="1:3" ht="12.5">
+    <row r="320" spans="1:3" ht="12.75">
       <c r="A320" s="5"/>
       <c r="C320" s="5"/>
     </row>
-    <row r="321" spans="1:3" ht="12.5">
+    <row r="321" spans="1:3" ht="12.75">
       <c r="A321" s="5"/>
       <c r="C321" s="5"/>
     </row>
-    <row r="322" spans="1:3" ht="12.5">
+    <row r="322" spans="1:3" ht="12.75">
       <c r="A322" s="5"/>
       <c r="C322" s="5"/>
     </row>
-    <row r="323" spans="1:3" ht="12.5">
+    <row r="323" spans="1:3" ht="12.75">
       <c r="A323" s="5"/>
       <c r="C323" s="5"/>
     </row>
-    <row r="324" spans="1:3" ht="12.5">
+    <row r="324" spans="1:3" ht="12.75">
       <c r="A324" s="5"/>
       <c r="C324" s="5"/>
     </row>
-    <row r="325" spans="1:3" ht="12.5">
+    <row r="325" spans="1:3" ht="12.75">
       <c r="A325" s="5"/>
       <c r="C325" s="5"/>
     </row>
-    <row r="326" spans="1:3" ht="12.5">
+    <row r="326" spans="1:3" ht="12.75">
       <c r="A326" s="5"/>
       <c r="C326" s="5"/>
     </row>
-    <row r="327" spans="1:3" ht="12.5">
+    <row r="327" spans="1:3" ht="12.75">
       <c r="A327" s="5"/>
       <c r="C327" s="5"/>
     </row>
-    <row r="328" spans="1:3" ht="12.5">
+    <row r="328" spans="1:3" ht="12.75">
       <c r="A328" s="5"/>
       <c r="C328" s="5"/>
     </row>
-    <row r="329" spans="1:3" ht="12.5">
+    <row r="329" spans="1:3" ht="12.75">
       <c r="A329" s="5"/>
       <c r="C329" s="5"/>
     </row>
-    <row r="330" spans="1:3" ht="12.5">
+    <row r="330" spans="1:3" ht="12.75">
       <c r="A330" s="5"/>
       <c r="C330" s="5"/>
     </row>
-    <row r="331" spans="1:3" ht="12.5">
+    <row r="331" spans="1:3" ht="12.75">
       <c r="A331" s="5"/>
       <c r="C331" s="5"/>
     </row>
-    <row r="332" spans="1:3" ht="12.5">
+    <row r="332" spans="1:3" ht="12.75">
       <c r="A332" s="5"/>
       <c r="C332" s="5"/>
     </row>
-    <row r="333" spans="1:3" ht="12.5">
+    <row r="333" spans="1:3" ht="12.75">
       <c r="A333" s="5"/>
       <c r="C333" s="5"/>
     </row>
-    <row r="334" spans="1:3" ht="12.5">
+    <row r="334" spans="1:3" ht="12.75">
       <c r="A334" s="5"/>
       <c r="C334" s="5"/>
     </row>
-    <row r="335" spans="1:3" ht="12.5">
+    <row r="335" spans="1:3" ht="12.75">
       <c r="A335" s="5"/>
       <c r="C335" s="5"/>
     </row>
-    <row r="336" spans="1:3" ht="12.5">
+    <row r="336" spans="1:3" ht="12.75">
       <c r="A336" s="5"/>
       <c r="C336" s="5"/>
     </row>
-    <row r="337" spans="1:3" ht="12.5">
+    <row r="337" spans="1:3" ht="12.75">
       <c r="A337" s="5"/>
       <c r="C337" s="5"/>
     </row>
-    <row r="338" spans="1:3" ht="12.5">
+    <row r="338" spans="1:3" ht="12.75">
       <c r="A338" s="5"/>
       <c r="C338" s="5"/>
     </row>
-    <row r="339" spans="1:3" ht="12.5">
+    <row r="339" spans="1:3" ht="12.75">
       <c r="A339" s="5"/>
       <c r="C339" s="5"/>
     </row>
-    <row r="340" spans="1:3" ht="12.5">
+    <row r="340" spans="1:3" ht="12.75">
       <c r="A340" s="5"/>
       <c r="C340" s="5"/>
     </row>
-    <row r="341" spans="1:3" ht="12.5">
+    <row r="341" spans="1:3" ht="12.75">
       <c r="A341" s="5"/>
       <c r="C341" s="5"/>
     </row>
-    <row r="342" spans="1:3" ht="12.5">
+    <row r="342" spans="1:3" ht="12.75">
       <c r="A342" s="5"/>
       <c r="C342" s="5"/>
     </row>
-    <row r="343" spans="1:3" ht="12.5">
+    <row r="343" spans="1:3" ht="12.75">
       <c r="A343" s="5"/>
       <c r="C343" s="5"/>
     </row>
-    <row r="344" spans="1:3" ht="12.5">
+    <row r="344" spans="1:3" ht="12.75">
       <c r="A344" s="5"/>
       <c r="C344" s="5"/>
     </row>
-    <row r="345" spans="1:3" ht="12.5">
+    <row r="345" spans="1:3" ht="12.75">
       <c r="A345" s="5"/>
       <c r="C345" s="5"/>
     </row>
-    <row r="346" spans="1:3" ht="12.5">
+    <row r="346" spans="1:3" ht="12.75">
       <c r="A346" s="5"/>
       <c r="C346" s="5"/>
     </row>
-    <row r="347" spans="1:3" ht="12.5">
+    <row r="347" spans="1:3" ht="12.75">
       <c r="A347" s="5"/>
       <c r="C347" s="5"/>
     </row>
-    <row r="348" spans="1:3" ht="12.5">
+    <row r="348" spans="1:3" ht="12.75">
       <c r="A348" s="5"/>
       <c r="C348" s="5"/>
     </row>
-    <row r="349" spans="1:3" ht="12.5">
+    <row r="349" spans="1:3" ht="12.75">
       <c r="A349" s="5"/>
       <c r="C349" s="5"/>
     </row>
-    <row r="350" spans="1:3" ht="12.5">
+    <row r="350" spans="1:3" ht="12.75">
       <c r="A350" s="5"/>
       <c r="C350" s="5"/>
     </row>
-    <row r="351" spans="1:3" ht="12.5">
+    <row r="351" spans="1:3" ht="12.75">
       <c r="A351" s="5"/>
       <c r="C351" s="5"/>
     </row>
-    <row r="352" spans="1:3" ht="12.5">
+    <row r="352" spans="1:3" ht="12.75">
       <c r="A352" s="5"/>
       <c r="C352" s="5"/>
     </row>
-    <row r="353" spans="1:3" ht="12.5">
+    <row r="353" spans="1:3" ht="12.75">
       <c r="A353" s="5"/>
       <c r="C353" s="5"/>
     </row>
-    <row r="354" spans="1:3" ht="12.5">
+    <row r="354" spans="1:3" ht="12.75">
       <c r="A354" s="5"/>
       <c r="C354" s="5"/>
     </row>
-    <row r="355" spans="1:3" ht="12.5">
+    <row r="355" spans="1:3" ht="12.75">
       <c r="A355" s="5"/>
       <c r="C355" s="5"/>
     </row>
-    <row r="356" spans="1:3" ht="12.5">
+    <row r="356" spans="1:3" ht="12.75">
       <c r="A356" s="5"/>
       <c r="C356" s="5"/>
     </row>
-    <row r="357" spans="1:3" ht="12.5">
+    <row r="357" spans="1:3" ht="12.75">
       <c r="A357" s="5"/>
       <c r="C357" s="5"/>
     </row>
-    <row r="358" spans="1:3" ht="12.5">
+    <row r="358" spans="1:3" ht="12.75">
       <c r="A358" s="5"/>
       <c r="C358" s="5"/>
     </row>
-    <row r="359" spans="1:3" ht="12.5">
+    <row r="359" spans="1:3" ht="12.75">
       <c r="A359" s="5"/>
       <c r="C359" s="5"/>
     </row>
-    <row r="360" spans="1:3" ht="12.5">
+    <row r="360" spans="1:3" ht="12.75">
       <c r="A360" s="5"/>
       <c r="C360" s="5"/>
     </row>
-    <row r="361" spans="1:3" ht="12.5">
+    <row r="361" spans="1:3" ht="12.75">
       <c r="A361" s="5"/>
       <c r="C361" s="5"/>
     </row>
-    <row r="362" spans="1:3" ht="12.5">
+    <row r="362" spans="1:3" ht="12.75">
       <c r="A362" s="5"/>
       <c r="C362" s="5"/>
     </row>
-    <row r="363" spans="1:3" ht="12.5">
+    <row r="363" spans="1:3" ht="12.75">
       <c r="A363" s="5"/>
       <c r="C363" s="5"/>
     </row>
-    <row r="364" spans="1:3" ht="12.5">
+    <row r="364" spans="1:3" ht="12.75">
       <c r="A364" s="5"/>
       <c r="C364" s="5"/>
     </row>
-    <row r="365" spans="1:3" ht="12.5">
+    <row r="365" spans="1:3" ht="12.75">
       <c r="A365" s="5"/>
       <c r="C365" s="5"/>
     </row>
-    <row r="366" spans="1:3" ht="12.5">
+    <row r="366" spans="1:3" ht="12.75">
       <c r="A366" s="5"/>
       <c r="C366" s="5"/>
     </row>
-    <row r="367" spans="1:3" ht="12.5">
+    <row r="367" spans="1:3" ht="12.75">
       <c r="A367" s="5"/>
       <c r="C367" s="5"/>
     </row>
-    <row r="368" spans="1:3" ht="12.5">
+    <row r="368" spans="1:3" ht="12.75">
       <c r="A368" s="5"/>
       <c r="C368" s="5"/>
     </row>
-    <row r="369" spans="1:3" ht="12.5">
+    <row r="369" spans="1:3" ht="12.75">
       <c r="A369" s="5"/>
       <c r="C369" s="5"/>
     </row>
-    <row r="370" spans="1:3" ht="12.5">
+    <row r="370" spans="1:3" ht="12.75">
       <c r="A370" s="5"/>
       <c r="C370" s="5"/>
     </row>
-    <row r="371" spans="1:3" ht="12.5">
+    <row r="371" spans="1:3" ht="12.75">
       <c r="A371" s="5"/>
       <c r="C371" s="5"/>
     </row>
-    <row r="372" spans="1:3" ht="12.5">
+    <row r="372" spans="1:3" ht="12.75">
       <c r="A372" s="5"/>
       <c r="C372" s="5"/>
     </row>
-    <row r="373" spans="1:3" ht="12.5">
+    <row r="373" spans="1:3" ht="12.75">
       <c r="A373" s="5"/>
       <c r="C373" s="5"/>
     </row>
-    <row r="374" spans="1:3" ht="12.5">
+    <row r="374" spans="1:3" ht="12.75">
       <c r="A374" s="5"/>
       <c r="C374" s="5"/>
     </row>
-    <row r="375" spans="1:3" ht="12.5">
+    <row r="375" spans="1:3" ht="12.75">
       <c r="A375" s="5"/>
       <c r="C375" s="5"/>
     </row>
-    <row r="376" spans="1:3" ht="12.5">
+    <row r="376" spans="1:3" ht="12.75">
       <c r="A376" s="5"/>
       <c r="C376" s="5"/>
     </row>
-    <row r="377" spans="1:3" ht="12.5">
+    <row r="377" spans="1:3" ht="12.75">
       <c r="A377" s="5"/>
       <c r="C377" s="5"/>
     </row>
-    <row r="378" spans="1:3" ht="12.5">
+    <row r="378" spans="1:3" ht="12.75">
       <c r="A378" s="5"/>
       <c r="C378" s="5"/>
     </row>
-    <row r="379" spans="1:3" ht="12.5">
+    <row r="379" spans="1:3" ht="12.75">
       <c r="A379" s="5"/>
       <c r="C379" s="5"/>
     </row>
-    <row r="380" spans="1:3" ht="12.5">
+    <row r="380" spans="1:3" ht="12.75">
       <c r="A380" s="5"/>
       <c r="C380" s="5"/>
     </row>
-    <row r="381" spans="1:3" ht="12.5">
+    <row r="381" spans="1:3" ht="12.75">
       <c r="A381" s="5"/>
       <c r="C381" s="5"/>
     </row>
-    <row r="382" spans="1:3" ht="12.5">
+    <row r="382" spans="1:3" ht="12.75">
       <c r="A382" s="5"/>
       <c r="C382" s="5"/>
     </row>
-    <row r="383" spans="1:3" ht="12.5">
+    <row r="383" spans="1:3" ht="12.75">
       <c r="A383" s="5"/>
       <c r="C383" s="5"/>
     </row>
-    <row r="384" spans="1:3" ht="12.5">
+    <row r="384" spans="1:3" ht="12.75">
       <c r="A384" s="5"/>
       <c r="C384" s="5"/>
     </row>
-    <row r="385" spans="1:3" ht="12.5">
+    <row r="385" spans="1:3" ht="12.75">
       <c r="A385" s="5"/>
       <c r="C385" s="5"/>
     </row>
-    <row r="386" spans="1:3" ht="12.5">
+    <row r="386" spans="1:3" ht="12.75">
       <c r="A386" s="5"/>
       <c r="C386" s="5"/>
     </row>
-    <row r="387" spans="1:3" ht="12.5">
+    <row r="387" spans="1:3" ht="12.75">
       <c r="A387" s="5"/>
       <c r="C387" s="5"/>
     </row>
-    <row r="388" spans="1:3" ht="12.5">
+    <row r="388" spans="1:3" ht="12.75">
       <c r="A388" s="5"/>
       <c r="C388" s="5"/>
     </row>
-    <row r="389" spans="1:3" ht="12.5">
+    <row r="389" spans="1:3" ht="12.75">
       <c r="A389" s="5"/>
       <c r="C389" s="5"/>
     </row>
-    <row r="390" spans="1:3" ht="12.5">
+    <row r="390" spans="1:3" ht="12.75">
       <c r="A390" s="5"/>
       <c r="C390" s="5"/>
     </row>
-    <row r="391" spans="1:3" ht="12.5">
+    <row r="391" spans="1:3" ht="12.75">
       <c r="A391" s="5"/>
       <c r="C391" s="5"/>
     </row>
-    <row r="392" spans="1:3" ht="12.5">
+    <row r="392" spans="1:3" ht="12.75">
       <c r="A392" s="5"/>
       <c r="C392" s="5"/>
     </row>
-    <row r="393" spans="1:3" ht="12.5">
+    <row r="393" spans="1:3" ht="12.75">
       <c r="A393" s="5"/>
       <c r="C393" s="5"/>
     </row>
-    <row r="394" spans="1:3" ht="12.5">
+    <row r="394" spans="1:3" ht="12.75">
       <c r="A394" s="5"/>
       <c r="C394" s="5"/>
     </row>
-    <row r="395" spans="1:3" ht="12.5">
+    <row r="395" spans="1:3" ht="12.75">
       <c r="A395" s="5"/>
       <c r="C395" s="5"/>
     </row>
-    <row r="396" spans="1:3" ht="12.5">
+    <row r="396" spans="1:3" ht="12.75">
       <c r="A396" s="5"/>
       <c r="C396" s="5"/>
     </row>
-    <row r="397" spans="1:3" ht="12.5">
+    <row r="397" spans="1:3" ht="12.75">
       <c r="A397" s="5"/>
       <c r="C397" s="5"/>
     </row>
-    <row r="398" spans="1:3" ht="12.5">
+    <row r="398" spans="1:3" ht="12.75">
       <c r="A398" s="5"/>
       <c r="C398" s="5"/>
     </row>
-    <row r="399" spans="1:3" ht="12.5">
+    <row r="399" spans="1:3" ht="12.75">
       <c r="A399" s="5"/>
       <c r="C399" s="5"/>
     </row>
-    <row r="400" spans="1:3" ht="12.5">
+    <row r="400" spans="1:3" ht="12.75">
       <c r="A400" s="5"/>
       <c r="C400" s="5"/>
     </row>
-    <row r="401" spans="1:3" ht="12.5">
+    <row r="401" spans="1:3" ht="12.75">
       <c r="A401" s="5"/>
       <c r="C401" s="5"/>
     </row>
-    <row r="402" spans="1:3" ht="12.5">
+    <row r="402" spans="1:3" ht="12.75">
       <c r="A402" s="5"/>
       <c r="C402" s="5"/>
     </row>
-    <row r="403" spans="1:3" ht="12.5">
+    <row r="403" spans="1:3" ht="12.75">
       <c r="A403" s="5"/>
       <c r="C403" s="5"/>
     </row>
-    <row r="404" spans="1:3" ht="12.5">
+    <row r="404" spans="1:3" ht="12.75">
       <c r="A404" s="5"/>
       <c r="C404" s="5"/>
     </row>
-    <row r="405" spans="1:3" ht="12.5">
+    <row r="405" spans="1:3" ht="12.75">
       <c r="A405" s="5"/>
       <c r="C405" s="5"/>
     </row>
-    <row r="406" spans="1:3" ht="12.5">
+    <row r="406" spans="1:3" ht="12.75">
       <c r="A406" s="5"/>
       <c r="C406" s="5"/>
     </row>
-    <row r="407" spans="1:3" ht="12.5">
+    <row r="407" spans="1:3" ht="12.75">
       <c r="A407" s="5"/>
       <c r="C407" s="5"/>
     </row>
-    <row r="408" spans="1:3" ht="12.5">
+    <row r="408" spans="1:3" ht="12.75">
       <c r="A408" s="5"/>
       <c r="C408" s="5"/>
     </row>
-    <row r="409" spans="1:3" ht="12.5">
+    <row r="409" spans="1:3" ht="12.75">
       <c r="A409" s="5"/>
       <c r="C409" s="5"/>
     </row>
-    <row r="410" spans="1:3" ht="12.5">
+    <row r="410" spans="1:3" ht="12.75">
       <c r="A410" s="5"/>
       <c r="C410" s="5"/>
     </row>
-    <row r="411" spans="1:3" ht="12.5">
+    <row r="411" spans="1:3" ht="12.75">
       <c r="A411" s="5"/>
       <c r="C411" s="5"/>
     </row>
-    <row r="412" spans="1:3" ht="12.5">
+    <row r="412" spans="1:3" ht="12.75">
       <c r="A412" s="5"/>
       <c r="C412" s="5"/>
     </row>
-    <row r="413" spans="1:3" ht="12.5">
+    <row r="413" spans="1:3" ht="12.75">
       <c r="A413" s="5"/>
       <c r="C413" s="5"/>
     </row>
-    <row r="414" spans="1:3" ht="12.5">
+    <row r="414" spans="1:3" ht="12.75">
       <c r="A414" s="5"/>
       <c r="C414" s="5"/>
     </row>
-    <row r="415" spans="1:3" ht="12.5">
+    <row r="415" spans="1:3" ht="12.75">
       <c r="A415" s="5"/>
       <c r="C415" s="5"/>
     </row>
-    <row r="416" spans="1:3" ht="12.5">
+    <row r="416" spans="1:3" ht="12.75">
       <c r="A416" s="5"/>
       <c r="C416" s="5"/>
     </row>
-    <row r="417" spans="1:3" ht="12.5">
+    <row r="417" spans="1:3" ht="12.75">
       <c r="A417" s="5"/>
       <c r="C417" s="5"/>
     </row>
-    <row r="418" spans="1:3" ht="12.5">
+    <row r="418" spans="1:3" ht="12.75">
       <c r="A418" s="5"/>
       <c r="C418" s="5"/>
     </row>
-    <row r="419" spans="1:3" ht="12.5">
+    <row r="419" spans="1:3" ht="12.75">
       <c r="A419" s="5"/>
       <c r="C419" s="5"/>
     </row>
-    <row r="420" spans="1:3" ht="12.5">
+    <row r="420" spans="1:3" ht="12.75">
       <c r="A420" s="5"/>
       <c r="C420" s="5"/>
     </row>
-    <row r="421" spans="1:3" ht="12.5">
+    <row r="421" spans="1:3" ht="12.75">
       <c r="A421" s="5"/>
       <c r="C421" s="5"/>
     </row>
-    <row r="422" spans="1:3" ht="12.5">
+    <row r="422" spans="1:3" ht="12.75">
       <c r="A422" s="5"/>
       <c r="C422" s="5"/>
     </row>
-    <row r="423" spans="1:3" ht="12.5">
+    <row r="423" spans="1:3" ht="12.75">
       <c r="A423" s="5"/>
       <c r="C423" s="5"/>
     </row>
-    <row r="424" spans="1:3" ht="12.5">
+    <row r="424" spans="1:3" ht="12.75">
       <c r="A424" s="5"/>
       <c r="C424" s="5"/>
     </row>
-    <row r="425" spans="1:3" ht="12.5">
+    <row r="425" spans="1:3" ht="12.75">
       <c r="A425" s="5"/>
       <c r="C425" s="5"/>
     </row>
-    <row r="426" spans="1:3" ht="12.5">
+    <row r="426" spans="1:3" ht="12.75">
       <c r="A426" s="5"/>
       <c r="C426" s="5"/>
     </row>
-    <row r="427" spans="1:3" ht="12.5">
+    <row r="427" spans="1:3" ht="12.75">
       <c r="A427" s="5"/>
       <c r="C427" s="5"/>
     </row>
-    <row r="428" spans="1:3" ht="12.5">
+    <row r="428" spans="1:3" ht="12.75">
       <c r="A428" s="5"/>
       <c r="C428" s="5"/>
     </row>
-    <row r="429" spans="1:3" ht="12.5">
+    <row r="429" spans="1:3" ht="12.75">
       <c r="A429" s="5"/>
       <c r="C429" s="5"/>
     </row>
-    <row r="430" spans="1:3" ht="12.5">
+    <row r="430" spans="1:3" ht="12.75">
       <c r="A430" s="5"/>
       <c r="C430" s="5"/>
     </row>
-    <row r="431" spans="1:3" ht="12.5">
+    <row r="431" spans="1:3" ht="12.75">
       <c r="A431" s="5"/>
       <c r="C431" s="5"/>
     </row>
-    <row r="432" spans="1:3" ht="12.5">
+    <row r="432" spans="1:3" ht="12.75">
       <c r="A432" s="5"/>
       <c r="C432" s="5"/>
     </row>
-    <row r="433" spans="1:3" ht="12.5">
+    <row r="433" spans="1:3" ht="12.75">
       <c r="A433" s="5"/>
       <c r="C433" s="5"/>
     </row>
-    <row r="434" spans="1:3" ht="12.5">
+    <row r="434" spans="1:3" ht="12.75">
       <c r="A434" s="5"/>
       <c r="C434" s="5"/>
     </row>
-    <row r="435" spans="1:3" ht="12.5">
+    <row r="435" spans="1:3" ht="12.75">
       <c r="A435" s="5"/>
       <c r="C435" s="5"/>
     </row>
-    <row r="436" spans="1:3" ht="12.5">
+    <row r="436" spans="1:3" ht="12.75">
       <c r="A436" s="5"/>
       <c r="C436" s="5"/>
     </row>
-    <row r="437" spans="1:3" ht="12.5">
+    <row r="437" spans="1:3" ht="12.75">
       <c r="A437" s="5"/>
       <c r="C437" s="5"/>
     </row>
-    <row r="438" spans="1:3" ht="12.5">
+    <row r="438" spans="1:3" ht="12.75">
       <c r="A438" s="5"/>
       <c r="C438" s="5"/>
     </row>
-    <row r="439" spans="1:3" ht="12.5">
+    <row r="439" spans="1:3" ht="12.75">
       <c r="A439" s="5"/>
       <c r="C439" s="5"/>
     </row>
-    <row r="440" spans="1:3" ht="12.5">
+    <row r="440" spans="1:3" ht="12.75">
       <c r="A440" s="5"/>
       <c r="C440" s="5"/>
     </row>
-    <row r="441" spans="1:3" ht="12.5">
+    <row r="441" spans="1:3" ht="12.75">
       <c r="A441" s="5"/>
       <c r="C441" s="5"/>
     </row>
-    <row r="442" spans="1:3" ht="12.5">
+    <row r="442" spans="1:3" ht="12.75">
       <c r="A442" s="5"/>
       <c r="C442" s="5"/>
     </row>
-    <row r="443" spans="1:3" ht="12.5">
+    <row r="443" spans="1:3" ht="12.75">
       <c r="A443" s="5"/>
       <c r="C443" s="5"/>
     </row>
-    <row r="444" spans="1:3" ht="12.5">
+    <row r="444" spans="1:3" ht="12.75">
       <c r="A444" s="5"/>
       <c r="C444" s="5"/>
     </row>
-    <row r="445" spans="1:3" ht="12.5">
+    <row r="445" spans="1:3" ht="12.75">
       <c r="A445" s="5"/>
       <c r="C445" s="5"/>
     </row>
-    <row r="446" spans="1:3" ht="12.5">
+    <row r="446" spans="1:3" ht="12.75">
       <c r="A446" s="5"/>
       <c r="C446" s="5"/>
     </row>
-    <row r="447" spans="1:3" ht="12.5">
+    <row r="447" spans="1:3" ht="12.75">
       <c r="A447" s="5"/>
       <c r="C447" s="5"/>
     </row>
-    <row r="448" spans="1:3" ht="12.5">
+    <row r="448" spans="1:3" ht="12.75">
       <c r="A448" s="5"/>
       <c r="C448" s="5"/>
     </row>
-    <row r="449" spans="1:3" ht="12.5">
+    <row r="449" spans="1:3" ht="12.75">
       <c r="A449" s="5"/>
       <c r="C449" s="5"/>
     </row>
-    <row r="450" spans="1:3" ht="12.5">
+    <row r="450" spans="1:3" ht="12.75">
       <c r="A450" s="5"/>
       <c r="C450" s="5"/>
     </row>
-    <row r="451" spans="1:3" ht="12.5">
+    <row r="451" spans="1:3" ht="12.75">
       <c r="A451" s="5"/>
       <c r="C451" s="5"/>
     </row>
-    <row r="452" spans="1:3" ht="12.5">
+    <row r="452" spans="1:3" ht="12.75">
       <c r="A452" s="5"/>
       <c r="C452" s="5"/>
     </row>
-    <row r="453" spans="1:3" ht="12.5">
+    <row r="453" spans="1:3" ht="12.75">
       <c r="A453" s="5"/>
       <c r="C453" s="5"/>
     </row>
-    <row r="454" spans="1:3" ht="12.5">
+    <row r="454" spans="1:3" ht="12.75">
       <c r="A454" s="5"/>
       <c r="C454" s="5"/>
     </row>
-    <row r="455" spans="1:3" ht="12.5">
+    <row r="455" spans="1:3" ht="12.75">
       <c r="A455" s="5"/>
       <c r="C455" s="5"/>
     </row>
-    <row r="456" spans="1:3" ht="12.5">
+    <row r="456" spans="1:3" ht="12.75">
       <c r="A456" s="5"/>
       <c r="C456" s="5"/>
     </row>
-    <row r="457" spans="1:3" ht="12.5">
+    <row r="457" spans="1:3" ht="12.75">
       <c r="A457" s="5"/>
       <c r="C457" s="5"/>
     </row>
-    <row r="458" spans="1:3" ht="12.5">
+    <row r="458" spans="1:3" ht="12.75">
       <c r="A458" s="5"/>
       <c r="C458" s="5"/>
     </row>
-    <row r="459" spans="1:3" ht="12.5">
+    <row r="459" spans="1:3" ht="12.75">
       <c r="A459" s="5"/>
       <c r="C459" s="5"/>
     </row>
-    <row r="460" spans="1:3" ht="12.5">
+    <row r="460" spans="1:3" ht="12.75">
       <c r="A460" s="5"/>
       <c r="C460" s="5"/>
     </row>
-    <row r="461" spans="1:3" ht="12.5">
+    <row r="461" spans="1:3" ht="12.75">
       <c r="A461" s="5"/>
       <c r="C461" s="5"/>
     </row>
-    <row r="462" spans="1:3" ht="12.5">
+    <row r="462" spans="1:3" ht="12.75">
       <c r="A462" s="5"/>
       <c r="C462" s="5"/>
     </row>
-    <row r="463" spans="1:3" ht="12.5">
+    <row r="463" spans="1:3" ht="12.75">
       <c r="A463" s="5"/>
       <c r="C463" s="5"/>
     </row>
-    <row r="464" spans="1:3" ht="12.5">
+    <row r="464" spans="1:3" ht="12.75">
       <c r="A464" s="5"/>
       <c r="C464" s="5"/>
     </row>
-    <row r="465" spans="1:3" ht="12.5">
+    <row r="465" spans="1:3" ht="12.75">
       <c r="A465" s="5"/>
       <c r="C465" s="5"/>
     </row>
-    <row r="466" spans="1:3" ht="12.5">
+    <row r="466" spans="1:3" ht="12.75">
       <c r="A466" s="5"/>
       <c r="C466" s="5"/>
     </row>
-    <row r="467" spans="1:3" ht="12.5">
+    <row r="467" spans="1:3" ht="12.75">
       <c r="A467" s="5"/>
       <c r="C467" s="5"/>
     </row>
-    <row r="468" spans="1:3" ht="12.5">
+    <row r="468" spans="1:3" ht="12.75">
       <c r="A468" s="5"/>
       <c r="C468" s="5"/>
     </row>
-    <row r="469" spans="1:3" ht="12.5">
+    <row r="469" spans="1:3" ht="12.75">
       <c r="A469" s="5"/>
       <c r="C469" s="5"/>
     </row>
-    <row r="470" spans="1:3" ht="12.5">
+    <row r="470" spans="1:3" ht="12.75">
       <c r="A470" s="5"/>
       <c r="C470" s="5"/>
     </row>
-    <row r="471" spans="1:3" ht="12.5">
+    <row r="471" spans="1:3" ht="12.75">
       <c r="A471" s="5"/>
       <c r="C471" s="5"/>
     </row>
-    <row r="472" spans="1:3" ht="12.5">
+    <row r="472" spans="1:3" ht="12.75">
       <c r="A472" s="5"/>
       <c r="C472" s="5"/>
     </row>
-    <row r="473" spans="1:3" ht="12.5">
+    <row r="473" spans="1:3" ht="12.75">
       <c r="A473" s="5"/>
       <c r="C473" s="5"/>
     </row>
-    <row r="474" spans="1:3" ht="12.5">
+    <row r="474" spans="1:3" ht="12.75">
       <c r="A474" s="5"/>
       <c r="C474" s="5"/>
     </row>
-    <row r="475" spans="1:3" ht="12.5">
+    <row r="475" spans="1:3" ht="12.75">
       <c r="A475" s="5"/>
       <c r="C475" s="5"/>
     </row>
-    <row r="476" spans="1:3" ht="12.5">
+    <row r="476" spans="1:3" ht="12.75">
       <c r="A476" s="5"/>
       <c r="C476" s="5"/>
     </row>
-    <row r="477" spans="1:3" ht="12.5">
+    <row r="477" spans="1:3" ht="12.75">
       <c r="A477" s="5"/>
       <c r="C477" s="5"/>
     </row>
-    <row r="478" spans="1:3" ht="12.5">
+    <row r="478" spans="1:3" ht="12.75">
       <c r="A478" s="5"/>
       <c r="C478" s="5"/>
     </row>
-    <row r="479" spans="1:3" ht="12.5">
+    <row r="479" spans="1:3" ht="12.75">
       <c r="A479" s="5"/>
       <c r="C479" s="5"/>
     </row>
-    <row r="480" spans="1:3" ht="12.5">
+    <row r="480" spans="1:3" ht="12.75">
       <c r="A480" s="5"/>
       <c r="C480" s="5"/>
     </row>
-    <row r="481" spans="1:3" ht="12.5">
+    <row r="481" spans="1:3" ht="12.75">
       <c r="A481" s="5"/>
       <c r="C481" s="5"/>
     </row>
-    <row r="482" spans="1:3" ht="12.5">
+    <row r="482" spans="1:3" ht="12.75">
       <c r="A482" s="5"/>
       <c r="C482" s="5"/>
     </row>
-    <row r="483" spans="1:3" ht="12.5">
+    <row r="483" spans="1:3" ht="12.75">
       <c r="A483" s="5"/>
       <c r="C483" s="5"/>
     </row>
-    <row r="484" spans="1:3" ht="12.5">
+    <row r="484" spans="1:3" ht="12.75">
       <c r="A484" s="5"/>
       <c r="C484" s="5"/>
     </row>
-    <row r="485" spans="1:3" ht="12.5">
+    <row r="485" spans="1:3" ht="12.75">
       <c r="A485" s="5"/>
       <c r="C485" s="5"/>
     </row>
-    <row r="486" spans="1:3" ht="12.5">
+    <row r="486" spans="1:3" ht="12.75">
       <c r="A486" s="5"/>
       <c r="C486" s="5"/>
     </row>
-    <row r="487" spans="1:3" ht="12.5">
+    <row r="487" spans="1:3" ht="12.75">
       <c r="A487" s="5"/>
       <c r="C487" s="5"/>
     </row>
-    <row r="488" spans="1:3" ht="12.5">
+    <row r="488" spans="1:3" ht="12.75">
       <c r="A488" s="5"/>
       <c r="C488" s="5"/>
     </row>
-    <row r="489" spans="1:3" ht="12.5">
+    <row r="489" spans="1:3" ht="12.75">
       <c r="A489" s="5"/>
       <c r="C489" s="5"/>
     </row>
-    <row r="490" spans="1:3" ht="12.5">
+    <row r="490" spans="1:3" ht="12.75">
       <c r="A490" s="5"/>
       <c r="C490" s="5"/>
     </row>
-    <row r="491" spans="1:3" ht="12.5">
+    <row r="491" spans="1:3" ht="12.75">
       <c r="A491" s="5"/>
       <c r="C491" s="5"/>
     </row>
-    <row r="492" spans="1:3" ht="12.5">
+    <row r="492" spans="1:3" ht="12.75">
       <c r="A492" s="5"/>
       <c r="C492" s="5"/>
     </row>
-    <row r="493" spans="1:3" ht="12.5">
+    <row r="493" spans="1:3" ht="12.75">
       <c r="A493" s="5"/>
       <c r="C493" s="5"/>
     </row>
-    <row r="494" spans="1:3" ht="12.5">
+    <row r="494" spans="1:3" ht="12.75">
       <c r="A494" s="5"/>
       <c r="C494" s="5"/>
     </row>
-    <row r="495" spans="1:3" ht="12.5">
+    <row r="495" spans="1:3" ht="12.75">
       <c r="A495" s="5"/>
       <c r="C495" s="5"/>
     </row>
-    <row r="496" spans="1:3" ht="12.5">
+    <row r="496" spans="1:3" ht="12.75">
       <c r="A496" s="5"/>
       <c r="C496" s="5"/>
     </row>
-    <row r="497" spans="1:3" ht="12.5">
+    <row r="497" spans="1:3" ht="12.75">
       <c r="A497" s="5"/>
       <c r="C497" s="5"/>
     </row>
-    <row r="498" spans="1:3" ht="12.5">
+    <row r="498" spans="1:3" ht="12.75">
       <c r="A498" s="5"/>
       <c r="C498" s="5"/>
     </row>
-    <row r="499" spans="1:3" ht="12.5">
+    <row r="499" spans="1:3" ht="12.75">
       <c r="A499" s="5"/>
       <c r="C499" s="5"/>
     </row>
-    <row r="500" spans="1:3" ht="12.5">
+    <row r="500" spans="1:3" ht="12.75">
       <c r="A500" s="5"/>
       <c r="C500" s="5"/>
     </row>
-    <row r="501" spans="1:3" ht="12.5">
+    <row r="501" spans="1:3" ht="12.75">
       <c r="A501" s="5"/>
       <c r="C501" s="5"/>
     </row>
-    <row r="502" spans="1:3" ht="12.5">
+    <row r="502" spans="1:3" ht="12.75">
       <c r="A502" s="5"/>
       <c r="C502" s="5"/>
     </row>
-    <row r="503" spans="1:3" ht="12.5">
+    <row r="503" spans="1:3" ht="12.75">
       <c r="A503" s="5"/>
       <c r="C503" s="5"/>
     </row>
-    <row r="504" spans="1:3" ht="12.5">
+    <row r="504" spans="1:3" ht="12.75">
       <c r="A504" s="5"/>
       <c r="C504" s="5"/>
     </row>
-    <row r="505" spans="1:3" ht="12.5">
+    <row r="505" spans="1:3" ht="12.75">
       <c r="A505" s="5"/>
       <c r="C505" s="5"/>
     </row>
-    <row r="506" spans="1:3" ht="12.5">
+    <row r="506" spans="1:3" ht="12.75">
       <c r="A506" s="5"/>
       <c r="C506" s="5"/>
     </row>
-    <row r="507" spans="1:3" ht="12.5">
+    <row r="507" spans="1:3" ht="12.75">
       <c r="A507" s="5"/>
       <c r="C507" s="5"/>
     </row>
-    <row r="508" spans="1:3" ht="12.5">
+    <row r="508" spans="1:3" ht="12.75">
       <c r="A508" s="5"/>
       <c r="C508" s="5"/>
     </row>
-    <row r="509" spans="1:3" ht="12.5">
+    <row r="509" spans="1:3" ht="12.75">
       <c r="A509" s="5"/>
       <c r="C509" s="5"/>
     </row>
-    <row r="510" spans="1:3" ht="12.5">
+    <row r="510" spans="1:3" ht="12.75">
       <c r="A510" s="5"/>
       <c r="C510" s="5"/>
     </row>
-    <row r="511" spans="1:3" ht="12.5">
+    <row r="511" spans="1:3" ht="12.75">
       <c r="A511" s="5"/>
       <c r="C511" s="5"/>
     </row>
-    <row r="512" spans="1:3" ht="12.5">
+    <row r="512" spans="1:3" ht="12.75">
       <c r="A512" s="5"/>
       <c r="C512" s="5"/>
     </row>
-    <row r="513" spans="1:3" ht="12.5">
+    <row r="513" spans="1:3" ht="12.75">
       <c r="A513" s="5"/>
       <c r="C513" s="5"/>
     </row>
-    <row r="514" spans="1:3" ht="12.5">
+    <row r="514" spans="1:3" ht="12.75">
       <c r="A514" s="5"/>
       <c r="C514" s="5"/>
     </row>
-    <row r="515" spans="1:3" ht="12.5">
+    <row r="515" spans="1:3" ht="12.75">
       <c r="A515" s="5"/>
       <c r="C515" s="5"/>
     </row>
-    <row r="516" spans="1:3" ht="12.5">
+    <row r="516" spans="1:3" ht="12.75">
       <c r="A516" s="5"/>
       <c r="C516" s="5"/>
     </row>
-    <row r="517" spans="1:3" ht="12.5">
+    <row r="517" spans="1:3" ht="12.75">
       <c r="A517" s="5"/>
       <c r="C517" s="5"/>
     </row>
-    <row r="518" spans="1:3" ht="12.5">
+    <row r="518" spans="1:3" ht="12.75">
       <c r="A518" s="5"/>
       <c r="C518" s="5"/>
     </row>
-    <row r="519" spans="1:3" ht="12.5">
+    <row r="519" spans="1:3" ht="12.75">
       <c r="A519" s="5"/>
       <c r="C519" s="5"/>
     </row>
-    <row r="520" spans="1:3" ht="12.5">
+    <row r="520" spans="1:3" ht="12.75">
       <c r="A520" s="5"/>
       <c r="C520" s="5"/>
     </row>
-    <row r="521" spans="1:3" ht="12.5">
+    <row r="521" spans="1:3" ht="12.75">
       <c r="A521" s="5"/>
       <c r="C521" s="5"/>
     </row>
-    <row r="522" spans="1:3" ht="12.5">
+    <row r="522" spans="1:3" ht="12.75">
       <c r="A522" s="5"/>
       <c r="C522" s="5"/>
     </row>
-    <row r="523" spans="1:3" ht="12.5">
+    <row r="523" spans="1:3" ht="12.75">
       <c r="A523" s="5"/>
       <c r="C523" s="5"/>
     </row>
-    <row r="524" spans="1:3" ht="12.5">
+    <row r="524" spans="1:3" ht="12.75">
       <c r="A524" s="5"/>
       <c r="C524" s="5"/>
     </row>
-    <row r="525" spans="1:3" ht="12.5">
+    <row r="525" spans="1:3" ht="12.75">
       <c r="A525" s="5"/>
       <c r="C525" s="5"/>
     </row>
-    <row r="526" spans="1:3" ht="12.5">
+    <row r="526" spans="1:3" ht="12.75">
       <c r="A526" s="5"/>
       <c r="C526" s="5"/>
     </row>
-    <row r="527" spans="1:3" ht="12.5">
+    <row r="527" spans="1:3" ht="12.75">
       <c r="A527" s="5"/>
       <c r="C527" s="5"/>
     </row>
-    <row r="528" spans="1:3" ht="12.5">
+    <row r="528" spans="1:3" ht="12.75">
       <c r="A528" s="5"/>
       <c r="C528" s="5"/>
     </row>
-    <row r="529" spans="1:3" ht="12.5">
+    <row r="529" spans="1:3" ht="12.75">
       <c r="A529" s="5"/>
       <c r="C529" s="5"/>
     </row>
-    <row r="530" spans="1:3" ht="12.5">
+    <row r="530" spans="1:3" ht="12.75">
       <c r="A530" s="5"/>
       <c r="C530" s="5"/>
     </row>
-    <row r="531" spans="1:3" ht="12.5">
+    <row r="531" spans="1:3" ht="12.75">
       <c r="A531" s="5"/>
       <c r="C531" s="5"/>
     </row>
-    <row r="532" spans="1:3" ht="12.5">
+    <row r="532" spans="1:3" ht="12.75">
       <c r="A532" s="5"/>
       <c r="C532" s="5"/>
     </row>
-    <row r="533" spans="1:3" ht="12.5">
+    <row r="533" spans="1:3" ht="12.75">
       <c r="A533" s="5"/>
       <c r="C533" s="5"/>
     </row>
-    <row r="534" spans="1:3" ht="12.5">
+    <row r="534" spans="1:3" ht="12.75">
       <c r="A534" s="5"/>
       <c r="C534" s="5"/>
     </row>
-    <row r="535" spans="1:3" ht="12.5">
+    <row r="535" spans="1:3" ht="12.75">
       <c r="A535" s="5"/>
       <c r="C535" s="5"/>
     </row>
-    <row r="536" spans="1:3" ht="12.5">
+    <row r="536" spans="1:3" ht="12.75">
       <c r="A536" s="5"/>
       <c r="C536" s="5"/>
     </row>
-    <row r="537" spans="1:3" ht="12.5">
+    <row r="537" spans="1:3" ht="12.75">
       <c r="A537" s="5"/>
       <c r="C537" s="5"/>
     </row>
-    <row r="538" spans="1:3" ht="12.5">
+    <row r="538" spans="1:3" ht="12.75">
       <c r="A538" s="5"/>
       <c r="C538" s="5"/>
     </row>
-    <row r="539" spans="1:3" ht="12.5">
+    <row r="539" spans="1:3" ht="12.75">
       <c r="A539" s="5"/>
       <c r="C539" s="5"/>
     </row>
-    <row r="540" spans="1:3" ht="12.5">
+    <row r="540" spans="1:3" ht="12.75">
       <c r="A540" s="5"/>
       <c r="C540" s="5"/>
     </row>
-    <row r="541" spans="1:3" ht="12.5">
+    <row r="541" spans="1:3" ht="12.75">
       <c r="A541" s="5"/>
       <c r="C541" s="5"/>
     </row>
-    <row r="542" spans="1:3" ht="12.5">
+    <row r="542" spans="1:3" ht="12.75">
       <c r="A542" s="5"/>
       <c r="C542" s="5"/>
     </row>
-    <row r="543" spans="1:3" ht="12.5">
+    <row r="543" spans="1:3" ht="12.75">
       <c r="A543" s="5"/>
       <c r="C543" s="5"/>
     </row>
-    <row r="544" spans="1:3" ht="12.5">
+    <row r="544" spans="1:3" ht="12.75">
       <c r="A544" s="5"/>
       <c r="C544" s="5"/>
     </row>
-    <row r="545" spans="1:3" ht="12.5">
+    <row r="545" spans="1:3" ht="12.75">
       <c r="A545" s="5"/>
       <c r="C545" s="5"/>
     </row>
-    <row r="546" spans="1:3" ht="12.5">
+    <row r="546" spans="1:3" ht="12.75">
       <c r="A546" s="5"/>
       <c r="C546" s="5"/>
     </row>
-    <row r="547" spans="1:3" ht="12.5">
+    <row r="547" spans="1:3" ht="12.75">
       <c r="A547" s="5"/>
       <c r="C547" s="5"/>
     </row>
-    <row r="548" spans="1:3" ht="12.5">
+    <row r="548" spans="1:3" ht="12.75">
       <c r="A548" s="5"/>
       <c r="C548" s="5"/>
     </row>
-    <row r="549" spans="1:3" ht="12.5">
+    <row r="549" spans="1:3" ht="12.75">
       <c r="A549" s="5"/>
       <c r="C549" s="5"/>
     </row>
-    <row r="550" spans="1:3" ht="12.5">
+    <row r="550" spans="1:3" ht="12.75">
       <c r="A550" s="5"/>
       <c r="C550" s="5"/>
     </row>
-    <row r="551" spans="1:3" ht="12.5">
+    <row r="551" spans="1:3" ht="12.75">
       <c r="A551" s="5"/>
       <c r="C551" s="5"/>
     </row>
-    <row r="552" spans="1:3" ht="12.5">
+    <row r="552" spans="1:3" ht="12.75">
       <c r="A552" s="5"/>
       <c r="C552" s="5"/>
     </row>
-    <row r="553" spans="1:3" ht="12.5">
+    <row r="553" spans="1:3" ht="12.75">
       <c r="A553" s="5"/>
       <c r="C553" s="5"/>
     </row>
-    <row r="554" spans="1:3" ht="12.5">
+    <row r="554" spans="1:3" ht="12.75">
       <c r="A554" s="5"/>
       <c r="C554" s="5"/>
     </row>
-    <row r="555" spans="1:3" ht="12.5">
+    <row r="555" spans="1:3" ht="12.75">
       <c r="A555" s="5"/>
       <c r="C555" s="5"/>
     </row>
-    <row r="556" spans="1:3" ht="12.5">
+    <row r="556" spans="1:3" ht="12.75">
       <c r="A556" s="5"/>
       <c r="C556" s="5"/>
     </row>
-    <row r="557" spans="1:3" ht="12.5">
+    <row r="557" spans="1:3" ht="12.75">
       <c r="A557" s="5"/>
       <c r="C557" s="5"/>
     </row>
-    <row r="558" spans="1:3" ht="12.5">
+    <row r="558" spans="1:3" ht="12.75">
       <c r="A558" s="5"/>
       <c r="C558" s="5"/>
     </row>
-    <row r="559" spans="1:3" ht="12.5">
+    <row r="559" spans="1:3" ht="12.75">
       <c r="A559" s="5"/>
       <c r="C559" s="5"/>
     </row>
-    <row r="560" spans="1:3" ht="12.5">
+    <row r="560" spans="1:3" ht="12.75">
       <c r="A560" s="5"/>
       <c r="C560" s="5"/>
     </row>
-    <row r="561" spans="1:3" ht="12.5">
+    <row r="561" spans="1:3" ht="12.75">
       <c r="A561" s="5"/>
       <c r="C561" s="5"/>
     </row>
-    <row r="562" spans="1:3" ht="12.5">
+    <row r="562" spans="1:3" ht="12.75">
       <c r="A562" s="5"/>
       <c r="C562" s="5"/>
     </row>
-    <row r="563" spans="1:3" ht="12.5">
+    <row r="563" spans="1:3" ht="12.75">
       <c r="A563" s="5"/>
       <c r="C563" s="5"/>
     </row>
-    <row r="564" spans="1:3" ht="12.5">
+    <row r="564" spans="1:3" ht="12.75">
       <c r="A564" s="5"/>
       <c r="C564" s="5"/>
     </row>
-    <row r="565" spans="1:3" ht="12.5">
+    <row r="565" spans="1:3" ht="12.75">
       <c r="A565" s="5"/>
       <c r="C565" s="5"/>
     </row>
-    <row r="566" spans="1:3" ht="12.5">
+    <row r="566" spans="1:3" ht="12.75">
       <c r="A566" s="5"/>
       <c r="C566" s="5"/>
     </row>
-    <row r="567" spans="1:3" ht="12.5">
+    <row r="567" spans="1:3" ht="12.75">
       <c r="A567" s="5"/>
       <c r="C567" s="5"/>
     </row>
-    <row r="568" spans="1:3" ht="12.5">
+    <row r="568" spans="1:3" ht="12.75">
       <c r="A568" s="5"/>
       <c r="C568" s="5"/>
     </row>
-    <row r="569" spans="1:3" ht="12.5">
+    <row r="569" spans="1:3" ht="12.75">
       <c r="A569" s="5"/>
       <c r="C569" s="5"/>
     </row>
-    <row r="570" spans="1:3" ht="12.5">
+    <row r="570" spans="1:3" ht="12.75">
       <c r="A570" s="5"/>
       <c r="C570" s="5"/>
     </row>
-    <row r="571" spans="1:3" ht="12.5">
+    <row r="571" spans="1:3" ht="12.75">
       <c r="A571" s="5"/>
       <c r="C571" s="5"/>
     </row>
-    <row r="572" spans="1:3" ht="12.5">
+    <row r="572" spans="1:3" ht="12.75">
       <c r="A572" s="5"/>
       <c r="C572" s="5"/>
     </row>
-    <row r="573" spans="1:3" ht="12.5">
+    <row r="573" spans="1:3" ht="12.75">
       <c r="A573" s="5"/>
       <c r="C573" s="5"/>
     </row>
-    <row r="574" spans="1:3" ht="12.5">
+    <row r="574" spans="1:3" ht="12.75">
       <c r="A574" s="5"/>
       <c r="C574" s="5"/>
     </row>
-    <row r="575" spans="1:3" ht="12.5">
+    <row r="575" spans="1:3" ht="12.75">
       <c r="A575" s="5"/>
       <c r="C575" s="5"/>
     </row>
-    <row r="576" spans="1:3" ht="12.5">
+    <row r="576" spans="1:3" ht="12.75">
       <c r="A576" s="5"/>
       <c r="C576" s="5"/>
     </row>
-    <row r="577" spans="1:3" ht="12.5">
+    <row r="577" spans="1:3" ht="12.75">
       <c r="A577" s="5"/>
       <c r="C577" s="5"/>
     </row>
-    <row r="578" spans="1:3" ht="12.5">
+    <row r="578" spans="1:3" ht="12.75">
       <c r="A578" s="5"/>
       <c r="C578" s="5"/>
     </row>
-    <row r="579" spans="1:3" ht="12.5">
+    <row r="579" spans="1:3" ht="12.75">
       <c r="A579" s="5"/>
       <c r="C579" s="5"/>
     </row>
-    <row r="580" spans="1:3" ht="12.5">
+    <row r="580" spans="1:3" ht="12.75">
       <c r="A580" s="5"/>
       <c r="C580" s="5"/>
     </row>
-    <row r="581" spans="1:3" ht="12.5">
+    <row r="581" spans="1:3" ht="12.75">
       <c r="A581" s="5"/>
       <c r="C581" s="5"/>
     </row>
-    <row r="582" spans="1:3" ht="12.5">
+    <row r="582" spans="1:3" ht="12.75">
       <c r="A582" s="5"/>
       <c r="C582" s="5"/>
     </row>
-    <row r="583" spans="1:3" ht="12.5">
+    <row r="583" spans="1:3" ht="12.75">
       <c r="A583" s="5"/>
       <c r="C583" s="5"/>
     </row>
-    <row r="584" spans="1:3" ht="12.5">
+    <row r="584" spans="1:3" ht="12.75">
       <c r="A584" s="5"/>
       <c r="C584" s="5"/>
     </row>
-    <row r="585" spans="1:3" ht="12.5">
+    <row r="585" spans="1:3" ht="12.75">
       <c r="A585" s="5"/>
       <c r="C585" s="5"/>
     </row>
-    <row r="586" spans="1:3" ht="12.5">
+    <row r="586" spans="1:3" ht="12.75">
       <c r="A586" s="5"/>
       <c r="C586" s="5"/>
     </row>
-    <row r="587" spans="1:3" ht="12.5">
+    <row r="587" spans="1:3" ht="12.75">
       <c r="A587" s="5"/>
       <c r="C587" s="5"/>
     </row>
-    <row r="588" spans="1:3" ht="12.5">
+    <row r="588" spans="1:3" ht="12.75">
       <c r="A588" s="5"/>
       <c r="C588" s="5"/>
     </row>
-    <row r="589" spans="1:3" ht="12.5">
+    <row r="589" spans="1:3" ht="12.75">
       <c r="A589" s="5"/>
       <c r="C589" s="5"/>
     </row>
-    <row r="590" spans="1:3" ht="12.5">
+    <row r="590" spans="1:3" ht="12.75">
       <c r="A590" s="5"/>
       <c r="C590" s="5"/>
     </row>
-    <row r="591" spans="1:3" ht="12.5">
+    <row r="591" spans="1:3" ht="12.75">
       <c r="A591" s="5"/>
       <c r="C591" s="5"/>
     </row>
-    <row r="592" spans="1:3" ht="12.5">
+    <row r="592" spans="1:3" ht="12.75">
       <c r="A592" s="5"/>
       <c r="C592" s="5"/>
     </row>
-    <row r="593" spans="1:3" ht="12.5">
+    <row r="593" spans="1:3" ht="12.75">
       <c r="A593" s="5"/>
       <c r="C593" s="5"/>
     </row>
-    <row r="594" spans="1:3" ht="12.5">
+    <row r="594" spans="1:3" ht="12.75">
       <c r="A594" s="5"/>
       <c r="C594" s="5"/>
     </row>
-    <row r="595" spans="1:3" ht="12.5">
+    <row r="595" spans="1:3" ht="12.75">
       <c r="A595" s="5"/>
       <c r="C595" s="5"/>
     </row>
-    <row r="596" spans="1:3" ht="12.5">
+    <row r="596" spans="1:3" ht="12.75">
       <c r="A596" s="5"/>
       <c r="C596" s="5"/>
     </row>
-    <row r="597" spans="1:3" ht="12.5">
+    <row r="597" spans="1:3" ht="12.75">
       <c r="A597" s="5"/>
       <c r="C597" s="5"/>
     </row>
-    <row r="598" spans="1:3" ht="12.5">
+    <row r="598" spans="1:3" ht="12.75">
       <c r="A598" s="5"/>
       <c r="C598" s="5"/>
     </row>
-    <row r="599" spans="1:3" ht="12.5">
+    <row r="599" spans="1:3" ht="12.75">
       <c r="A599" s="5"/>
       <c r="C599" s="5"/>
     </row>
-    <row r="600" spans="1:3" ht="12.5">
+    <row r="600" spans="1:3" ht="12.75">
       <c r="A600" s="5"/>
       <c r="C600" s="5"/>
     </row>
-    <row r="601" spans="1:3" ht="12.5">
+    <row r="601" spans="1:3" ht="12.75">
       <c r="A601" s="5"/>
       <c r="C601" s="5"/>
     </row>
-    <row r="602" spans="1:3" ht="12.5">
+    <row r="602" spans="1:3" ht="12.75">
       <c r="A602" s="5"/>
       <c r="C602" s="5"/>
     </row>
-    <row r="603" spans="1:3" ht="12.5">
+    <row r="603" spans="1:3" ht="12.75">
       <c r="A603" s="5"/>
       <c r="C603" s="5"/>
     </row>
-    <row r="604" spans="1:3" ht="12.5">
+    <row r="604" spans="1:3" ht="12.75">
       <c r="A604" s="5"/>
       <c r="C604" s="5"/>
     </row>
-    <row r="605" spans="1:3" ht="12.5">
+    <row r="605" spans="1:3" ht="12.75">
       <c r="A605" s="5"/>
       <c r="C605" s="5"/>
     </row>
-    <row r="606" spans="1:3" ht="12.5">
+    <row r="606" spans="1:3" ht="12.75">
       <c r="A606" s="5"/>
       <c r="C606" s="5"/>
     </row>
-    <row r="607" spans="1:3" ht="12.5">
+    <row r="607" spans="1:3" ht="12.75">
       <c r="A607" s="5"/>
       <c r="C607" s="5"/>
     </row>
-    <row r="608" spans="1:3" ht="12.5">
+    <row r="608" spans="1:3" ht="12.75">
       <c r="A608" s="5"/>
       <c r="C608" s="5"/>
     </row>
-    <row r="609" spans="1:3" ht="12.5">
+    <row r="609" spans="1:3" ht="12.75">
       <c r="A609" s="5"/>
       <c r="C609" s="5"/>
     </row>
-    <row r="610" spans="1:3" ht="12.5">
+    <row r="610" spans="1:3" ht="12.75">
       <c r="A610" s="5"/>
       <c r="C610" s="5"/>
     </row>
-    <row r="611" spans="1:3" ht="12.5">
+    <row r="611" spans="1:3" ht="12.75">
       <c r="A611" s="5"/>
       <c r="C611" s="5"/>
     </row>
-    <row r="612" spans="1:3" ht="12.5">
+    <row r="612" spans="1:3" ht="12.75">
       <c r="A612" s="5"/>
       <c r="C612" s="5"/>
     </row>
-    <row r="613" spans="1:3" ht="12.5">
+    <row r="613" spans="1:3" ht="12.75">
       <c r="A613" s="5"/>
       <c r="C613" s="5"/>
     </row>
-    <row r="614" spans="1:3" ht="12.5">
+    <row r="614" spans="1:3" ht="12.75">
       <c r="A614" s="5"/>
       <c r="C614" s="5"/>
     </row>
-    <row r="615" spans="1:3" ht="12.5">
+    <row r="615" spans="1:3" ht="12.75">
       <c r="A615" s="5"/>
       <c r="C615" s="5"/>
     </row>
-    <row r="616" spans="1:3" ht="12.5">
+    <row r="616" spans="1:3" ht="12.75">
       <c r="A616" s="5"/>
       <c r="C616" s="5"/>
     </row>
-    <row r="617" spans="1:3" ht="12.5">
+    <row r="617" spans="1:3" ht="12.75">
       <c r="A617" s="5"/>
       <c r="C617" s="5"/>
     </row>
-    <row r="618" spans="1:3" ht="12.5">
+    <row r="618" spans="1:3" ht="12.75">
       <c r="A618" s="5"/>
       <c r="C618" s="5"/>
     </row>
-    <row r="619" spans="1:3" ht="12.5">
+    <row r="619" spans="1:3" ht="12.75">
       <c r="A619" s="5"/>
       <c r="C619" s="5"/>
     </row>
-    <row r="620" spans="1:3" ht="12.5">
+    <row r="620" spans="1:3" ht="12.75">
       <c r="A620" s="5"/>
       <c r="C620" s="5"/>
     </row>
-    <row r="621" spans="1:3" ht="12.5">
+    <row r="621" spans="1:3" ht="12.75">
       <c r="A621" s="5"/>
       <c r="C621" s="5"/>
     </row>
-    <row r="622" spans="1:3" ht="12.5">
+    <row r="622" spans="1:3" ht="12.75">
       <c r="A622" s="5"/>
       <c r="C622" s="5"/>
     </row>
-    <row r="623" spans="1:3" ht="12.5">
+    <row r="623" spans="1:3" ht="12.75">
       <c r="A623" s="5"/>
       <c r="C623" s="5"/>
     </row>
-    <row r="624" spans="1:3" ht="12.5">
+    <row r="624" spans="1:3" ht="12.75">
       <c r="A624" s="5"/>
       <c r="C624" s="5"/>
     </row>
-    <row r="625" spans="1:3" ht="12.5">
+    <row r="625" spans="1:3" ht="12.75">
       <c r="A625" s="5"/>
       <c r="C625" s="5"/>
     </row>
-    <row r="626" spans="1:3" ht="12.5">
+    <row r="626" spans="1:3" ht="12.75">
       <c r="A626" s="5"/>
       <c r="C626" s="5"/>
     </row>
-    <row r="627" spans="1:3" ht="12.5">
+    <row r="627" spans="1:3" ht="12.75">
       <c r="A627" s="5"/>
       <c r="C627" s="5"/>
     </row>
-    <row r="628" spans="1:3" ht="12.5">
+    <row r="628" spans="1:3" ht="12.75">
       <c r="A628" s="5"/>
       <c r="C628" s="5"/>
     </row>
-    <row r="629" spans="1:3" ht="12.5">
+    <row r="629" spans="1:3" ht="12.75">
       <c r="A629" s="5"/>
       <c r="C629" s="5"/>
     </row>
-    <row r="630" spans="1:3" ht="12.5">
+    <row r="630" spans="1:3" ht="12.75">
       <c r="A630" s="5"/>
       <c r="C630" s="5"/>
     </row>
-    <row r="631" spans="1:3" ht="12.5">
+    <row r="631" spans="1:3" ht="12.75">
       <c r="A631" s="5"/>
       <c r="C631" s="5"/>
     </row>
-    <row r="632" spans="1:3" ht="12.5">
+    <row r="632" spans="1:3" ht="12.75">
       <c r="A632" s="5"/>
       <c r="C632" s="5"/>
     </row>
-    <row r="633" spans="1:3" ht="12.5">
+    <row r="633" spans="1:3" ht="12.75">
       <c r="A633" s="5"/>
       <c r="C633" s="5"/>
     </row>
-    <row r="634" spans="1:3" ht="12.5">
+    <row r="634" spans="1:3" ht="12.75">
       <c r="A634" s="5"/>
       <c r="C634" s="5"/>
     </row>
-    <row r="635" spans="1:3" ht="12.5">
+    <row r="635" spans="1:3" ht="12.75">
       <c r="A635" s="5"/>
       <c r="C635" s="5"/>
     </row>
-    <row r="636" spans="1:3" ht="12.5">
+    <row r="636" spans="1:3" ht="12.75">
       <c r="A636" s="5"/>
       <c r="C636" s="5"/>
     </row>
-    <row r="637" spans="1:3" ht="12.5">
+    <row r="637" spans="1:3" ht="12.75">
       <c r="A637" s="5"/>
       <c r="C637" s="5"/>
     </row>
-    <row r="638" spans="1:3" ht="12.5">
+    <row r="638" spans="1:3" ht="12.75">
       <c r="A638" s="5"/>
       <c r="C638" s="5"/>
     </row>
-    <row r="639" spans="1:3" ht="12.5">
+    <row r="639" spans="1:3" ht="12.75">
       <c r="A639" s="5"/>
       <c r="C639" s="5"/>
     </row>
-    <row r="640" spans="1:3" ht="12.5">
+    <row r="640" spans="1:3" ht="12.75">
       <c r="A640" s="5"/>
       <c r="C640" s="5"/>
     </row>
-    <row r="641" spans="1:3" ht="12.5">
+    <row r="641" spans="1:3" ht="12.75">
       <c r="A641" s="5"/>
       <c r="C641" s="5"/>
     </row>
-    <row r="642" spans="1:3" ht="12.5">
+    <row r="642" spans="1:3" ht="12.75">
       <c r="A642" s="5"/>
       <c r="C642" s="5"/>
     </row>
-    <row r="643" spans="1:3" ht="12.5">
+    <row r="643" spans="1:3" ht="12.75">
       <c r="A643" s="5"/>
       <c r="C643" s="5"/>
     </row>
-    <row r="644" spans="1:3" ht="12.5">
+    <row r="644" spans="1:3" ht="12.75">
       <c r="A644" s="5"/>
       <c r="C644" s="5"/>
     </row>
-    <row r="645" spans="1:3" ht="12.5">
+    <row r="645" spans="1:3" ht="12.75">
       <c r="A645" s="5"/>
       <c r="C645" s="5"/>
     </row>
-    <row r="646" spans="1:3" ht="12.5">
+    <row r="646" spans="1:3" ht="12.75">
       <c r="A646" s="5"/>
       <c r="C646" s="5"/>
     </row>
-    <row r="647" spans="1:3" ht="12.5">
+    <row r="647" spans="1:3" ht="12.75">
       <c r="A647" s="5"/>
       <c r="C647" s="5"/>
     </row>
-    <row r="648" spans="1:3" ht="12.5">
+    <row r="648" spans="1:3" ht="12.75">
       <c r="A648" s="5"/>
       <c r="C648" s="5"/>
     </row>
-    <row r="649" spans="1:3" ht="12.5">
+    <row r="649" spans="1:3" ht="12.75">
       <c r="A649" s="5"/>
       <c r="C649" s="5"/>
     </row>
-    <row r="650" spans="1:3" ht="12.5">
+    <row r="650" spans="1:3" ht="12.75">
       <c r="A650" s="5"/>
       <c r="C650" s="5"/>
     </row>
-    <row r="651" spans="1:3" ht="12.5">
+    <row r="651" spans="1:3" ht="12.75">
       <c r="A651" s="5"/>
       <c r="C651" s="5"/>
     </row>
-    <row r="652" spans="1:3" ht="12.5">
+    <row r="652" spans="1:3" ht="12.75">
       <c r="A652" s="5"/>
       <c r="C652" s="5"/>
     </row>
-    <row r="653" spans="1:3" ht="12.5">
+    <row r="653" spans="1:3" ht="12.75">
       <c r="A653" s="5"/>
       <c r="C653" s="5"/>
     </row>
-    <row r="654" spans="1:3" ht="12.5">
+    <row r="654" spans="1:3" ht="12.75">
       <c r="A654" s="5"/>
       <c r="C654" s="5"/>
     </row>
-    <row r="655" spans="1:3" ht="12.5">
+    <row r="655" spans="1:3" ht="12.75">
       <c r="A655" s="5"/>
       <c r="C655" s="5"/>
     </row>
-    <row r="656" spans="1:3" ht="12.5">
+    <row r="656" spans="1:3" ht="12.75">
       <c r="A656" s="5"/>
       <c r="C656" s="5"/>
     </row>
-    <row r="657" spans="1:3" ht="12.5">
+    <row r="657" spans="1:3" ht="12.75">
       <c r="A657" s="5"/>
       <c r="C657" s="5"/>
     </row>
-    <row r="658" spans="1:3" ht="12.5">
+    <row r="658" spans="1:3" ht="12.75">
       <c r="A658" s="5"/>
       <c r="C658" s="5"/>
     </row>
-    <row r="659" spans="1:3" ht="12.5">
+    <row r="659" spans="1:3" ht="12.75">
       <c r="A659" s="5"/>
       <c r="C659" s="5"/>
     </row>
-    <row r="660" spans="1:3" ht="12.5">
+    <row r="660" spans="1:3" ht="12.75">
       <c r="A660" s="5"/>
       <c r="C660" s="5"/>
     </row>
-    <row r="661" spans="1:3" ht="12.5">
+    <row r="661" spans="1:3" ht="12.75">
       <c r="A661" s="5"/>
       <c r="C661" s="5"/>
     </row>
-    <row r="662" spans="1:3" ht="12.5">
+    <row r="662" spans="1:3" ht="12.75">
       <c r="A662" s="5"/>
       <c r="C662" s="5"/>
     </row>
-    <row r="663" spans="1:3" ht="12.5">
+    <row r="663" spans="1:3" ht="12.75">
       <c r="A663" s="5"/>
       <c r="C663" s="5"/>
     </row>
-    <row r="664" spans="1:3" ht="12.5">
+    <row r="664" spans="1:3" ht="12.75">
       <c r="A664" s="5"/>
       <c r="C664" s="5"/>
     </row>
-    <row r="665" spans="1:3" ht="12.5">
+    <row r="665" spans="1:3" ht="12.75">
       <c r="A665" s="5"/>
       <c r="C665" s="5"/>
     </row>
-    <row r="666" spans="1:3" ht="12.5">
+    <row r="666" spans="1:3" ht="12.75">
       <c r="A666" s="5"/>
       <c r="C666" s="5"/>
     </row>
-    <row r="667" spans="1:3" ht="12.5">
+    <row r="667" spans="1:3" ht="12.75">
       <c r="A667" s="5"/>
       <c r="C667" s="5"/>
     </row>
-    <row r="668" spans="1:3" ht="12.5">
+    <row r="668" spans="1:3" ht="12.75">
       <c r="A668" s="5"/>
       <c r="C668" s="5"/>
     </row>
-    <row r="669" spans="1:3" ht="12.5">
+    <row r="669" spans="1:3" ht="12.75">
       <c r="A669" s="5"/>
       <c r="C669" s="5"/>
     </row>
-    <row r="670" spans="1:3" ht="12.5">
+    <row r="670" spans="1:3" ht="12.75">
       <c r="A670" s="5"/>
       <c r="C670" s="5"/>
     </row>
-    <row r="671" spans="1:3" ht="12.5">
+    <row r="671" spans="1:3" ht="12.75">
       <c r="A671" s="5"/>
       <c r="C671" s="5"/>
     </row>
-    <row r="672" spans="1:3" ht="12.5">
+    <row r="672" spans="1:3" ht="12.75">
       <c r="A672" s="5"/>
       <c r="C672" s="5"/>
     </row>
-    <row r="673" spans="1:3" ht="12.5">
+    <row r="673" spans="1:3" ht="12.75">
       <c r="A673" s="5"/>
       <c r="C673" s="5"/>
     </row>
-    <row r="674" spans="1:3" ht="12.5">
+    <row r="674" spans="1:3" ht="12.75">
       <c r="A674" s="5"/>
       <c r="C674" s="5"/>
     </row>
-    <row r="675" spans="1:3" ht="12.5">
+    <row r="675" spans="1:3" ht="12.75">
       <c r="A675" s="5"/>
       <c r="C675" s="5"/>
     </row>
-    <row r="676" spans="1:3" ht="12.5">
+    <row r="676" spans="1:3" ht="12.75">
       <c r="A676" s="5"/>
       <c r="C676" s="5"/>
     </row>
-    <row r="677" spans="1:3" ht="12.5">
+    <row r="677" spans="1:3" ht="12.75">
       <c r="A677" s="5"/>
       <c r="C677" s="5"/>
     </row>
-    <row r="678" spans="1:3" ht="12.5">
+    <row r="678" spans="1:3" ht="12.75">
       <c r="A678" s="5"/>
       <c r="C678" s="5"/>
     </row>
-    <row r="679" spans="1:3" ht="12.5">
+    <row r="679" spans="1:3" ht="12.75">
       <c r="A679" s="5"/>
       <c r="C679" s="5"/>
     </row>
-    <row r="680" spans="1:3" ht="12.5">
+    <row r="680" spans="1:3" ht="12.75">
       <c r="A680" s="5"/>
       <c r="C680" s="5"/>
     </row>
-    <row r="681" spans="1:3" ht="12.5">
+    <row r="681" spans="1:3" ht="12.75">
       <c r="A681" s="5"/>
       <c r="C681" s="5"/>
     </row>
-    <row r="682" spans="1:3" ht="12.5">
+    <row r="682" spans="1:3" ht="12.75">
       <c r="A682" s="5"/>
       <c r="C682" s="5"/>
     </row>
-    <row r="683" spans="1:3" ht="12.5">
+    <row r="683" spans="1:3" ht="12.75">
       <c r="A683" s="5"/>
       <c r="C683" s="5"/>
     </row>
-    <row r="684" spans="1:3" ht="12.5">
+    <row r="684" spans="1:3" ht="12.75">
       <c r="A684" s="5"/>
       <c r="C684" s="5"/>
     </row>
-    <row r="685" spans="1:3" ht="12.5">
+    <row r="685" spans="1:3" ht="12.75">
       <c r="A685" s="5"/>
       <c r="C685" s="5"/>
     </row>
-    <row r="686" spans="1:3" ht="12.5">
+    <row r="686" spans="1:3" ht="12.75">
       <c r="A686" s="5"/>
       <c r="C686" s="5"/>
     </row>
-    <row r="687" spans="1:3" ht="12.5">
+    <row r="687" spans="1:3" ht="12.75">
       <c r="A687" s="5"/>
       <c r="C687" s="5"/>
     </row>
-    <row r="688" spans="1:3" ht="12.5">
+    <row r="688" spans="1:3" ht="12.75">
       <c r="A688" s="5"/>
       <c r="C688" s="5"/>
     </row>
-    <row r="689" spans="1:3" ht="12.5">
+    <row r="689" spans="1:3" ht="12.75">
       <c r="A689" s="5"/>
       <c r="C689" s="5"/>
     </row>
-    <row r="690" spans="1:3" ht="12.5">
+    <row r="690" spans="1:3" ht="12.75">
       <c r="A690" s="5"/>
       <c r="C690" s="5"/>
     </row>
-    <row r="691" spans="1:3" ht="12.5">
+    <row r="691" spans="1:3" ht="12.75">
       <c r="A691" s="5"/>
       <c r="C691" s="5"/>
     </row>
-    <row r="692" spans="1:3" ht="12.5">
+    <row r="692" spans="1:3" ht="12.75">
       <c r="A692" s="5"/>
       <c r="C692" s="5"/>
     </row>
-    <row r="693" spans="1:3" ht="12.5">
+    <row r="693" spans="1:3" ht="12.75">
       <c r="A693" s="5"/>
       <c r="C693" s="5"/>
     </row>
-    <row r="694" spans="1:3" ht="12.5">
+    <row r="694" spans="1:3" ht="12.75">
       <c r="A694" s="5"/>
       <c r="C694" s="5"/>
     </row>
-    <row r="695" spans="1:3" ht="12.5">
+    <row r="695" spans="1:3" ht="12.75">
       <c r="A695" s="5"/>
       <c r="C695" s="5"/>
     </row>
-    <row r="696" spans="1:3" ht="12.5">
+    <row r="696" spans="1:3" ht="12.75">
       <c r="A696" s="5"/>
       <c r="C696" s="5"/>
     </row>
-    <row r="697" spans="1:3" ht="12.5">
+    <row r="697" spans="1:3" ht="12.75">
       <c r="A697" s="5"/>
       <c r="C697" s="5"/>
     </row>
-    <row r="698" spans="1:3" ht="12.5">
+    <row r="698" spans="1:3" ht="12.75">
       <c r="A698" s="5"/>
       <c r="C698" s="5"/>
     </row>
-    <row r="699" spans="1:3" ht="12.5">
+    <row r="699" spans="1:3" ht="12.75">
       <c r="A699" s="5"/>
       <c r="C699" s="5"/>
     </row>
-    <row r="700" spans="1:3" ht="12.5">
+    <row r="700" spans="1:3" ht="12.75">
       <c r="A700" s="5"/>
       <c r="C700" s="5"/>
     </row>
-    <row r="701" spans="1:3" ht="12.5">
+    <row r="701" spans="1:3" ht="12.75">
       <c r="A701" s="5"/>
       <c r="C701" s="5"/>
     </row>
-    <row r="702" spans="1:3" ht="12.5">
+    <row r="702" spans="1:3" ht="12.75">
       <c r="A702" s="5"/>
       <c r="C702" s="5"/>
     </row>
-    <row r="703" spans="1:3" ht="12.5">
+    <row r="703" spans="1:3" ht="12.75">
       <c r="A703" s="5"/>
       <c r="C703" s="5"/>
     </row>
-    <row r="704" spans="1:3" ht="12.5">
+    <row r="704" spans="1:3" ht="12.75">
       <c r="A704" s="5"/>
       <c r="C704" s="5"/>
     </row>
-    <row r="705" spans="1:3" ht="12.5">
+    <row r="705" spans="1:3" ht="12.75">
       <c r="A705" s="5"/>
       <c r="C705" s="5"/>
     </row>
-    <row r="706" spans="1:3" ht="12.5">
+    <row r="706" spans="1:3" ht="12.75">
       <c r="A706" s="5"/>
       <c r="C706" s="5"/>
     </row>
-    <row r="707" spans="1:3" ht="12.5">
+    <row r="707" spans="1:3" ht="12.75">
       <c r="A707" s="5"/>
       <c r="C707" s="5"/>
     </row>
-    <row r="708" spans="1:3" ht="12.5">
+    <row r="708" spans="1:3" ht="12.75">
       <c r="A708" s="5"/>
       <c r="C708" s="5"/>
     </row>
-    <row r="709" spans="1:3" ht="12.5">
+    <row r="709" spans="1:3" ht="12.75">
       <c r="A709" s="5"/>
       <c r="C709" s="5"/>
     </row>
-    <row r="710" spans="1:3" ht="12.5">
+    <row r="710" spans="1:3" ht="12.75">
       <c r="A710" s="5"/>
       <c r="C710" s="5"/>
     </row>
-    <row r="711" spans="1:3" ht="12.5">
+    <row r="711" spans="1:3" ht="12.75">
       <c r="A711" s="5"/>
       <c r="C711" s="5"/>
     </row>
-    <row r="712" spans="1:3" ht="12.5">
+    <row r="712" spans="1:3" ht="12.75">
       <c r="A712" s="5"/>
       <c r="C712" s="5"/>
     </row>
-    <row r="713" spans="1:3" ht="12.5">
+    <row r="713" spans="1:3" ht="12.75">
       <c r="A713" s="5"/>
       <c r="C713" s="5"/>
     </row>
-    <row r="714" spans="1:3" ht="12.5">
+    <row r="714" spans="1:3" ht="12.75">
       <c r="A714" s="5"/>
       <c r="C714" s="5"/>
     </row>
-    <row r="715" spans="1:3" ht="12.5">
+    <row r="715" spans="1:3" ht="12.75">
       <c r="A715" s="5"/>
       <c r="C715" s="5"/>
     </row>
-    <row r="716" spans="1:3" ht="12.5">
+    <row r="716" spans="1:3" ht="12.75">
       <c r="A716" s="5"/>
       <c r="C716" s="5"/>
     </row>
-    <row r="717" spans="1:3" ht="12.5">
+    <row r="717" spans="1:3" ht="12.75">
       <c r="A717" s="5"/>
       <c r="C717" s="5"/>
     </row>
-    <row r="718" spans="1:3" ht="12.5">
+    <row r="718" spans="1:3" ht="12.75">
       <c r="A718" s="5"/>
       <c r="C718" s="5"/>
     </row>
-    <row r="719" spans="1:3" ht="12.5">
+    <row r="719" spans="1:3" ht="12.75">
       <c r="A719" s="5"/>
       <c r="C719" s="5"/>
     </row>
-    <row r="720" spans="1:3" ht="12.5">
+    <row r="720" spans="1:3" ht="12.75">
       <c r="A720" s="5"/>
       <c r="C720" s="5"/>
     </row>
-    <row r="721" spans="1:3" ht="12.5">
+    <row r="721" spans="1:3" ht="12.75">
       <c r="A721" s="5"/>
       <c r="C721" s="5"/>
     </row>
-    <row r="722" spans="1:3" ht="12.5">
+    <row r="722" spans="1:3" ht="12.75">
       <c r="A722" s="5"/>
       <c r="C722" s="5"/>
     </row>
-    <row r="723" spans="1:3" ht="12.5">
+    <row r="723" spans="1:3" ht="12.75">
       <c r="A723" s="5"/>
       <c r="C723" s="5"/>
     </row>
-    <row r="724" spans="1:3" ht="12.5">
+    <row r="724" spans="1:3" ht="12.75">
       <c r="A724" s="5"/>
       <c r="C724" s="5"/>
     </row>
-    <row r="725" spans="1:3" ht="12.5">
+    <row r="725" spans="1:3" ht="12.75">
       <c r="A725" s="5"/>
       <c r="C725" s="5"/>
     </row>
-    <row r="726" spans="1:3" ht="12.5">
+    <row r="726" spans="1:3" ht="12.75">
       <c r="A726" s="5"/>
       <c r="C726" s="5"/>
     </row>
-    <row r="727" spans="1:3" ht="12.5">
+    <row r="727" spans="1:3" ht="12.75">
       <c r="A727" s="5"/>
       <c r="C727" s="5"/>
     </row>
-    <row r="728" spans="1:3" ht="12.5">
+    <row r="728" spans="1:3" ht="12.75">
       <c r="A728" s="5"/>
       <c r="C728" s="5"/>
     </row>
-    <row r="729" spans="1:3" ht="12.5">
+    <row r="729" spans="1:3" ht="12.75">
       <c r="A729" s="5"/>
       <c r="C729" s="5"/>
     </row>
-    <row r="730" spans="1:3" ht="12.5">
+    <row r="730" spans="1:3" ht="12.75">
       <c r="A730" s="5"/>
       <c r="C730" s="5"/>
     </row>
-    <row r="731" spans="1:3" ht="12.5">
+    <row r="731" spans="1:3" ht="12.75">
       <c r="A731" s="5"/>
       <c r="C731" s="5"/>
     </row>
-    <row r="732" spans="1:3" ht="12.5">
+    <row r="732" spans="1:3" ht="12.75">
       <c r="A732" s="5"/>
       <c r="C732" s="5"/>
     </row>
-    <row r="733" spans="1:3" ht="12.5">
+    <row r="733" spans="1:3" ht="12.75">
       <c r="A733" s="5"/>
       <c r="C733" s="5"/>
     </row>
-    <row r="734" spans="1:3" ht="12.5">
+    <row r="734" spans="1:3" ht="12.75">
       <c r="A734" s="5"/>
       <c r="C734" s="5"/>
     </row>
-    <row r="735" spans="1:3" ht="12.5">
+    <row r="735" spans="1:3" ht="12.75">
       <c r="A735" s="5"/>
       <c r="C735" s="5"/>
     </row>
-    <row r="736" spans="1:3" ht="12.5">
+    <row r="736" spans="1:3" ht="12.75">
       <c r="A736" s="5"/>
       <c r="C736" s="5"/>
     </row>
-    <row r="737" spans="1:3" ht="12.5">
+    <row r="737" spans="1:3" ht="12.75">
       <c r="A737" s="5"/>
       <c r="C737" s="5"/>
     </row>
-    <row r="738" spans="1:3" ht="12.5">
+    <row r="738" spans="1:3" ht="12.75">
       <c r="A738" s="5"/>
       <c r="C738" s="5"/>
     </row>
-    <row r="739" spans="1:3" ht="12.5">
+    <row r="739" spans="1:3" ht="12.75">
       <c r="A739" s="5"/>
       <c r="C739" s="5"/>
     </row>
-    <row r="740" spans="1:3" ht="12.5">
+    <row r="740" spans="1:3" ht="12.75">
       <c r="A740" s="5"/>
       <c r="C740" s="5"/>
     </row>
-    <row r="741" spans="1:3" ht="12.5">
+    <row r="741" spans="1:3" ht="12.75">
       <c r="A741" s="5"/>
       <c r="C741" s="5"/>
     </row>
-    <row r="742" spans="1:3" ht="12.5">
+    <row r="742" spans="1:3" ht="12.75">
       <c r="A742" s="5"/>
       <c r="C742" s="5"/>
     </row>
-    <row r="743" spans="1:3" ht="12.5">
+    <row r="743" spans="1:3" ht="12.75">
       <c r="A743" s="5"/>
       <c r="C743" s="5"/>
     </row>
-    <row r="744" spans="1:3" ht="12.5">
+    <row r="744" spans="1:3" ht="12.75">
       <c r="A744" s="5"/>
       <c r="C744" s="5"/>
     </row>
-    <row r="745" spans="1:3" ht="12.5">
+    <row r="745" spans="1:3" ht="12.75">
       <c r="A745" s="5"/>
       <c r="C745" s="5"/>
     </row>
-    <row r="746" spans="1:3" ht="12.5">
+    <row r="746" spans="1:3" ht="12.75">
       <c r="A746" s="5"/>
       <c r="C746" s="5"/>
     </row>
-    <row r="747" spans="1:3" ht="12.5">
+    <row r="747" spans="1:3" ht="12.75">
       <c r="A747" s="5"/>
       <c r="C747" s="5"/>
     </row>
-    <row r="748" spans="1:3" ht="12.5">
+    <row r="748" spans="1:3" ht="12.75">
       <c r="A748" s="5"/>
       <c r="C748" s="5"/>
     </row>
-    <row r="749" spans="1:3" ht="12.5">
+    <row r="749" spans="1:3" ht="12.75">
       <c r="A749" s="5"/>
       <c r="C749" s="5"/>
     </row>
-    <row r="750" spans="1:3" ht="12.5">
+    <row r="750" spans="1:3" ht="12.75">
       <c r="A750" s="5"/>
       <c r="C750" s="5"/>
     </row>
-    <row r="751" spans="1:3" ht="12.5">
+    <row r="751" spans="1:3" ht="12.75">
       <c r="A751" s="5"/>
       <c r="C751" s="5"/>
     </row>
-    <row r="752" spans="1:3" ht="12.5">
+    <row r="752" spans="1:3" ht="12.75">
       <c r="A752" s="5"/>
       <c r="C752" s="5"/>
     </row>
-    <row r="753" spans="1:3" ht="12.5">
+    <row r="753" spans="1:3" ht="12.75">
       <c r="A753" s="5"/>
       <c r="C753" s="5"/>
     </row>
-    <row r="754" spans="1:3" ht="12.5">
+    <row r="754" spans="1:3" ht="12.75">
       <c r="A754" s="5"/>
       <c r="C754" s="5"/>
     </row>
-    <row r="755" spans="1:3" ht="12.5">
+    <row r="755" spans="1:3" ht="12.75">
       <c r="A755" s="5"/>
       <c r="C755" s="5"/>
     </row>
-    <row r="756" spans="1:3" ht="12.5">
+    <row r="756" spans="1:3" ht="12.75">
       <c r="A756" s="5"/>
       <c r="C756" s="5"/>
     </row>
-    <row r="757" spans="1:3" ht="12.5">
+    <row r="757" spans="1:3" ht="12.75">
       <c r="A757" s="5"/>
       <c r="C757" s="5"/>
     </row>
-    <row r="758" spans="1:3" ht="12.5">
+    <row r="758" spans="1:3" ht="12.75">
       <c r="A758" s="5"/>
       <c r="C758" s="5"/>
     </row>
-    <row r="759" spans="1:3" ht="12.5">
+    <row r="759" spans="1:3" ht="12.75">
       <c r="A759" s="5"/>
       <c r="C759" s="5"/>
     </row>
-    <row r="760" spans="1:3" ht="12.5">
+    <row r="760" spans="1:3" ht="12.75">
       <c r="A760" s="5"/>
       <c r="C760" s="5"/>
     </row>
-    <row r="761" spans="1:3" ht="12.5">
+    <row r="761" spans="1:3" ht="12.75">
       <c r="A761" s="5"/>
       <c r="C761" s="5"/>
     </row>
-    <row r="762" spans="1:3" ht="12.5">
+    <row r="762" spans="1:3" ht="12.75">
       <c r="A762" s="5"/>
       <c r="C762" s="5"/>
     </row>
-    <row r="763" spans="1:3" ht="12.5">
+    <row r="763" spans="1:3" ht="12.75">
       <c r="A763" s="5"/>
       <c r="C763" s="5"/>
     </row>
-    <row r="764" spans="1:3" ht="12.5">
+    <row r="764" spans="1:3" ht="12.75">
       <c r="A764" s="5"/>
       <c r="C764" s="5"/>
     </row>
-    <row r="765" spans="1:3" ht="12.5">
+    <row r="765" spans="1:3" ht="12.75">
       <c r="A765" s="5"/>
       <c r="C765" s="5"/>
     </row>
-    <row r="766" spans="1:3" ht="12.5">
+    <row r="766" spans="1:3" ht="12.75">
       <c r="A766" s="5"/>
       <c r="C766" s="5"/>
     </row>
-    <row r="767" spans="1:3" ht="12.5">
+    <row r="767" spans="1:3" ht="12.75">
       <c r="A767" s="5"/>
       <c r="C767" s="5"/>
     </row>
-    <row r="768" spans="1:3" ht="12.5">
+    <row r="768" spans="1:3" ht="12.75">
       <c r="A768" s="5"/>
       <c r="C768" s="5"/>
     </row>
-    <row r="769" spans="1:3" ht="12.5">
+    <row r="769" spans="1:3" ht="12.75">
       <c r="A769" s="5"/>
       <c r="C769" s="5"/>
     </row>
-    <row r="770" spans="1:3" ht="12.5">
+    <row r="770" spans="1:3" ht="12.75">
       <c r="A770" s="5"/>
       <c r="C770" s="5"/>
     </row>
-    <row r="771" spans="1:3" ht="12.5">
+    <row r="771" spans="1:3" ht="12.75">
       <c r="A771" s="5"/>
       <c r="C771" s="5"/>
     </row>
-    <row r="772" spans="1:3" ht="12.5">
+    <row r="772" spans="1:3" ht="12.75">
       <c r="A772" s="5"/>
       <c r="C772" s="5"/>
     </row>
-    <row r="773" spans="1:3" ht="12.5">
+    <row r="773" spans="1:3" ht="12.75">
       <c r="A773" s="5"/>
       <c r="C773" s="5"/>
     </row>
-    <row r="774" spans="1:3" ht="12.5">
+    <row r="774" spans="1:3" ht="12.75">
       <c r="A774" s="5"/>
       <c r="C774" s="5"/>
     </row>
-    <row r="775" spans="1:3" ht="12.5">
+    <row r="775" spans="1:3" ht="12.75">
       <c r="A775" s="5"/>
       <c r="C775" s="5"/>
     </row>
-    <row r="776" spans="1:3" ht="12.5">
+    <row r="776" spans="1:3" ht="12.75">
       <c r="A776" s="5"/>
       <c r="C776" s="5"/>
     </row>
-    <row r="777" spans="1:3" ht="12.5">
+    <row r="777" spans="1:3" ht="12.75">
       <c r="A777" s="5"/>
       <c r="C777" s="5"/>
     </row>
-    <row r="778" spans="1:3" ht="12.5">
+    <row r="778" spans="1:3" ht="12.75">
       <c r="A778" s="5"/>
       <c r="C778" s="5"/>
     </row>
-    <row r="779" spans="1:3" ht="12.5">
+    <row r="779" spans="1:3" ht="12.75">
       <c r="A779" s="5"/>
       <c r="C779" s="5"/>
     </row>
-    <row r="780" spans="1:3" ht="12.5">
+    <row r="780" spans="1:3" ht="12.75">
       <c r="A780" s="5"/>
       <c r="C780" s="5"/>
     </row>
-    <row r="781" spans="1:3" ht="12.5">
+    <row r="781" spans="1:3" ht="12.75">
       <c r="A781" s="5"/>
       <c r="C781" s="5"/>
     </row>
-    <row r="782" spans="1:3" ht="12.5">
+    <row r="782" spans="1:3" ht="12.75">
       <c r="A782" s="5"/>
       <c r="C782" s="5"/>
     </row>
-    <row r="783" spans="1:3" ht="12.5">
+    <row r="783" spans="1:3" ht="12.75">
       <c r="A783" s="5"/>
       <c r="C783" s="5"/>
     </row>
-    <row r="784" spans="1:3" ht="12.5">
+    <row r="784" spans="1:3" ht="12.75">
       <c r="A784" s="5"/>
       <c r="C784" s="5"/>
     </row>
-    <row r="785" spans="1:3" ht="12.5">
+    <row r="785" spans="1:3" ht="12.75">
       <c r="A785" s="5"/>
       <c r="C785" s="5"/>
     </row>
-    <row r="786" spans="1:3" ht="12.5">
+    <row r="786" spans="1:3" ht="12.75">
       <c r="A786" s="5"/>
       <c r="C786" s="5"/>
     </row>
-    <row r="787" spans="1:3" ht="12.5">
+    <row r="787" spans="1:3" ht="12.75">
       <c r="A787" s="5"/>
       <c r="C787" s="5"/>
     </row>
-    <row r="788" spans="1:3" ht="12.5">
+    <row r="788" spans="1:3" ht="12.75">
       <c r="A788" s="5"/>
       <c r="C788" s="5"/>
     </row>
-    <row r="789" spans="1:3" ht="12.5">
+    <row r="789" spans="1:3" ht="12.75">
       <c r="A789" s="5"/>
       <c r="C789" s="5"/>
     </row>
-    <row r="790" spans="1:3" ht="12.5">
+    <row r="790" spans="1:3" ht="12.75">
       <c r="A790" s="5"/>
       <c r="C790" s="5"/>
     </row>
-    <row r="791" spans="1:3" ht="12.5">
+    <row r="791" spans="1:3" ht="12.75">
       <c r="A791" s="5"/>
       <c r="C791" s="5"/>
     </row>
-    <row r="792" spans="1:3" ht="12.5">
+    <row r="792" spans="1:3" ht="12.75">
       <c r="A792" s="5"/>
       <c r="C792" s="5"/>
     </row>
-    <row r="793" spans="1:3" ht="12.5">
+    <row r="793" spans="1:3" ht="12.75">
       <c r="A793" s="5"/>
       <c r="C793" s="5"/>
     </row>
-    <row r="794" spans="1:3" ht="12.5">
+    <row r="794" spans="1:3" ht="12.75">
       <c r="A794" s="5"/>
       <c r="C794" s="5"/>
     </row>
-    <row r="795" spans="1:3" ht="12.5">
+    <row r="795" spans="1:3" ht="12.75">
       <c r="A795" s="5"/>
       <c r="C795" s="5"/>
     </row>
-    <row r="796" spans="1:3" ht="12.5">
+    <row r="796" spans="1:3" ht="12.75">
       <c r="A796" s="5"/>
       <c r="C796" s="5"/>
     </row>
-    <row r="797" spans="1:3" ht="12.5">
+    <row r="797" spans="1:3" ht="12.75">
       <c r="A797" s="5"/>
       <c r="C797" s="5"/>
     </row>
-    <row r="798" spans="1:3" ht="12.5">
+    <row r="798" spans="1:3" ht="12.75">
       <c r="A798" s="5"/>
       <c r="C798" s="5"/>
     </row>
-    <row r="799" spans="1:3" ht="12.5">
+    <row r="799" spans="1:3" ht="12.75">
       <c r="A799" s="5"/>
       <c r="C799" s="5"/>
     </row>
-    <row r="800" spans="1:3" ht="12.5">
+    <row r="800" spans="1:3" ht="12.75">
       <c r="A800" s="5"/>
       <c r="C800" s="5"/>
     </row>
-    <row r="801" spans="1:3" ht="12.5">
+    <row r="801" spans="1:3" ht="12.75">
       <c r="A801" s="5"/>
       <c r="C801" s="5"/>
     </row>
-    <row r="802" spans="1:3" ht="12.5">
+    <row r="802" spans="1:3" ht="12.75">
       <c r="A802" s="5"/>
       <c r="C802" s="5"/>
     </row>
-    <row r="803" spans="1:3" ht="12.5">
+    <row r="803" spans="1:3" ht="12.75">
       <c r="A803" s="5"/>
       <c r="C803" s="5"/>
     </row>
-    <row r="804" spans="1:3" ht="12.5">
+    <row r="804" spans="1:3" ht="12.75">
       <c r="A804" s="5"/>
       <c r="C804" s="5"/>
     </row>
-    <row r="805" spans="1:3" ht="12.5">
+    <row r="805" spans="1:3" ht="12.75">
       <c r="A805" s="5"/>
       <c r="C805" s="5"/>
     </row>
-    <row r="806" spans="1:3" ht="12.5">
+    <row r="806" spans="1:3" ht="12.75">
       <c r="A806" s="5"/>
       <c r="C806" s="5"/>
     </row>
-    <row r="807" spans="1:3" ht="12.5">
+    <row r="807" spans="1:3" ht="12.75">
       <c r="A807" s="5"/>
       <c r="C807" s="5"/>
     </row>
-    <row r="808" spans="1:3" ht="12.5">
+    <row r="808" spans="1:3" ht="12.75">
       <c r="A808" s="5"/>
       <c r="C808" s="5"/>
     </row>
-    <row r="809" spans="1:3" ht="12.5">
+    <row r="809" spans="1:3" ht="12.75">
       <c r="A809" s="5"/>
       <c r="C809" s="5"/>
     </row>
-    <row r="810" spans="1:3" ht="12.5">
+    <row r="810" spans="1:3" ht="12.75">
       <c r="A810" s="5"/>
       <c r="C810" s="5"/>
     </row>
-    <row r="811" spans="1:3" ht="12.5">
+    <row r="811" spans="1:3" ht="12.75">
       <c r="A811" s="5"/>
       <c r="C811" s="5"/>
     </row>
-    <row r="812" spans="1:3" ht="12.5">
+    <row r="812" spans="1:3" ht="12.75">
       <c r="A812" s="5"/>
       <c r="C812" s="5"/>
     </row>
-    <row r="813" spans="1:3" ht="12.5">
+    <row r="813" spans="1:3" ht="12.75">
       <c r="A813" s="5"/>
       <c r="C813" s="5"/>
     </row>
-    <row r="814" spans="1:3" ht="12.5">
+    <row r="814" spans="1:3" ht="12.75">
       <c r="A814" s="5"/>
       <c r="C814" s="5"/>
     </row>
-    <row r="815" spans="1:3" ht="12.5">
+    <row r="815" spans="1:3" ht="12.75">
       <c r="A815" s="5"/>
       <c r="C815" s="5"/>
     </row>
-    <row r="816" spans="1:3" ht="12.5">
+    <row r="816" spans="1:3" ht="12.75">
       <c r="A816" s="5"/>
       <c r="C816" s="5"/>
     </row>
-    <row r="817" spans="1:3" ht="12.5">
+    <row r="817" spans="1:3" ht="12.75">
       <c r="A817" s="5"/>
       <c r="C817" s="5"/>
     </row>
-    <row r="818" spans="1:3" ht="12.5">
+    <row r="818" spans="1:3" ht="12.75">
       <c r="A818" s="5"/>
       <c r="C818" s="5"/>
     </row>
-    <row r="819" spans="1:3" ht="12.5">
+    <row r="819" spans="1:3" ht="12.75">
       <c r="A819" s="5"/>
       <c r="C819" s="5"/>
     </row>
-    <row r="820" spans="1:3" ht="12.5">
+    <row r="820" spans="1:3" ht="12.75">
       <c r="A820" s="5"/>
       <c r="C820" s="5"/>
     </row>
-    <row r="821" spans="1:3" ht="12.5">
+    <row r="821" spans="1:3" ht="12.75">
       <c r="A821" s="5"/>
       <c r="C821" s="5"/>
     </row>
-    <row r="822" spans="1:3" ht="12.5">
+    <row r="822" spans="1:3" ht="12.75">
       <c r="A822" s="5"/>
       <c r="C822" s="5"/>
     </row>
-    <row r="823" spans="1:3" ht="12.5">
+    <row r="823" spans="1:3" ht="12.75">
       <c r="A823" s="5"/>
       <c r="C823" s="5"/>
     </row>
-    <row r="824" spans="1:3" ht="12.5">
+    <row r="824" spans="1:3" ht="12.75">
       <c r="A824" s="5"/>
       <c r="C824" s="5"/>
     </row>
-    <row r="825" spans="1:3" ht="12.5">
+    <row r="825" spans="1:3" ht="12.75">
       <c r="A825" s="5"/>
       <c r="C825" s="5"/>
     </row>
-    <row r="826" spans="1:3" ht="12.5">
+    <row r="826" spans="1:3" ht="12.75">
       <c r="A826" s="5"/>
       <c r="C826" s="5"/>
     </row>
-    <row r="827" spans="1:3" ht="12.5">
+    <row r="827" spans="1:3" ht="12.75">
       <c r="A827" s="5"/>
       <c r="C827" s="5"/>
     </row>
-    <row r="828" spans="1:3" ht="12.5">
+    <row r="828" spans="1:3" ht="12.75">
       <c r="A828" s="5"/>
       <c r="C828" s="5"/>
     </row>
-    <row r="829" spans="1:3" ht="12.5">
+    <row r="829" spans="1:3" ht="12.75">
       <c r="A829" s="5"/>
       <c r="C829" s="5"/>
     </row>
-    <row r="830" spans="1:3" ht="12.5">
+    <row r="830" spans="1:3" ht="12.75">
       <c r="A830" s="5"/>
       <c r="C830" s="5"/>
     </row>
-    <row r="831" spans="1:3" ht="12.5">
+    <row r="831" spans="1:3" ht="12.75">
       <c r="A831" s="5"/>
       <c r="C831" s="5"/>
     </row>
-    <row r="832" spans="1:3" ht="12.5">
+    <row r="832" spans="1:3" ht="12.75">
       <c r="A832" s="5"/>
       <c r="C832" s="5"/>
     </row>
-    <row r="833" spans="1:3" ht="12.5">
+    <row r="833" spans="1:3" ht="12.75">
       <c r="A833" s="5"/>
       <c r="C833" s="5"/>
     </row>
-    <row r="834" spans="1:3" ht="12.5">
+    <row r="834" spans="1:3" ht="12.75">
       <c r="A834" s="5"/>
       <c r="C834" s="5"/>
     </row>
-    <row r="835" spans="1:3" ht="12.5">
+    <row r="835" spans="1:3" ht="12.75">
       <c r="A835" s="5"/>
       <c r="C835" s="5"/>
     </row>
-    <row r="836" spans="1:3" ht="12.5">
+    <row r="836" spans="1:3" ht="12.75">
       <c r="A836" s="5"/>
       <c r="C836" s="5"/>
     </row>
-    <row r="837" spans="1:3" ht="12.5">
+    <row r="837" spans="1:3" ht="12.75">
       <c r="A837" s="5"/>
       <c r="C837" s="5"/>
     </row>
-    <row r="838" spans="1:3" ht="12.5">
+    <row r="838" spans="1:3" ht="12.75">
       <c r="A838" s="5"/>
       <c r="C838" s="5"/>
     </row>
-    <row r="839" spans="1:3" ht="12.5">
+    <row r="839" spans="1:3" ht="12.75">
       <c r="A839" s="5"/>
       <c r="C839" s="5"/>
     </row>
-    <row r="840" spans="1:3" ht="12.5">
+    <row r="840" spans="1:3" ht="12.75">
       <c r="A840" s="5"/>
       <c r="C840" s="5"/>
     </row>
-    <row r="841" spans="1:3" ht="12.5">
+    <row r="841" spans="1:3" ht="12.75">
       <c r="A841" s="5"/>
       <c r="C841" s="5"/>
     </row>
-    <row r="842" spans="1:3" ht="12.5">
+    <row r="842" spans="1:3" ht="12.75">
       <c r="A842" s="5"/>
       <c r="C842" s="5"/>
     </row>
-    <row r="843" spans="1:3" ht="12.5">
+    <row r="843" spans="1:3" ht="12.75">
       <c r="A843" s="5"/>
       <c r="C843" s="5"/>
     </row>
-    <row r="844" spans="1:3" ht="12.5">
+    <row r="844" spans="1:3" ht="12.75">
       <c r="A844" s="5"/>
       <c r="C844" s="5"/>
     </row>
-    <row r="845" spans="1:3" ht="12.5">
+    <row r="845" spans="1:3" ht="12.75">
       <c r="A845" s="5"/>
       <c r="C845" s="5"/>
     </row>
-    <row r="846" spans="1:3" ht="12.5">
+    <row r="846" spans="1:3" ht="12.75">
       <c r="A846" s="5"/>
       <c r="C846" s="5"/>
     </row>
-    <row r="847" spans="1:3" ht="12.5">
+    <row r="847" spans="1:3" ht="12.75">
       <c r="A847" s="5"/>
       <c r="C847" s="5"/>
     </row>
-    <row r="848" spans="1:3" ht="12.5">
+    <row r="848" spans="1:3" ht="12.75">
       <c r="A848" s="5"/>
       <c r="C848" s="5"/>
     </row>
-    <row r="849" spans="1:3" ht="12.5">
+    <row r="849" spans="1:3" ht="12.75">
       <c r="A849" s="5"/>
       <c r="C849" s="5"/>
     </row>
-    <row r="850" spans="1:3" ht="12.5">
+    <row r="850" spans="1:3" ht="12.75">
       <c r="A850" s="5"/>
       <c r="C850" s="5"/>
     </row>
-    <row r="851" spans="1:3" ht="12.5">
+    <row r="851" spans="1:3" ht="12.75">
       <c r="A851" s="5"/>
       <c r="C851" s="5"/>
     </row>
-    <row r="852" spans="1:3" ht="12.5">
+    <row r="852" spans="1:3" ht="12.75">
       <c r="A852" s="5"/>
       <c r="C852" s="5"/>
     </row>
-    <row r="853" spans="1:3" ht="12.5">
+    <row r="853" spans="1:3" ht="12.75">
       <c r="A853" s="5"/>
       <c r="C853" s="5"/>
     </row>
-    <row r="854" spans="1:3" ht="12.5">
+    <row r="854" spans="1:3" ht="12.75">
       <c r="A854" s="5"/>
       <c r="C854" s="5"/>
     </row>
-    <row r="855" spans="1:3" ht="12.5">
+    <row r="855" spans="1:3" ht="12.75">
       <c r="A855" s="5"/>
       <c r="C855" s="5"/>
     </row>
-    <row r="856" spans="1:3" ht="12.5">
+    <row r="856" spans="1:3" ht="12.75">
       <c r="A856" s="5"/>
       <c r="C856" s="5"/>
     </row>
-    <row r="857" spans="1:3" ht="12.5">
+    <row r="857" spans="1:3" ht="12.75">
       <c r="A857" s="5"/>
       <c r="C857" s="5"/>
     </row>
-    <row r="858" spans="1:3" ht="12.5">
+    <row r="858" spans="1:3" ht="12.75">
       <c r="A858" s="5"/>
       <c r="C858" s="5"/>
     </row>
-    <row r="859" spans="1:3" ht="12.5">
+    <row r="859" spans="1:3" ht="12.75">
       <c r="A859" s="5"/>
       <c r="C859" s="5"/>
     </row>
-    <row r="860" spans="1:3" ht="12.5">
+    <row r="860" spans="1:3" ht="12.75">
       <c r="A860" s="5"/>
       <c r="C860" s="5"/>
     </row>
-    <row r="861" spans="1:3" ht="12.5">
+    <row r="861" spans="1:3" ht="12.75">
       <c r="A861" s="5"/>
       <c r="C861" s="5"/>
     </row>
-    <row r="862" spans="1:3" ht="12.5">
+    <row r="862" spans="1:3" ht="12.75">
       <c r="A862" s="5"/>
       <c r="C862" s="5"/>
     </row>
-    <row r="863" spans="1:3" ht="12.5">
+    <row r="863" spans="1:3" ht="12.75">
       <c r="A863" s="5"/>
       <c r="C863" s="5"/>
     </row>
-    <row r="864" spans="1:3" ht="12.5">
+    <row r="864" spans="1:3" ht="12.75">
       <c r="A864" s="5"/>
       <c r="C864" s="5"/>
     </row>
-    <row r="865" spans="1:3" ht="12.5">
+    <row r="865" spans="1:3" ht="12.75">
       <c r="A865" s="5"/>
       <c r="C865" s="5"/>
     </row>
-    <row r="866" spans="1:3" ht="12.5">
+    <row r="866" spans="1:3" ht="12.75">
       <c r="A866" s="5"/>
       <c r="C866" s="5"/>
     </row>
-    <row r="867" spans="1:3" ht="12.5">
+    <row r="867" spans="1:3" ht="12.75">
       <c r="A867" s="5"/>
       <c r="C867" s="5"/>
     </row>
-    <row r="868" spans="1:3" ht="12.5">
+    <row r="868" spans="1:3" ht="12.75">
       <c r="A868" s="5"/>
       <c r="C868" s="5"/>
     </row>
-    <row r="869" spans="1:3" ht="12.5">
+    <row r="869" spans="1:3" ht="12.75">
       <c r="A869" s="5"/>
       <c r="C869" s="5"/>
     </row>
-    <row r="870" spans="1:3" ht="12.5">
+    <row r="870" spans="1:3" ht="12.75">
       <c r="A870" s="5"/>
       <c r="C870" s="5"/>
     </row>
-    <row r="871" spans="1:3" ht="12.5">
+    <row r="871" spans="1:3" ht="12.75">
       <c r="A871" s="5"/>
       <c r="C871" s="5"/>
     </row>
-    <row r="872" spans="1:3" ht="12.5">
+    <row r="872" spans="1:3" ht="12.75">
       <c r="A872" s="5"/>
       <c r="C872" s="5"/>
     </row>
-    <row r="873" spans="1:3" ht="12.5">
+    <row r="873" spans="1:3" ht="12.75">
       <c r="A873" s="5"/>
       <c r="C873" s="5"/>
     </row>
-    <row r="874" spans="1:3" ht="12.5">
+    <row r="874" spans="1:3" ht="12.75">
       <c r="A874" s="5"/>
       <c r="C874" s="5"/>
     </row>
-    <row r="875" spans="1:3" ht="12.5">
+    <row r="875" spans="1:3" ht="12.75">
       <c r="A875" s="5"/>
       <c r="C875" s="5"/>
     </row>
-    <row r="876" spans="1:3" ht="12.5">
+    <row r="876" spans="1:3" ht="12.75">
       <c r="A876" s="5"/>
       <c r="C876" s="5"/>
     </row>
-    <row r="877" spans="1:3" ht="12.5">
+    <row r="877" spans="1:3" ht="12.75">
       <c r="A877" s="5"/>
       <c r="C877" s="5"/>
     </row>
-    <row r="878" spans="1:3" ht="12.5">
+    <row r="878" spans="1:3" ht="12.75">
       <c r="A878" s="5"/>
       <c r="C878" s="5"/>
     </row>
-    <row r="879" spans="1:3" ht="12.5">
+    <row r="879" spans="1:3" ht="12.75">
       <c r="A879" s="5"/>
       <c r="C879" s="5"/>
     </row>
-    <row r="880" spans="1:3" ht="12.5">
+    <row r="880" spans="1:3" ht="12.75">
       <c r="A880" s="5"/>
       <c r="C880" s="5"/>
     </row>
-    <row r="881" spans="1:3" ht="12.5">
+    <row r="881" spans="1:3" ht="12.75">
       <c r="A881" s="5"/>
       <c r="C881" s="5"/>
     </row>
-    <row r="882" spans="1:3" ht="12.5">
+    <row r="882" spans="1:3" ht="12.75">
       <c r="A882" s="5"/>
       <c r="C882" s="5"/>
     </row>
-    <row r="883" spans="1:3" ht="12.5">
+    <row r="883" spans="1:3" ht="12.75">
       <c r="A883" s="5"/>
       <c r="C883" s="5"/>
     </row>
-    <row r="884" spans="1:3" ht="12.5">
+    <row r="884" spans="1:3" ht="12.75">
       <c r="A884" s="5"/>
       <c r="C884" s="5"/>
     </row>
-    <row r="885" spans="1:3" ht="12.5">
+    <row r="885" spans="1:3" ht="12.75">
       <c r="A885" s="5"/>
       <c r="C885" s="5"/>
     </row>
-    <row r="886" spans="1:3" ht="12.5">
+    <row r="886" spans="1:3" ht="12.75">
       <c r="A886" s="5"/>
       <c r="C886" s="5"/>
     </row>
-    <row r="887" spans="1:3" ht="12.5">
+    <row r="887" spans="1:3" ht="12.75">
       <c r="A887" s="5"/>
       <c r="C887" s="5"/>
     </row>
-    <row r="888" spans="1:3" ht="12.5">
+    <row r="888" spans="1:3" ht="12.75">
       <c r="A888" s="5"/>
       <c r="C888" s="5"/>
     </row>
-    <row r="889" spans="1:3" ht="12.5">
+    <row r="889" spans="1:3" ht="12.75">
       <c r="A889" s="5"/>
       <c r="C889" s="5"/>
     </row>
-    <row r="890" spans="1:3" ht="12.5">
+    <row r="890" spans="1:3" ht="12.75">
       <c r="A890" s="5"/>
       <c r="C890" s="5"/>
     </row>
-    <row r="891" spans="1:3" ht="12.5">
+    <row r="891" spans="1:3" ht="12.75">
       <c r="A891" s="5"/>
       <c r="C891" s="5"/>
     </row>
-    <row r="892" spans="1:3" ht="12.5">
+    <row r="892" spans="1:3" ht="12.75">
       <c r="A892" s="5"/>
       <c r="C892" s="5"/>
     </row>
-    <row r="893" spans="1:3" ht="12.5">
+    <row r="893" spans="1:3" ht="12.75">
       <c r="A893" s="5"/>
       <c r="C893" s="5"/>
     </row>
-    <row r="894" spans="1:3" ht="12.5">
+    <row r="894" spans="1:3" ht="12.75">
       <c r="A894" s="5"/>
       <c r="C894" s="5"/>
     </row>
-    <row r="895" spans="1:3" ht="12.5">
+    <row r="895" spans="1:3" ht="12.75">
       <c r="A895" s="5"/>
       <c r="C895" s="5"/>
     </row>
-    <row r="896" spans="1:3" ht="12.5">
+    <row r="896" spans="1:3" ht="12.75">
       <c r="A896" s="5"/>
       <c r="C896" s="5"/>
     </row>
-    <row r="897" spans="1:3" ht="12.5">
+    <row r="897" spans="1:3" ht="12.75">
       <c r="A897" s="5"/>
       <c r="C897" s="5"/>
     </row>
-    <row r="898" spans="1:3" ht="12.5">
+    <row r="898" spans="1:3" ht="12.75">
       <c r="A898" s="5"/>
       <c r="C898" s="5"/>
     </row>
-    <row r="899" spans="1:3" ht="12.5">
+    <row r="899" spans="1:3" ht="12.75">
       <c r="A899" s="5"/>
       <c r="C899" s="5"/>
     </row>
-    <row r="900" spans="1:3" ht="12.5">
+    <row r="900" spans="1:3" ht="12.75">
       <c r="A900" s="5"/>
       <c r="C900" s="5"/>
     </row>
-    <row r="901" spans="1:3" ht="12.5">
+    <row r="901" spans="1:3" ht="12.75">
       <c r="A901" s="5"/>
       <c r="C901" s="5"/>
     </row>
-    <row r="902" spans="1:3" ht="12.5">
+    <row r="902" spans="1:3" ht="12.75">
       <c r="A902" s="5"/>
       <c r="C902" s="5"/>
     </row>
-    <row r="903" spans="1:3" ht="12.5">
+    <row r="903" spans="1:3" ht="12.75">
       <c r="A903" s="5"/>
       <c r="C903" s="5"/>
     </row>
-    <row r="904" spans="1:3" ht="12.5">
+    <row r="904" spans="1:3" ht="12.75">
       <c r="A904" s="5"/>
       <c r="C904" s="5"/>
     </row>
-    <row r="905" spans="1:3" ht="12.5">
+    <row r="905" spans="1:3" ht="12.75">
       <c r="A905" s="5"/>
       <c r="C905" s="5"/>
     </row>
-    <row r="906" spans="1:3" ht="12.5">
+    <row r="906" spans="1:3" ht="12.75">
       <c r="A906" s="5"/>
       <c r="C906" s="5"/>
     </row>
-    <row r="907" spans="1:3" ht="12.5">
+    <row r="907" spans="1:3" ht="12.75">
       <c r="A907" s="5"/>
       <c r="C907" s="5"/>
     </row>
-    <row r="908" spans="1:3" ht="12.5">
+    <row r="908" spans="1:3" ht="12.75">
       <c r="A908" s="5"/>
       <c r="C908" s="5"/>
     </row>
-    <row r="909" spans="1:3" ht="12.5">
+    <row r="909" spans="1:3" ht="12.75">
       <c r="A909" s="5"/>
       <c r="C909" s="5"/>
     </row>
-    <row r="910" spans="1:3" ht="12.5">
+    <row r="910" spans="1:3" ht="12.75">
       <c r="A910" s="5"/>
       <c r="C910" s="5"/>
     </row>
-    <row r="911" spans="1:3" ht="12.5">
+    <row r="911" spans="1:3" ht="12.75">
       <c r="A911" s="5"/>
       <c r="C911" s="5"/>
     </row>
-    <row r="912" spans="1:3" ht="12.5">
+    <row r="912" spans="1:3" ht="12.75">
       <c r="A912" s="5"/>
       <c r="C912" s="5"/>
     </row>
-    <row r="913" spans="1:3" ht="12.5">
+    <row r="913" spans="1:3" ht="12.75">
       <c r="A913" s="5"/>
       <c r="C913" s="5"/>
     </row>
-    <row r="914" spans="1:3" ht="12.5">
+    <row r="914" spans="1:3" ht="12.75">
       <c r="A914" s="5"/>
       <c r="C914" s="5"/>
     </row>
-    <row r="915" spans="1:3" ht="12.5">
+    <row r="915" spans="1:3" ht="12.75">
       <c r="A915" s="5"/>
       <c r="C915" s="5"/>
     </row>
-    <row r="916" spans="1:3" ht="12.5">
+    <row r="916" spans="1:3" ht="12.75">
       <c r="A916" s="5"/>
       <c r="C916" s="5"/>
     </row>
-    <row r="917" spans="1:3" ht="12.5">
+    <row r="917" spans="1:3" ht="12.75">
       <c r="A917" s="5"/>
       <c r="C917" s="5"/>
     </row>
-    <row r="918" spans="1:3" ht="12.5">
+    <row r="918" spans="1:3" ht="12.75">
       <c r="A918" s="5"/>
       <c r="C918" s="5"/>
     </row>
-    <row r="919" spans="1:3" ht="12.5">
+    <row r="919" spans="1:3" ht="12.75">
       <c r="A919" s="5"/>
       <c r="C919" s="5"/>
     </row>
-    <row r="920" spans="1:3" ht="12.5">
+    <row r="920" spans="1:3" ht="12.75">
       <c r="A920" s="5"/>
       <c r="C920" s="5"/>
     </row>
-    <row r="921" spans="1:3" ht="12.5">
+    <row r="921" spans="1:3" ht="12.75">
       <c r="A921" s="5"/>
       <c r="C921" s="5"/>
     </row>
-    <row r="922" spans="1:3" ht="12.5">
+    <row r="922" spans="1:3" ht="12.75">
       <c r="A922" s="5"/>
       <c r="C922" s="5"/>
     </row>
-    <row r="923" spans="1:3" ht="12.5">
+    <row r="923" spans="1:3" ht="12.75">
       <c r="A923" s="5"/>
       <c r="C923" s="5"/>
     </row>
-    <row r="924" spans="1:3" ht="12.5">
+    <row r="924" spans="1:3" ht="12.75">
       <c r="A924" s="5"/>
       <c r="C924" s="5"/>
     </row>
-    <row r="925" spans="1:3" ht="12.5">
+    <row r="925" spans="1:3" ht="12.75">
       <c r="A925" s="5"/>
       <c r="C925" s="5"/>
     </row>
-    <row r="926" spans="1:3" ht="12.5">
+    <row r="926" spans="1:3" ht="12.75">
       <c r="A926" s="5"/>
       <c r="C926" s="5"/>
     </row>
-    <row r="927" spans="1:3" ht="12.5">
+    <row r="927" spans="1:3" ht="12.75">
       <c r="A927" s="5"/>
       <c r="C927" s="5"/>
     </row>
-    <row r="928" spans="1:3" ht="12.5">
+    <row r="928" spans="1:3" ht="12.75">
       <c r="A928" s="5"/>
       <c r="C928" s="5"/>
     </row>
-    <row r="929" spans="1:3" ht="12.5">
+    <row r="929" spans="1:3" ht="12.75">
       <c r="A929" s="5"/>
       <c r="C929" s="5"/>
     </row>
-    <row r="930" spans="1:3" ht="12.5">
+    <row r="930" spans="1:3" ht="12.75">
       <c r="A930" s="5"/>
       <c r="C930" s="5"/>
     </row>
-    <row r="931" spans="1:3" ht="12.5">
+    <row r="931" spans="1:3" ht="12.75">
       <c r="A931" s="5"/>
       <c r="C931" s="5"/>
     </row>
-    <row r="932" spans="1:3" ht="12.5">
+    <row r="932" spans="1:3" ht="12.75">
       <c r="A932" s="5"/>
       <c r="C932" s="5"/>
     </row>
-    <row r="933" spans="1:3" ht="12.5">
+    <row r="933" spans="1:3" ht="12.75">
       <c r="A933" s="5"/>
       <c r="C933" s="5"/>
     </row>
-    <row r="934" spans="1:3" ht="12.5">
+    <row r="934" spans="1:3" ht="12.75">
       <c r="A934" s="5"/>
       <c r="C934" s="5"/>
     </row>
-    <row r="935" spans="1:3" ht="12.5">
+    <row r="935" spans="1:3" ht="12.75">
       <c r="A935" s="5"/>
       <c r="C935" s="5"/>
     </row>
-    <row r="936" spans="1:3" ht="12.5">
+    <row r="936" spans="1:3" ht="12.75">
       <c r="A936" s="5"/>
       <c r="C936" s="5"/>
     </row>
-    <row r="937" spans="1:3" ht="12.5">
+    <row r="937" spans="1:3" ht="12.75">
       <c r="A937" s="5"/>
       <c r="C937" s="5"/>
     </row>
-    <row r="938" spans="1:3" ht="12.5">
+    <row r="938" spans="1:3" ht="12.75">
       <c r="A938" s="5"/>
       <c r="C938" s="5"/>
     </row>
-    <row r="939" spans="1:3" ht="12.5">
+    <row r="939" spans="1:3" ht="12.75">
       <c r="A939" s="5"/>
       <c r="C939" s="5"/>
     </row>
-    <row r="940" spans="1:3" ht="12.5">
+    <row r="940" spans="1:3" ht="12.75">
       <c r="A940" s="5"/>
       <c r="C940" s="5"/>
     </row>
-    <row r="941" spans="1:3" ht="12.5">
+    <row r="941" spans="1:3" ht="12.75">
       <c r="A941" s="5"/>
       <c r="C941" s="5"/>
     </row>
-    <row r="942" spans="1:3" ht="12.5">
+    <row r="942" spans="1:3" ht="12.75">
       <c r="A942" s="5"/>
       <c r="C942" s="5"/>
     </row>
-    <row r="943" spans="1:3" ht="12.5">
+    <row r="943" spans="1:3" ht="12.75">
       <c r="A943" s="5"/>
       <c r="C943" s="5"/>
     </row>
-    <row r="944" spans="1:3" ht="12.5">
+    <row r="944" spans="1:3" ht="12.75">
       <c r="A944" s="5"/>
       <c r="C944" s="5"/>
     </row>
-    <row r="945" spans="1:3" ht="12.5">
+    <row r="945" spans="1:3" ht="12.75">
       <c r="A945" s="5"/>
       <c r="C945" s="5"/>
     </row>
-    <row r="946" spans="1:3" ht="12.5">
+    <row r="946" spans="1:3" ht="12.75">
       <c r="A946" s="5"/>
       <c r="C946" s="5"/>
     </row>
-    <row r="947" spans="1:3" ht="12.5">
+    <row r="947" spans="1:3" ht="12.75">
       <c r="A947" s="5"/>
       <c r="C947" s="5"/>
     </row>
-    <row r="948" spans="1:3" ht="12.5">
+    <row r="948" spans="1:3" ht="12.75">
       <c r="A948" s="5"/>
       <c r="C948" s="5"/>
     </row>
-    <row r="949" spans="1:3" ht="12.5">
+    <row r="949" spans="1:3" ht="12.75">
       <c r="A949" s="5"/>
       <c r="C949" s="5"/>
     </row>
-    <row r="950" spans="1:3" ht="12.5">
+    <row r="950" spans="1:3" ht="12.75">
       <c r="A950" s="5"/>
       <c r="C950" s="5"/>
     </row>
-    <row r="951" spans="1:3" ht="12.5">
+    <row r="951" spans="1:3" ht="12.75">
       <c r="A951" s="5"/>
       <c r="C951" s="5"/>
     </row>
-    <row r="952" spans="1:3" ht="12.5">
+    <row r="952" spans="1:3" ht="12.75">
       <c r="A952" s="5"/>
       <c r="C952" s="5"/>
     </row>
-    <row r="953" spans="1:3" ht="12.5">
+    <row r="953" spans="1:3" ht="12.75">
       <c r="A953" s="5"/>
       <c r="C953" s="5"/>
     </row>
-    <row r="954" spans="1:3" ht="12.5">
+    <row r="954" spans="1:3" ht="12.75">
       <c r="A954" s="5"/>
       <c r="C954" s="5"/>
     </row>
-    <row r="955" spans="1:3" ht="12.5">
+    <row r="955" spans="1:3" ht="12.75">
       <c r="A955" s="5"/>
       <c r="C955" s="5"/>
     </row>
-    <row r="956" spans="1:3" ht="12.5">
+    <row r="956" spans="1:3" ht="12.75">
       <c r="A956" s="5"/>
       <c r="C956" s="5"/>
     </row>
-    <row r="957" spans="1:3" ht="12.5">
+    <row r="957" spans="1:3" ht="12.75">
       <c r="A957" s="5"/>
       <c r="C957" s="5"/>
     </row>
-    <row r="958" spans="1:3" ht="12.5">
+    <row r="958" spans="1:3" ht="12.75">
       <c r="A958" s="5"/>
       <c r="C958" s="5"/>
     </row>
-    <row r="959" spans="1:3" ht="12.5">
+    <row r="959" spans="1:3" ht="12.75">
       <c r="A959" s="5"/>
       <c r="C959" s="5"/>
     </row>
-    <row r="960" spans="1:3" ht="12.5">
+    <row r="960" spans="1:3" ht="12.75">
       <c r="A960" s="5"/>
       <c r="C960" s="5"/>
     </row>
-    <row r="961" spans="1:3" ht="12.5">
+    <row r="961" spans="1:3" ht="12.75">
       <c r="A961" s="5"/>
       <c r="C961" s="5"/>
     </row>
-    <row r="962" spans="1:3" ht="12.5">
+    <row r="962" spans="1:3" ht="12.75">
       <c r="A962" s="5"/>
       <c r="C962" s="5"/>
     </row>
-    <row r="963" spans="1:3" ht="12.5">
+    <row r="963" spans="1:3" ht="12.75">
       <c r="A963" s="5"/>
       <c r="C963" s="5"/>
     </row>
-    <row r="964" spans="1:3" ht="12.5">
+    <row r="964" spans="1:3" ht="12.75">
       <c r="A964" s="5"/>
       <c r="C964" s="5"/>
     </row>
-    <row r="965" spans="1:3" ht="12.5">
+    <row r="965" spans="1:3" ht="12.75">
       <c r="A965" s="5"/>
       <c r="C965" s="5"/>
     </row>
-    <row r="966" spans="1:3" ht="12.5">
+    <row r="966" spans="1:3" ht="12.75">
       <c r="A966" s="5"/>
       <c r="C966" s="5"/>
     </row>
-    <row r="967" spans="1:3" ht="12.5">
+    <row r="967" spans="1:3" ht="12.75">
       <c r="A967" s="5"/>
       <c r="C967" s="5"/>
     </row>
-    <row r="968" spans="1:3" ht="12.5">
+    <row r="968" spans="1:3" ht="12.75">
       <c r="A968" s="5"/>
       <c r="C968" s="5"/>
     </row>
-    <row r="969" spans="1:3" ht="12.5">
+    <row r="969" spans="1:3" ht="12.75">
       <c r="A969" s="5"/>
       <c r="C969" s="5"/>
     </row>
-    <row r="970" spans="1:3" ht="12.5">
+    <row r="970" spans="1:3" ht="12.75">
       <c r="A970" s="5"/>
       <c r="C970" s="5"/>
     </row>
-    <row r="971" spans="1:3" ht="12.5">
+    <row r="971" spans="1:3" ht="12.75">
       <c r="A971" s="5"/>
       <c r="C971" s="5"/>
     </row>
-    <row r="972" spans="1:3" ht="12.5">
+    <row r="972" spans="1:3" ht="12.75">
       <c r="A972" s="5"/>
       <c r="C972" s="5"/>
     </row>
-    <row r="973" spans="1:3" ht="12.5">
+    <row r="973" spans="1:3" ht="12.75">
       <c r="A973" s="5"/>
       <c r="C973" s="5"/>
     </row>
-    <row r="974" spans="1:3" ht="12.5">
+    <row r="974" spans="1:3" ht="12.75">
       <c r="A974" s="5"/>
       <c r="C974" s="5"/>
     </row>
-    <row r="975" spans="1:3" ht="12.5">
+    <row r="975" spans="1:3" ht="12.75">
       <c r="A975" s="5"/>
       <c r="C975" s="5"/>
     </row>
-    <row r="976" spans="1:3" ht="12.5">
+    <row r="976" spans="1:3" ht="12.75">
       <c r="A976" s="5"/>
       <c r="C976" s="5"/>
     </row>
-    <row r="977" spans="1:3" ht="12.5">
+    <row r="977" spans="1:3" ht="12.75">
       <c r="A977" s="5"/>
       <c r="C977" s="5"/>
     </row>
-    <row r="978" spans="1:3" ht="12.5">
+    <row r="978" spans="1:3" ht="12.75">
       <c r="A978" s="5"/>
       <c r="C978" s="5"/>
     </row>
-    <row r="979" spans="1:3" ht="12.5">
+    <row r="979" spans="1:3" ht="12.75">
       <c r="A979" s="5"/>
       <c r="C979" s="5"/>
     </row>
-    <row r="980" spans="1:3" ht="12.5">
+    <row r="980" spans="1:3" ht="12.75">
       <c r="A980" s="5"/>
       <c r="C980" s="5"/>
     </row>
-    <row r="981" spans="1:3" ht="12.5">
+    <row r="981" spans="1:3" ht="12.75">
       <c r="A981" s="5"/>
       <c r="C981" s="5"/>
     </row>
-    <row r="982" spans="1:3" ht="12.5">
+    <row r="982" spans="1:3" ht="12.75">
       <c r="A982" s="5"/>
       <c r="C982" s="5"/>
     </row>
-    <row r="983" spans="1:3" ht="12.5">
+    <row r="983" spans="1:3" ht="12.75">
       <c r="A983" s="5"/>
       <c r="C983" s="5"/>
     </row>
-    <row r="984" spans="1:3" ht="12.5">
+    <row r="984" spans="1:3" ht="12.75">
       <c r="A984" s="5"/>
       <c r="C984" s="5"/>
     </row>
-    <row r="985" spans="1:3" ht="12.5">
+    <row r="985" spans="1:3" ht="12.75">
       <c r="A985" s="5"/>
       <c r="C985" s="5"/>
     </row>
-    <row r="986" spans="1:3" ht="12.5">
+    <row r="986" spans="1:3" ht="12.75">
       <c r="A986" s="5"/>
       <c r="C986" s="5"/>
     </row>
-    <row r="987" spans="1:3" ht="12.5">
+    <row r="987" spans="1:3" ht="12.75">
       <c r="A987" s="5"/>
       <c r="C987" s="5"/>
     </row>
-    <row r="988" spans="1:3" ht="12.5">
+    <row r="988" spans="1:3" ht="12.75">
       <c r="A988" s="5"/>
       <c r="C988" s="5"/>
     </row>
-    <row r="989" spans="1:3" ht="12.5">
+    <row r="989" spans="1:3" ht="12.75">
       <c r="A989" s="5"/>
       <c r="C989" s="5"/>
     </row>
-    <row r="990" spans="1:3" ht="12.5">
+    <row r="990" spans="1:3" ht="12.75">
       <c r="A990" s="5"/>
       <c r="C990" s="5"/>
     </row>
-    <row r="991" spans="1:3" ht="12.5">
+    <row r="991" spans="1:3" ht="12.75">
       <c r="A991" s="5"/>
       <c r="C991" s="5"/>
     </row>
-    <row r="992" spans="1:3" ht="12.5">
+    <row r="992" spans="1:3" ht="12.75">
       <c r="A992" s="5"/>
       <c r="C992" s="5"/>
     </row>
-    <row r="993" spans="1:3" ht="12.5">
+    <row r="993" spans="1:3" ht="12.75">
       <c r="A993" s="5"/>
       <c r="C993" s="5"/>
     </row>
-    <row r="994" spans="1:3" ht="12.5">
+    <row r="994" spans="1:3" ht="12.75">
       <c r="A994" s="5"/>
       <c r="C994" s="5"/>
     </row>
-    <row r="995" spans="1:3" ht="12.5">
+    <row r="995" spans="1:3" ht="12.75">
       <c r="A995" s="5"/>
       <c r="C995" s="5"/>
-    </row>
-    <row r="996" spans="1:3" ht="12.5">
-      <c r="A996" s="5"/>
-      <c r="C996" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/data/撲克資料.xlsx
+++ b/data/撲克資料.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my program\NLP\NLP_Poker_Chinese\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFF550F-4104-45E0-8B7A-0708B9BF8CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0678F9-24E3-4082-B011-D0E39AF7F4B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1294,11 +1294,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1603,2318 +1603,2321 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C235"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="50.7109375" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:3" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="13" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="14" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="15" spans="1:3" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="16" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="17" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="18" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="19" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="20" spans="1:3" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="21" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="22" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="23" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="24" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="25" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="26" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="27" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="28" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="29" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="30" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="31" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="32" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="33" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="34" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="35" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="36" spans="1:3" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="37" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="1" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="38" spans="1:3" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="39" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="40" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="41" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C41" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="C41" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="1" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="A43" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="44" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="45" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="46" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="47" spans="1:3" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="48" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="49" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="50" spans="1:3" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    <row r="51" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="52" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="1" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="53" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="54" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+    <row r="55" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    <row r="56" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="57" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="58" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="59" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="60" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="1" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="61" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+    <row r="62" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+    <row r="63" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+    <row r="64" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+    <row r="65" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+    <row r="66" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="67" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="68" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="69" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+    <row r="70" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+    <row r="71" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+    <row r="72" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+    <row r="73" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+    <row r="74" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+    <row r="75" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+    <row r="76" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+    <row r="77" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+    <row r="78" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+    <row r="79" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+    <row r="80" spans="1:3" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+    <row r="81" spans="1:3" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+    <row r="82" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+    <row r="83" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="A84" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+    <row r="85" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+    <row r="86" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B86" t="s">
-        <v>125</v>
-      </c>
-      <c r="C86" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="B86" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B87" t="s">
-        <v>125</v>
-      </c>
-      <c r="C87" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="B87" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B88" t="s">
-        <v>125</v>
-      </c>
-      <c r="C88" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="B88" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B89" t="s">
-        <v>125</v>
-      </c>
-      <c r="C89" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="B89" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B90" t="s">
-        <v>125</v>
-      </c>
-      <c r="C90" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="B90" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B91" t="s">
-        <v>125</v>
-      </c>
-      <c r="C91" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="B91" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B92" t="s">
-        <v>125</v>
-      </c>
-      <c r="C92" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="B92" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B93" t="s">
-        <v>125</v>
-      </c>
-      <c r="C93" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+      <c r="B93" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B94" t="s">
-        <v>125</v>
-      </c>
-      <c r="C94" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+      <c r="B94" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B95" t="s">
-        <v>125</v>
-      </c>
-      <c r="C95" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+      <c r="B95" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B96" t="s">
-        <v>125</v>
-      </c>
-      <c r="C96" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="B96" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B97" t="s">
-        <v>125</v>
-      </c>
-      <c r="C97" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="B97" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B98" t="s">
-        <v>125</v>
-      </c>
-      <c r="C98" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="B98" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B99" t="s">
-        <v>125</v>
-      </c>
-      <c r="C99" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="B99" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B100" t="s">
-        <v>125</v>
-      </c>
-      <c r="C100" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="B100" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B101" t="s">
-        <v>125</v>
-      </c>
-      <c r="C101" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="B101" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B102" t="s">
-        <v>125</v>
-      </c>
-      <c r="C102" t="s">
+      <c r="B102" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="A103" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B103" t="s">
-        <v>125</v>
-      </c>
-      <c r="C103" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+      <c r="B103" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B104" t="s">
-        <v>125</v>
-      </c>
-      <c r="C104" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+      <c r="B104" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B105" t="s">
-        <v>125</v>
-      </c>
-      <c r="C105" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+      <c r="B105" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B106" t="s">
-        <v>125</v>
-      </c>
-      <c r="C106" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="B106" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B107" t="s">
-        <v>125</v>
-      </c>
-      <c r="C107" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="B107" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B108" t="s">
-        <v>125</v>
-      </c>
-      <c r="C108" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+      <c r="B108" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B109" t="s">
-        <v>125</v>
-      </c>
-      <c r="C109" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="B109" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B110" t="s">
-        <v>125</v>
-      </c>
-      <c r="C110" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="B110" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B111" t="s">
-        <v>125</v>
-      </c>
-      <c r="C111" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+      <c r="B111" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B112" t="s">
-        <v>125</v>
-      </c>
-      <c r="C112" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+      <c r="B112" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B113" t="s">
-        <v>125</v>
-      </c>
-      <c r="C113" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+      <c r="B113" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B114" t="s">
-        <v>125</v>
-      </c>
-      <c r="C114" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+      <c r="B114" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B115" t="s">
-        <v>125</v>
-      </c>
-      <c r="C115" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="B115" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B116" t="s">
-        <v>125</v>
-      </c>
-      <c r="C116" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+      <c r="B116" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B117" t="s">
-        <v>125</v>
-      </c>
-      <c r="C117" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+      <c r="B117" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B118" t="s">
-        <v>125</v>
-      </c>
-      <c r="C118" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+      <c r="B118" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B119" t="s">
-        <v>125</v>
-      </c>
-      <c r="C119" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+      <c r="B119" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B120" t="s">
-        <v>125</v>
-      </c>
-      <c r="C120" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="B120" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B121" t="s">
-        <v>125</v>
-      </c>
-      <c r="C121" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+      <c r="B121" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B122" t="s">
-        <v>125</v>
-      </c>
-      <c r="C122" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="B122" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B123" t="s">
-        <v>125</v>
-      </c>
-      <c r="C123" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+      <c r="B123" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B124" t="s">
-        <v>125</v>
-      </c>
-      <c r="C124" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="B124" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B125" t="s">
-        <v>125</v>
-      </c>
-      <c r="C125" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+      <c r="B125" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B126" t="s">
-        <v>125</v>
-      </c>
-      <c r="C126" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
+      <c r="B126" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B127" t="s">
-        <v>125</v>
-      </c>
-      <c r="C127" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
+      <c r="B127" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B128" t="s">
-        <v>125</v>
-      </c>
-      <c r="C128" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+      <c r="B128" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B129" t="s">
-        <v>125</v>
-      </c>
-      <c r="C129" t="s">
+      <c r="B129" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+      <c r="A130" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B130" t="s">
-        <v>125</v>
-      </c>
-      <c r="C130" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="B130" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B131" t="s">
-        <v>125</v>
-      </c>
-      <c r="C131" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+      <c r="B131" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B132" t="s">
-        <v>125</v>
-      </c>
-      <c r="C132" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
+      <c r="B132" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B133" t="s">
-        <v>125</v>
-      </c>
-      <c r="C133" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
+      <c r="B133" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B134" t="s">
-        <v>125</v>
-      </c>
-      <c r="C134" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+      <c r="B134" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B135" t="s">
-        <v>125</v>
-      </c>
-      <c r="C135" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
+      <c r="B135" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B136" t="s">
-        <v>125</v>
-      </c>
-      <c r="C136" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+      <c r="B136" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B137" t="s">
-        <v>125</v>
-      </c>
-      <c r="C137" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
+      <c r="B137" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B138" t="s">
-        <v>125</v>
-      </c>
-      <c r="C138" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
+      <c r="B138" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B139" t="s">
-        <v>125</v>
-      </c>
-      <c r="C139" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
+      <c r="B139" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B140" t="s">
-        <v>125</v>
-      </c>
-      <c r="C140" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
+      <c r="B140" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B141" t="s">
-        <v>125</v>
-      </c>
-      <c r="C141" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
+      <c r="B141" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B142" t="s">
-        <v>125</v>
-      </c>
-      <c r="C142" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
+      <c r="B142" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B143" t="s">
-        <v>125</v>
-      </c>
-      <c r="C143" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
+      <c r="B143" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B144" t="s">
-        <v>125</v>
-      </c>
-      <c r="C144" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
+      <c r="B144" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B145" t="s">
-        <v>125</v>
-      </c>
-      <c r="C145" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
+      <c r="B145" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C146" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
+    <row r="147" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C147" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
+    <row r="148" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C148" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+    <row r="149" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C149" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
+    <row r="150" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C150" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
+    <row r="151" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C151" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
+    <row r="152" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C152" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
+    <row r="153" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B153" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C153" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
+    <row r="154" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C154" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
+    <row r="155" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C155" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
+    <row r="156" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C156" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
+    <row r="157" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C157" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
+    <row r="158" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C158" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+    <row r="159" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C159" s="1" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
+    <row r="160" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B160" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C160" t="s">
+      <c r="C160" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
+    <row r="161" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B161" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C161" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
+    <row r="162" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B162" t="s">
-        <v>199</v>
-      </c>
-      <c r="C162" t="s">
+      <c r="B162" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C162" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
+    <row r="163" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B163" t="s">
-        <v>199</v>
-      </c>
-      <c r="C163" t="s">
+      <c r="B163" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C163" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
+    <row r="164" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B164" t="s">
-        <v>199</v>
-      </c>
-      <c r="C164" t="s">
+      <c r="B164" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C164" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
+    <row r="165" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B165" t="s">
-        <v>199</v>
-      </c>
-      <c r="C165" t="s">
+      <c r="B165" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C165" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
+    <row r="166" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B166" t="s">
-        <v>199</v>
-      </c>
-      <c r="C166" t="s">
+      <c r="B166" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C166" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
+    <row r="167" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B167" t="s">
-        <v>199</v>
-      </c>
-      <c r="C167" t="s">
+      <c r="B167" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C167" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
+    <row r="168" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C168" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
+    <row r="169" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B169" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C169" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+    <row r="170" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B170" t="s">
-        <v>199</v>
-      </c>
-      <c r="C170" t="s">
+      <c r="B170" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C170" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
+    <row r="171" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B171" t="s">
-        <v>199</v>
-      </c>
-      <c r="C171" t="s">
+      <c r="B171" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C171" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
+    <row r="172" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B172" t="s">
-        <v>199</v>
-      </c>
-      <c r="C172" t="s">
+      <c r="B172" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C172" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
+    <row r="173" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B173" t="s">
-        <v>199</v>
-      </c>
-      <c r="C173" t="s">
+      <c r="B173" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C173" s="1" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
+    <row r="174" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B174" t="s">
-        <v>199</v>
-      </c>
-      <c r="C174" t="s">
+      <c r="B174" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C174" s="1" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
+    <row r="175" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B175" t="s">
-        <v>199</v>
-      </c>
-      <c r="C175" t="s">
+      <c r="B175" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C175" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
+    <row r="176" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B176" t="s">
-        <v>199</v>
-      </c>
-      <c r="C176" t="s">
+      <c r="B176" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C176" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
+    <row r="177" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B177" t="s">
-        <v>199</v>
-      </c>
-      <c r="C177" t="s">
+      <c r="B177" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C177" s="1" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
+    <row r="178" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B178" t="s">
-        <v>199</v>
-      </c>
-      <c r="C178" t="s">
+      <c r="B178" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C178" s="1" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
+    <row r="179" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B179" t="s">
-        <v>199</v>
-      </c>
-      <c r="C179" t="s">
+      <c r="B179" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C179" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
+    <row r="180" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B180" t="s">
-        <v>199</v>
-      </c>
-      <c r="C180" t="s">
+      <c r="B180" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C180" s="1" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
+    <row r="181" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B181" t="s">
-        <v>199</v>
-      </c>
-      <c r="C181" t="s">
+      <c r="B181" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C181" s="1" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
+    <row r="182" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B182" t="s">
-        <v>199</v>
-      </c>
-      <c r="C182" t="s">
+      <c r="B182" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C182" s="1" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
+    <row r="183" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B183" t="s">
-        <v>199</v>
-      </c>
-      <c r="C183" t="s">
+      <c r="B183" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C183" s="1" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
+    <row r="184" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B184" t="s">
-        <v>199</v>
-      </c>
-      <c r="C184" t="s">
+      <c r="B184" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C184" s="1" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
+    <row r="185" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B185" t="s">
-        <v>199</v>
-      </c>
-      <c r="C185" t="s">
+      <c r="B185" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C185" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
+    <row r="186" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B186" t="s">
-        <v>199</v>
-      </c>
-      <c r="C186" t="s">
+      <c r="B186" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C186" s="1" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
+    <row r="187" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B187" t="s">
-        <v>199</v>
-      </c>
-      <c r="C187" t="s">
+      <c r="B187" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C187" s="1" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
+    <row r="188" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B188" t="s">
-        <v>199</v>
-      </c>
-      <c r="C188" t="s">
+      <c r="B188" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C188" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
+    <row r="189" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B189" t="s">
-        <v>199</v>
-      </c>
-      <c r="C189" t="s">
+      <c r="B189" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C189" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
+    <row r="190" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B190" t="s">
-        <v>199</v>
-      </c>
-      <c r="C190" t="s">
+      <c r="B190" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C190" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
+    <row r="191" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B191" t="s">
-        <v>199</v>
-      </c>
-      <c r="C191" t="s">
+      <c r="B191" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C191" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
+    <row r="192" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B192" t="s">
-        <v>199</v>
-      </c>
-      <c r="C192" t="s">
+      <c r="B192" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C192" s="1" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
+    <row r="193" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B193" t="s">
-        <v>199</v>
-      </c>
-      <c r="C193" t="s">
+      <c r="B193" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C193" s="1" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
+    <row r="194" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B194" t="s">
-        <v>199</v>
-      </c>
-      <c r="C194" t="s">
+      <c r="B194" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C194" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
+    <row r="195" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B195" t="s">
-        <v>199</v>
-      </c>
-      <c r="C195" t="s">
+      <c r="B195" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C195" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
+    <row r="196" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B196" t="s">
-        <v>199</v>
-      </c>
-      <c r="C196" t="s">
+      <c r="B196" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C196" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
+    <row r="197" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B197" t="s">
-        <v>199</v>
-      </c>
-      <c r="C197" t="s">
+      <c r="B197" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C197" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
+    <row r="198" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B198" t="s">
-        <v>199</v>
-      </c>
-      <c r="C198" t="s">
+      <c r="B198" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C198" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
+    <row r="199" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B199" t="s">
-        <v>199</v>
-      </c>
-      <c r="C199" t="s">
+      <c r="B199" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C199" s="1" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
+    <row r="200" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B200" t="s">
-        <v>199</v>
-      </c>
-      <c r="C200" t="s">
+      <c r="B200" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C200" s="1" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
+    <row r="201" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B201" t="s">
-        <v>199</v>
-      </c>
-      <c r="C201" t="s">
+      <c r="B201" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C201" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
+    <row r="202" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B202" t="s">
-        <v>199</v>
-      </c>
-      <c r="C202" t="s">
+      <c r="B202" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C202" s="1" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
+    <row r="203" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B203" t="s">
-        <v>199</v>
-      </c>
-      <c r="C203" t="s">
+      <c r="B203" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C203" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
+    <row r="204" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B204" t="s">
-        <v>199</v>
-      </c>
-      <c r="C204" t="s">
+      <c r="B204" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C204" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
+    <row r="205" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B205" t="s">
-        <v>199</v>
-      </c>
-      <c r="C205" t="s">
+      <c r="B205" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C205" s="1" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
+    <row r="206" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B206" t="s">
-        <v>199</v>
-      </c>
-      <c r="C206" t="s">
+      <c r="B206" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C206" s="1" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
+    <row r="207" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B207" t="s">
-        <v>199</v>
-      </c>
-      <c r="C207" t="s">
+      <c r="B207" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C207" s="1" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
+    <row r="208" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B208" t="s">
-        <v>199</v>
-      </c>
-      <c r="C208" t="s">
+      <c r="B208" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C208" s="1" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
+    <row r="209" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B209" t="s">
-        <v>199</v>
-      </c>
-      <c r="C209" t="s">
+      <c r="B209" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C209" s="1" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
+    <row r="210" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B210" t="s">
-        <v>199</v>
-      </c>
-      <c r="C210" t="s">
+      <c r="B210" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C210" s="1" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>300</v>
       </c>
@@ -3925,7 +3928,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>283</v>
       </c>
@@ -3936,7 +3939,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>299</v>
       </c>
@@ -3947,7 +3950,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>286</v>
       </c>
@@ -3958,7 +3961,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>288</v>
       </c>
@@ -3969,223 +3972,223 @@
         <v>289</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
+    <row r="216" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B216" t="s">
-        <v>199</v>
-      </c>
-      <c r="C216" t="s">
+      <c r="B216" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C216" s="1" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
+    <row r="217" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B217" t="s">
-        <v>199</v>
-      </c>
-      <c r="C217" t="s">
+      <c r="B217" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C217" s="1" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
+    <row r="218" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B218" t="s">
-        <v>199</v>
-      </c>
-      <c r="C218" t="s">
+      <c r="B218" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C218" s="1" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
+    <row r="219" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B219" t="s">
-        <v>199</v>
-      </c>
-      <c r="C219" t="s">
+      <c r="B219" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C219" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
+    <row r="220" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B220" t="s">
-        <v>199</v>
-      </c>
-      <c r="C220" t="s">
+      <c r="B220" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C220" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
+    <row r="221" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B221" t="s">
-        <v>199</v>
-      </c>
-      <c r="C221" t="s">
+      <c r="B221" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C221" s="1" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" s="2" t="s">
+    <row r="222" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B222" s="2" t="s">
+      <c r="B222" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C222" s="2" t="s">
+      <c r="C222" s="1" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" s="2" t="s">
+    <row r="223" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B223" s="2" t="s">
+      <c r="B223" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C223" s="2" t="s">
+      <c r="C223" s="1" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" s="2" t="s">
+    <row r="224" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B224" s="2" t="s">
+      <c r="B224" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C224" s="2" t="s">
+      <c r="C224" s="1" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" s="2" t="s">
+    <row r="225" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B225" s="2" t="s">
+      <c r="B225" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C225" s="2" t="s">
+      <c r="C225" s="1" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" s="2" t="s">
+    <row r="226" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B226" s="2" t="s">
+      <c r="B226" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C226" s="2" t="s">
+      <c r="C226" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" s="2" t="s">
+    <row r="227" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B227" s="2" t="s">
+      <c r="B227" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C227" s="2" t="s">
+      <c r="C227" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" s="2" t="s">
+    <row r="228" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B228" s="2" t="s">
+      <c r="B228" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C228" s="2" t="s">
+      <c r="C228" s="1" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" s="2" t="s">
+    <row r="229" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B229" s="2" t="s">
+      <c r="B229" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C229" s="2" t="s">
+      <c r="C229" s="1" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" s="3" t="s">
+    <row r="230" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B230" s="3" t="s">
+      <c r="B230" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C230" s="3" t="s">
+      <c r="C230" s="1" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" s="3" t="s">
+    <row r="231" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B231" s="3" t="s">
+      <c r="B231" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C231" s="3" t="s">
+      <c r="C231" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" s="3" t="s">
+    <row r="232" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B232" s="3" t="s">
+      <c r="B232" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C232" s="3" t="s">
+      <c r="C232" s="1" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233" s="3" t="s">
+    <row r="233" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B233" s="3" t="s">
+      <c r="B233" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C233" s="3" t="s">
+      <c r="C233" s="1" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234" s="3" t="s">
+    <row r="234" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B234" s="3" t="s">
+      <c r="B234" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C234" s="3" t="s">
+      <c r="C234" s="1" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235" s="3" t="s">
+    <row r="235" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B235" s="3" t="s">
+      <c r="B235" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C235" s="3" t="s">
+      <c r="C235" s="1" t="s">
         <v>404</v>
       </c>
     </row>
